--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa-my.sharepoint.com/personal/pablo_gomes_reenergisa_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BD2B99-D037-4819-BE50-900EC9292116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{16BD2B99-D037-4819-BE50-900EC9292116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D244EF3E-9C2E-45B1-9A9B-B678E0965595}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="92">
   <si>
     <t>Usuário</t>
   </si>
@@ -121,9 +121,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>Neg Aberta</t>
-  </si>
-  <si>
     <t>LEAD AGENDADO</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
   </si>
   <si>
     <t>Padaria e Confeitaria Pao Imperial LTDA</t>
-  </si>
-  <si>
-    <t>Venda</t>
   </si>
   <si>
     <t>FECHAMENTO DE VENDA</t>
@@ -703,7 +697,7 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -747,16 +741,16 @@
         <v>604128</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O2">
         <v>8.3699999999999992</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R2" t="e">
         <v>#N/A</v>
@@ -764,10 +758,10 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
         <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -776,19 +770,19 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
         <v>33</v>
-      </c>
-      <c r="H3">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>34</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
@@ -803,16 +797,16 @@
         <v>593213</v>
       </c>
       <c r="N3" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O3">
         <v>3.66</v>
       </c>
       <c r="P3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R3" t="s">
         <v>26</v>
@@ -820,10 +814,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -832,19 +826,19 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4">
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
@@ -859,16 +853,16 @@
         <v>595396</v>
       </c>
       <c r="N4" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O4">
         <v>11.66</v>
       </c>
       <c r="P4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R4" t="s">
         <v>26</v>
@@ -876,10 +870,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -888,19 +882,19 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H5">
         <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
         <v>25</v>
@@ -915,16 +909,16 @@
         <v>588146</v>
       </c>
       <c r="N5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O5">
         <v>67.37</v>
       </c>
       <c r="P5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R5" t="s">
         <v>26</v>
@@ -932,10 +926,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -944,13 +938,13 @@
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -971,16 +965,16 @@
         <v>603017</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O6">
         <v>1.89</v>
       </c>
       <c r="P6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R6" t="e">
         <v>#N/A</v>
@@ -988,10 +982,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -1000,13 +994,13 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -1027,16 +1021,16 @@
         <v>601944</v>
       </c>
       <c r="N7" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O7">
         <v>1.67</v>
       </c>
       <c r="P7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R7" t="s">
         <v>26</v>
@@ -1044,10 +1038,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -1056,19 +1050,19 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8">
         <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J8" t="s">
         <v>25</v>
@@ -1083,16 +1077,16 @@
         <v>591481</v>
       </c>
       <c r="N8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O8">
         <v>10</v>
       </c>
       <c r="P8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R8" t="s">
         <v>26</v>
@@ -1100,10 +1094,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -1112,13 +1106,13 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -1139,16 +1133,16 @@
         <v>601025</v>
       </c>
       <c r="N9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O9">
         <v>41.62</v>
       </c>
       <c r="P9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R9" t="s">
         <v>26</v>
@@ -1156,10 +1150,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -1168,13 +1162,13 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -1195,16 +1189,16 @@
         <v>601583</v>
       </c>
       <c r="N10" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R10" t="s">
         <v>26</v>
@@ -1212,10 +1206,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -1224,19 +1218,19 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11">
         <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" t="s">
         <v>25</v>
@@ -1251,16 +1245,16 @@
         <v>594789</v>
       </c>
       <c r="N11" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O11">
         <v>10.75</v>
       </c>
       <c r="P11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R11" t="s">
         <v>26</v>
@@ -1268,10 +1262,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -1280,13 +1274,13 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -1307,16 +1301,16 @@
         <v>603608</v>
       </c>
       <c r="N12" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O12">
         <v>6.94</v>
       </c>
       <c r="P12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R12" t="e">
         <v>#N/A</v>
@@ -1324,10 +1318,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -1336,13 +1330,13 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H13">
         <v>11</v>
@@ -1363,16 +1357,16 @@
         <v>604194</v>
       </c>
       <c r="N13" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O13">
         <v>2.98</v>
       </c>
       <c r="P13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R13" t="e">
         <v>#N/A</v>
@@ -1380,31 +1374,31 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
         <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J14" t="s">
         <v>25</v>
@@ -1419,16 +1413,16 @@
         <v>589870</v>
       </c>
       <c r="N14" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O14">
         <v>27.46</v>
       </c>
       <c r="P14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R14" t="s">
         <v>26</v>
@@ -1436,10 +1430,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -1448,19 +1442,19 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H15">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J15" t="s">
         <v>25</v>
@@ -1475,16 +1469,16 @@
         <v>598334</v>
       </c>
       <c r="N15" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O15">
         <v>9.7899999999999991</v>
       </c>
       <c r="P15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R15" t="s">
         <v>26</v>
@@ -1492,10 +1486,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -1504,19 +1498,19 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H16">
         <v>20</v>
       </c>
       <c r="I16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J16" t="s">
         <v>25</v>
@@ -1531,16 +1525,16 @@
         <v>594209</v>
       </c>
       <c r="N16" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O16">
         <v>41.75</v>
       </c>
       <c r="P16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R16" t="s">
         <v>26</v>
@@ -1548,10 +1542,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
         <v>19</v>
@@ -1560,7 +1554,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
@@ -1572,7 +1566,7 @@
         <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J17" t="s">
         <v>25</v>
@@ -1587,16 +1581,16 @@
         <v>598353</v>
       </c>
       <c r="N17" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O17">
         <v>6.9</v>
       </c>
       <c r="P17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R17" t="s">
         <v>26</v>
@@ -1604,10 +1598,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
@@ -1616,19 +1610,19 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J18" t="s">
         <v>25</v>
@@ -1643,16 +1637,16 @@
         <v>585567</v>
       </c>
       <c r="N18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O18">
         <v>1.41</v>
       </c>
       <c r="P18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R18" t="s">
         <v>26</v>
@@ -1660,10 +1654,10 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
@@ -1672,19 +1666,19 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H19">
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J19" t="s">
         <v>25</v>
@@ -1699,16 +1693,16 @@
         <v>585435</v>
       </c>
       <c r="N19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O19">
         <v>34.979999999999997</v>
       </c>
       <c r="P19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -1716,10 +1710,10 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -1728,19 +1722,19 @@
         <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s">
         <v>22</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H20">
         <v>6</v>
       </c>
       <c r="I20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J20" t="s">
         <v>25</v>
@@ -1755,16 +1749,16 @@
         <v>587363</v>
       </c>
       <c r="N20" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O20">
         <v>7.85</v>
       </c>
       <c r="P20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R20" t="s">
         <v>26</v>
@@ -1772,10 +1766,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -1784,19 +1778,19 @@
         <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
         <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H21">
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J21" t="s">
         <v>25</v>
@@ -1811,16 +1805,16 @@
         <v>589815</v>
       </c>
       <c r="N21" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="O21">
         <v>30.92</v>
       </c>
       <c r="P21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Q21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R21" t="s">
         <v>26</v>
@@ -1828,10 +1822,10 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
@@ -1840,13 +1834,13 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
         <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H22">
         <v>7</v>
@@ -1867,16 +1861,16 @@
         <v>602969</v>
       </c>
       <c r="N22" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O22">
         <v>6.12</v>
       </c>
       <c r="P22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R22" t="s">
         <v>26</v>
@@ -1884,10 +1878,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
@@ -1896,19 +1890,19 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F23" t="s">
         <v>22</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H23">
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J23" t="s">
         <v>25</v>
@@ -1923,16 +1917,16 @@
         <v>593210</v>
       </c>
       <c r="N23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O23">
         <v>3.5</v>
       </c>
       <c r="P23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R23" t="s">
         <v>26</v>
@@ -1940,10 +1934,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -1952,13 +1946,13 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>22</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -1979,16 +1973,16 @@
         <v>601537</v>
       </c>
       <c r="N24" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O24">
         <v>4.63</v>
       </c>
       <c r="P24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R24" t="s">
         <v>26</v>
@@ -1996,10 +1990,10 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -2008,19 +2002,19 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25">
         <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J25" t="s">
         <v>25</v>
@@ -2035,16 +2029,16 @@
         <v>588663</v>
       </c>
       <c r="N25" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O25">
         <v>35.78</v>
       </c>
       <c r="P25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R25" t="s">
         <v>26</v>
@@ -2052,10 +2046,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
@@ -2064,19 +2058,19 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
         <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H26">
         <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J26" t="s">
         <v>25</v>
@@ -2091,16 +2085,16 @@
         <v>591629</v>
       </c>
       <c r="N26" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="O26">
         <v>10.44</v>
       </c>
       <c r="P26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R26" t="s">
         <v>26</v>
@@ -2108,10 +2102,10 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -2120,19 +2114,19 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
         <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H27">
         <v>24</v>
       </c>
       <c r="I27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J27" t="s">
         <v>25</v>
@@ -2147,16 +2141,16 @@
         <v>582148</v>
       </c>
       <c r="N27" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="O27">
         <v>7.87</v>
       </c>
       <c r="P27" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Q27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R27" t="s">
         <v>26</v>
@@ -2178,40 +2172,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
         <v>75</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>76</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>77</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>78</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>79</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>80</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>81</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>82</v>
-      </c>
-      <c r="K1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2219,10 +2213,10 @@
         <v>46204</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>937.51199999999994</v>
@@ -2257,10 +2251,10 @@
         <v>46235</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>279.04500000000002</v>
@@ -2295,13 +2289,13 @@
         <v>46235</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>51.615999999997996</v>
@@ -2319,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K4">
         <v>12</v>
@@ -2333,13 +2327,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>104.44589999999999</v>
@@ -2357,7 +2351,7 @@
         <v>4.0816326530612242E-2</v>
       </c>
       <c r="J5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K5">
         <v>13</v>
@@ -2371,13 +2365,13 @@
         <v>46235</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>3.7643</v>
@@ -2395,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -2409,10 +2403,10 @@
         <v>46235</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>43.552</v>
@@ -2447,13 +2441,13 @@
         <v>46235</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>49.051300000000005</v>
@@ -2485,13 +2479,13 @@
         <v>46235</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E9">
         <v>18.294</v>
@@ -2536,13 +2530,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2550,7 +2544,7 @@
         <v>46204</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -2561,7 +2555,7 @@
         <v>46204</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C3">
         <v>15</v>
@@ -2572,7 +2566,7 @@
         <v>46235</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -2583,7 +2577,7 @@
         <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -2594,7 +2588,7 @@
         <v>46235</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>19</v>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa-my.sharepoint.com/personal/pablo_gomes_reenergisa_com_br/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{16BD2B99-D037-4819-BE50-900EC9292116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D244EF3E-9C2E-45B1-9A9B-B678E0965595}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BD2B99-D037-4819-BE50-900EC9292116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="94">
   <si>
     <t>Usuário</t>
   </si>
@@ -121,6 +121,9 @@
     <t>1</t>
   </si>
   <si>
+    <t>Neg Aberta</t>
+  </si>
+  <si>
     <t>LEAD AGENDADO</t>
   </si>
   <si>
@@ -215,6 +218,9 @@
   </si>
   <si>
     <t>Padaria e Confeitaria Pao Imperial LTDA</t>
+  </si>
+  <si>
+    <t>Venda</t>
   </si>
   <si>
     <t>FECHAMENTO DE VENDA</t>
@@ -697,7 +703,7 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -741,16 +747,16 @@
         <v>604128</v>
       </c>
       <c r="N2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O2">
         <v>8.3699999999999992</v>
       </c>
       <c r="P2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R2" t="e">
         <v>#N/A</v>
@@ -758,10 +764,10 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -770,19 +776,19 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3">
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
@@ -797,16 +803,16 @@
         <v>593213</v>
       </c>
       <c r="N3" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O3">
         <v>3.66</v>
       </c>
       <c r="P3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R3" t="s">
         <v>26</v>
@@ -814,10 +820,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -826,19 +832,19 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4">
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
@@ -853,16 +859,16 @@
         <v>595396</v>
       </c>
       <c r="N4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O4">
         <v>11.66</v>
       </c>
       <c r="P4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R4" t="s">
         <v>26</v>
@@ -870,10 +876,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -882,19 +888,19 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5">
         <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
         <v>25</v>
@@ -909,16 +915,16 @@
         <v>588146</v>
       </c>
       <c r="N5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O5">
         <v>67.37</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R5" t="s">
         <v>26</v>
@@ -926,10 +932,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -938,13 +944,13 @@
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -965,16 +971,16 @@
         <v>603017</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O6">
         <v>1.89</v>
       </c>
       <c r="P6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R6" t="e">
         <v>#N/A</v>
@@ -982,10 +988,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -994,13 +1000,13 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -1021,16 +1027,16 @@
         <v>601944</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O7">
         <v>1.67</v>
       </c>
       <c r="P7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R7" t="s">
         <v>26</v>
@@ -1038,10 +1044,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -1050,19 +1056,19 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8">
         <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J8" t="s">
         <v>25</v>
@@ -1077,16 +1083,16 @@
         <v>591481</v>
       </c>
       <c r="N8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O8">
         <v>10</v>
       </c>
       <c r="P8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R8" t="s">
         <v>26</v>
@@ -1094,10 +1100,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -1106,13 +1112,13 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -1133,16 +1139,16 @@
         <v>601025</v>
       </c>
       <c r="N9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O9">
         <v>41.62</v>
       </c>
       <c r="P9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R9" t="s">
         <v>26</v>
@@ -1150,10 +1156,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -1162,13 +1168,13 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -1189,16 +1195,16 @@
         <v>601583</v>
       </c>
       <c r="N10" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R10" t="s">
         <v>26</v>
@@ -1206,10 +1212,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -1218,19 +1224,19 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11">
         <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J11" t="s">
         <v>25</v>
@@ -1245,16 +1251,16 @@
         <v>594789</v>
       </c>
       <c r="N11" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O11">
         <v>10.75</v>
       </c>
       <c r="P11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R11" t="s">
         <v>26</v>
@@ -1262,10 +1268,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -1274,13 +1280,13 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -1301,16 +1307,16 @@
         <v>603608</v>
       </c>
       <c r="N12" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O12">
         <v>6.94</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R12" t="e">
         <v>#N/A</v>
@@ -1318,10 +1324,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -1330,13 +1336,13 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13">
         <v>11</v>
@@ -1357,16 +1363,16 @@
         <v>604194</v>
       </c>
       <c r="N13" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O13">
         <v>2.98</v>
       </c>
       <c r="P13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R13" t="e">
         <v>#N/A</v>
@@ -1374,31 +1380,31 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J14" t="s">
         <v>25</v>
@@ -1413,16 +1419,16 @@
         <v>589870</v>
       </c>
       <c r="N14" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O14">
         <v>27.46</v>
       </c>
       <c r="P14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R14" t="s">
         <v>26</v>
@@ -1430,10 +1436,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -1442,19 +1448,19 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H15">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J15" t="s">
         <v>25</v>
@@ -1469,16 +1475,16 @@
         <v>598334</v>
       </c>
       <c r="N15" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O15">
         <v>9.7899999999999991</v>
       </c>
       <c r="P15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R15" t="s">
         <v>26</v>
@@ -1486,10 +1492,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -1498,19 +1504,19 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H16">
         <v>20</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
         <v>25</v>
@@ -1525,16 +1531,16 @@
         <v>594209</v>
       </c>
       <c r="N16" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O16">
         <v>41.75</v>
       </c>
       <c r="P16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R16" t="s">
         <v>26</v>
@@ -1542,10 +1548,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
         <v>19</v>
@@ -1554,7 +1560,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
@@ -1566,7 +1572,7 @@
         <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" t="s">
         <v>25</v>
@@ -1581,16 +1587,16 @@
         <v>598353</v>
       </c>
       <c r="N17" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O17">
         <v>6.9</v>
       </c>
       <c r="P17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R17" t="s">
         <v>26</v>
@@ -1598,10 +1604,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
@@ -1610,19 +1616,19 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J18" t="s">
         <v>25</v>
@@ -1637,16 +1643,16 @@
         <v>585567</v>
       </c>
       <c r="N18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O18">
         <v>1.41</v>
       </c>
       <c r="P18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R18" t="s">
         <v>26</v>
@@ -1654,10 +1660,10 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
@@ -1666,19 +1672,19 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H19">
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J19" t="s">
         <v>25</v>
@@ -1693,16 +1699,16 @@
         <v>585435</v>
       </c>
       <c r="N19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O19">
         <v>34.979999999999997</v>
       </c>
       <c r="P19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -1710,10 +1716,10 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -1722,19 +1728,19 @@
         <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
         <v>22</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20">
         <v>6</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J20" t="s">
         <v>25</v>
@@ -1749,16 +1755,16 @@
         <v>587363</v>
       </c>
       <c r="N20" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O20">
         <v>7.85</v>
       </c>
       <c r="P20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R20" t="s">
         <v>26</v>
@@ -1766,10 +1772,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -1778,19 +1784,19 @@
         <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
         <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H21">
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J21" t="s">
         <v>25</v>
@@ -1805,16 +1811,16 @@
         <v>589815</v>
       </c>
       <c r="N21" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="O21">
         <v>30.92</v>
       </c>
       <c r="P21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R21" t="s">
         <v>26</v>
@@ -1822,10 +1828,10 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
@@ -1834,13 +1840,13 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
         <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H22">
         <v>7</v>
@@ -1861,16 +1867,16 @@
         <v>602969</v>
       </c>
       <c r="N22" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O22">
         <v>6.12</v>
       </c>
       <c r="P22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R22" t="s">
         <v>26</v>
@@ -1878,10 +1884,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
@@ -1890,19 +1896,19 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
         <v>22</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23">
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J23" t="s">
         <v>25</v>
@@ -1917,16 +1923,16 @@
         <v>593210</v>
       </c>
       <c r="N23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O23">
         <v>3.5</v>
       </c>
       <c r="P23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R23" t="s">
         <v>26</v>
@@ -1934,10 +1940,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -1946,13 +1952,13 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
         <v>22</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -1973,16 +1979,16 @@
         <v>601537</v>
       </c>
       <c r="N24" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O24">
         <v>4.63</v>
       </c>
       <c r="P24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R24" t="s">
         <v>26</v>
@@ -1990,10 +1996,10 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -2002,19 +2008,19 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25">
         <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J25" t="s">
         <v>25</v>
@@ -2029,16 +2035,16 @@
         <v>588663</v>
       </c>
       <c r="N25" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O25">
         <v>35.78</v>
       </c>
       <c r="P25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R25" t="s">
         <v>26</v>
@@ -2046,10 +2052,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
@@ -2058,19 +2064,19 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
         <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26">
         <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J26" t="s">
         <v>25</v>
@@ -2085,16 +2091,16 @@
         <v>591629</v>
       </c>
       <c r="N26" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O26">
         <v>10.44</v>
       </c>
       <c r="P26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R26" t="s">
         <v>26</v>
@@ -2102,10 +2108,10 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -2114,19 +2120,19 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
         <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H27">
         <v>24</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J27" t="s">
         <v>25</v>
@@ -2141,16 +2147,16 @@
         <v>582148</v>
       </c>
       <c r="N27" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="O27">
         <v>7.87</v>
       </c>
       <c r="P27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R27" t="s">
         <v>26</v>
@@ -2172,40 +2178,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2213,10 +2219,10 @@
         <v>46204</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <v>937.51199999999994</v>
@@ -2251,10 +2257,10 @@
         <v>46235</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>279.04500000000002</v>
@@ -2289,13 +2295,13 @@
         <v>46235</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E4">
         <v>51.615999999997996</v>
@@ -2313,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K4">
         <v>12</v>
@@ -2327,13 +2333,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5">
         <v>104.44589999999999</v>
@@ -2351,7 +2357,7 @@
         <v>4.0816326530612242E-2</v>
       </c>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K5">
         <v>13</v>
@@ -2365,13 +2371,13 @@
         <v>46235</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
         <v>86</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
       </c>
       <c r="E6">
         <v>3.7643</v>
@@ -2389,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -2403,10 +2409,10 @@
         <v>46235</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>43.552</v>
@@ -2441,13 +2447,13 @@
         <v>46235</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E8">
         <v>49.051300000000005</v>
@@ -2479,13 +2485,13 @@
         <v>46235</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>18.294</v>
@@ -2530,13 +2536,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" t="s">
-        <v>66</v>
-      </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2544,7 +2550,7 @@
         <v>46204</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -2555,7 +2561,7 @@
         <v>46204</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>15</v>
@@ -2566,7 +2572,7 @@
         <v>46235</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -2577,7 +2583,7 @@
         <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -2588,7 +2594,7 @@
         <v>46235</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>19</v>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BD2B99-D037-4819-BE50-900EC9292116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C2D850-E783-4AA4-87DE-B6D1AF382382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="97">
   <si>
     <t>Usuário</t>
   </si>
@@ -320,6 +320,15 @@
   </si>
   <si>
     <t>Qualificado</t>
+  </si>
+  <si>
+    <t>INELEGÍVEL - BAIXO CONSUMO</t>
+  </si>
+  <si>
+    <t>INELEGÍVEL CONCORRÊNCIA RETORNO 180 DIAS</t>
+  </si>
+  <si>
+    <t>FALTA DE CONTATO - DECISOR NÃO ENCONTRAD</t>
   </si>
 </sst>
 </file>
@@ -647,7 +656,7 @@
   <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="11" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -678,10 +687,10 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -734,10 +743,10 @@
       <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
       <c r="L2">
@@ -790,10 +799,10 @@
       <c r="I3" t="s">
         <v>34</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
       <c r="L3">
@@ -846,10 +855,10 @@
       <c r="I4" t="s">
         <v>34</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>26</v>
       </c>
       <c r="L4">
@@ -902,10 +911,10 @@
       <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>26</v>
       </c>
       <c r="L5">
@@ -958,10 +967,10 @@
       <c r="I6" t="s">
         <v>24</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>26</v>
       </c>
       <c r="L6">
@@ -1014,10 +1023,10 @@
       <c r="I7" t="s">
         <v>24</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>26</v>
       </c>
       <c r="L7">
@@ -1030,10 +1039,10 @@
         <v>27</v>
       </c>
       <c r="O7">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="P7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q7" t="s">
         <v>29</v>
@@ -1070,10 +1079,10 @@
       <c r="I8" t="s">
         <v>34</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>26</v>
       </c>
       <c r="L8">
@@ -1126,10 +1135,10 @@
       <c r="I9" t="s">
         <v>24</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" t="s">
         <v>26</v>
       </c>
       <c r="L9">
@@ -1182,10 +1191,10 @@
       <c r="I10" t="s">
         <v>24</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>26</v>
       </c>
       <c r="L10">
@@ -1238,10 +1247,10 @@
       <c r="I11" t="s">
         <v>34</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" t="s">
         <v>26</v>
       </c>
       <c r="L11">
@@ -1294,10 +1303,10 @@
       <c r="I12" t="s">
         <v>24</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" t="s">
         <v>26</v>
       </c>
       <c r="L12">
@@ -1350,10 +1359,10 @@
       <c r="I13" t="s">
         <v>24</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" t="s">
         <v>26</v>
       </c>
       <c r="L13">
@@ -1406,10 +1415,10 @@
       <c r="I14" t="s">
         <v>34</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" t="s">
         <v>26</v>
       </c>
       <c r="L14">
@@ -1462,10 +1471,10 @@
       <c r="I15" t="s">
         <v>34</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" t="s">
         <v>26</v>
       </c>
       <c r="L15">
@@ -1518,10 +1527,10 @@
       <c r="I16" t="s">
         <v>34</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" t="s">
         <v>26</v>
       </c>
       <c r="L16">
@@ -1574,10 +1583,10 @@
       <c r="I17" t="s">
         <v>34</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" t="s">
         <v>26</v>
       </c>
       <c r="L17">
@@ -1630,10 +1639,10 @@
       <c r="I18" t="s">
         <v>34</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" t="s">
         <v>26</v>
       </c>
       <c r="L18">
@@ -1652,7 +1661,7 @@
         <v>56</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="R18" t="s">
         <v>26</v>
@@ -1686,10 +1695,10 @@
       <c r="I19" t="s">
         <v>34</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" t="s">
         <v>26</v>
       </c>
       <c r="L19">
@@ -1708,7 +1717,7 @@
         <v>36</v>
       </c>
       <c r="Q19" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -1742,10 +1751,10 @@
       <c r="I20" t="s">
         <v>34</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" t="s">
         <v>26</v>
       </c>
       <c r="L20">
@@ -1798,10 +1807,10 @@
       <c r="I21" t="s">
         <v>34</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" t="s">
         <v>26</v>
       </c>
       <c r="L21">
@@ -1854,10 +1863,10 @@
       <c r="I22" t="s">
         <v>24</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" t="s">
         <v>26</v>
       </c>
       <c r="L22">
@@ -1873,7 +1882,7 @@
         <v>6.12</v>
       </c>
       <c r="P22" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q22" t="s">
         <v>29</v>
@@ -1910,10 +1919,10 @@
       <c r="I23" t="s">
         <v>34</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" t="s">
         <v>26</v>
       </c>
       <c r="L23">
@@ -1932,7 +1941,7 @@
         <v>56</v>
       </c>
       <c r="Q23" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="R23" t="s">
         <v>26</v>
@@ -1966,10 +1975,10 @@
       <c r="I24" t="s">
         <v>24</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" t="s">
         <v>26</v>
       </c>
       <c r="L24">
@@ -1985,7 +1994,7 @@
         <v>4.63</v>
       </c>
       <c r="P24" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q24" t="s">
         <v>29</v>
@@ -2022,10 +2031,10 @@
       <c r="I25" t="s">
         <v>34</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" t="s">
         <v>26</v>
       </c>
       <c r="L25">
@@ -2078,10 +2087,10 @@
       <c r="I26" t="s">
         <v>34</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" t="s">
         <v>26</v>
       </c>
       <c r="L26">
@@ -2134,10 +2143,10 @@
       <c r="I27" t="s">
         <v>34</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" t="s">
         <v>26</v>
       </c>
       <c r="L27">
@@ -2415,31 +2424,31 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>43.552</v>
+        <v>71.608999999999995</v>
       </c>
       <c r="E7">
-        <v>20.378700000000002</v>
+        <v>62.838799999998997</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J7">
-        <v>1.8</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="K7">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="L7">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2456,28 +2465,28 @@
         <v>86</v>
       </c>
       <c r="E8">
-        <v>49.051300000000005</v>
+        <v>75.433699999998993</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I8">
-        <v>0.1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J8">
-        <v>0.2</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2494,28 +2503,28 @@
         <v>86</v>
       </c>
       <c r="E9">
-        <v>18.294</v>
+        <v>126.43339999999999</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H9">
         <v>5</v>
       </c>
       <c r="I9">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2586,7 +2595,7 @@
         <v>74</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2597,7 +2606,7 @@
         <v>72</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C2D850-E783-4AA4-87DE-B6D1AF382382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C6DE12-E055-4BF8-9745-5229D892F594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="102">
   <si>
     <t>Usuário</t>
   </si>
@@ -329,6 +329,21 @@
   </si>
   <si>
     <t>FALTA DE CONTATO - DECISOR NÃO ENCONTRAD</t>
+  </si>
+  <si>
+    <t>FELDER COMERCIO DE PANIFICACAO LTDA EPP</t>
+  </si>
+  <si>
+    <t>Joao Vitor Brum</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>LITORAL FRUTOS DO MAR, INDUSTRIA E COMERCIO DE ALIMENTOS LTD</t>
   </si>
 </sst>
 </file>
@@ -653,10 +668,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -684,10 +699,10 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -740,10 +755,10 @@
       <c r="H2">
         <v>11</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>25</v>
       </c>
       <c r="K2" t="s">
@@ -773,10 +788,10 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -785,46 +800,46 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
         <v>25</v>
       </c>
       <c r="K3" t="s">
         <v>26</v>
       </c>
       <c r="L3">
-        <v>46231</v>
+        <v>46247</v>
       </c>
       <c r="M3">
-        <v>593213</v>
+        <v>605287</v>
       </c>
       <c r="N3" t="s">
         <v>27</v>
       </c>
       <c r="O3">
-        <v>3.66</v>
+        <v>61.58</v>
       </c>
       <c r="P3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="Q3" t="s">
         <v>29</v>
       </c>
-      <c r="R3" t="s">
-        <v>26</v>
+      <c r="R3" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -832,7 +847,7 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -850,28 +865,28 @@
         <v>33</v>
       </c>
       <c r="H4">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>25</v>
       </c>
       <c r="K4" t="s">
         <v>26</v>
       </c>
       <c r="L4">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="M4">
-        <v>595396</v>
+        <v>593213</v>
       </c>
       <c r="N4" t="s">
         <v>27</v>
       </c>
       <c r="O4">
-        <v>11.66</v>
+        <v>3.66</v>
       </c>
       <c r="P4" t="s">
         <v>36</v>
@@ -879,8 +894,8 @@
       <c r="Q4" t="s">
         <v>29</v>
       </c>
-      <c r="R4" t="s">
-        <v>26</v>
+      <c r="R4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -888,7 +903,7 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -906,28 +921,28 @@
         <v>33</v>
       </c>
       <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>25</v>
       </c>
       <c r="K5" t="s">
         <v>26</v>
       </c>
       <c r="L5">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="M5">
-        <v>588146</v>
+        <v>595396</v>
       </c>
       <c r="N5" t="s">
         <v>27</v>
       </c>
       <c r="O5">
-        <v>67.37</v>
+        <v>11.66</v>
       </c>
       <c r="P5" t="s">
         <v>36</v>
@@ -935,8 +950,8 @@
       <c r="Q5" t="s">
         <v>29</v>
       </c>
-      <c r="R5" t="s">
-        <v>26</v>
+      <c r="R5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -944,7 +959,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -964,35 +979,35 @@
       <c r="H6">
         <v>7</v>
       </c>
-      <c r="I6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" t="s">
         <v>25</v>
       </c>
       <c r="K6" t="s">
         <v>26</v>
       </c>
       <c r="L6">
-        <v>46241</v>
+        <v>46210</v>
       </c>
       <c r="M6">
-        <v>603017</v>
+        <v>588146</v>
       </c>
       <c r="N6" t="s">
         <v>27</v>
       </c>
       <c r="O6">
-        <v>1.89</v>
+        <v>67.37</v>
       </c>
       <c r="P6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="s">
         <v>29</v>
       </c>
-      <c r="R6" t="e">
-        <v>#N/A</v>
+      <c r="R6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1000,7 +1015,7 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -1018,28 +1033,28 @@
         <v>33</v>
       </c>
       <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>25</v>
       </c>
       <c r="K7" t="s">
         <v>26</v>
       </c>
       <c r="L7">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="M7">
-        <v>601944</v>
+        <v>603017</v>
       </c>
       <c r="N7" t="s">
         <v>27</v>
       </c>
       <c r="O7">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="P7" t="s">
         <v>36</v>
@@ -1047,8 +1062,8 @@
       <c r="Q7" t="s">
         <v>29</v>
       </c>
-      <c r="R7" t="s">
-        <v>26</v>
+      <c r="R7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1056,7 +1071,7 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -1071,31 +1086,31 @@
         <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
         <v>25</v>
       </c>
       <c r="K8" t="s">
         <v>26</v>
       </c>
       <c r="L8">
-        <v>46218</v>
+        <v>46240</v>
       </c>
       <c r="M8">
-        <v>591481</v>
+        <v>601944</v>
       </c>
       <c r="N8" t="s">
         <v>27</v>
       </c>
       <c r="O8">
-        <v>10</v>
+        <v>1.96</v>
       </c>
       <c r="P8" t="s">
         <v>36</v>
@@ -1103,8 +1118,8 @@
       <c r="Q8" t="s">
         <v>29</v>
       </c>
-      <c r="R8" t="s">
-        <v>26</v>
+      <c r="R8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1112,7 +1127,7 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -1127,40 +1142,40 @@
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" t="s">
         <v>25</v>
       </c>
       <c r="K9" t="s">
         <v>26</v>
       </c>
       <c r="L9">
-        <v>46238</v>
+        <v>46218</v>
       </c>
       <c r="M9">
-        <v>601025</v>
+        <v>591481</v>
       </c>
       <c r="N9" t="s">
         <v>27</v>
       </c>
       <c r="O9">
-        <v>41.62</v>
+        <v>10</v>
       </c>
       <c r="P9" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="s">
         <v>29</v>
       </c>
-      <c r="R9" t="s">
-        <v>26</v>
+      <c r="R9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1168,7 +1183,7 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -1183,40 +1198,40 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>25</v>
       </c>
       <c r="K10" t="s">
         <v>26</v>
       </c>
       <c r="L10">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="M10">
-        <v>601583</v>
+        <v>601025</v>
       </c>
       <c r="N10" t="s">
         <v>27</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>41.62</v>
       </c>
       <c r="P10" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="s">
         <v>29</v>
       </c>
-      <c r="R10" t="s">
-        <v>26</v>
+      <c r="R10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1224,7 +1239,7 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -1239,40 +1254,40 @@
         <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H11">
-        <v>16</v>
-      </c>
-      <c r="I11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" t="s">
         <v>25</v>
       </c>
       <c r="K11" t="s">
         <v>26</v>
       </c>
       <c r="L11">
-        <v>46219</v>
+        <v>46237</v>
       </c>
       <c r="M11">
-        <v>594789</v>
+        <v>601583</v>
       </c>
       <c r="N11" t="s">
         <v>27</v>
       </c>
       <c r="O11">
-        <v>10.75</v>
+        <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q11" t="s">
         <v>29</v>
       </c>
-      <c r="R11" t="s">
-        <v>26</v>
+      <c r="R11">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1280,7 +1295,7 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -1298,37 +1313,37 @@
         <v>33</v>
       </c>
       <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" t="s">
         <v>25</v>
       </c>
       <c r="K12" t="s">
         <v>26</v>
       </c>
       <c r="L12">
-        <v>46244</v>
+        <v>46219</v>
       </c>
       <c r="M12">
-        <v>603608</v>
+        <v>594789</v>
       </c>
       <c r="N12" t="s">
         <v>27</v>
       </c>
       <c r="O12">
-        <v>6.94</v>
+        <v>10.75</v>
       </c>
       <c r="P12" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q12" t="s">
         <v>29</v>
       </c>
-      <c r="R12" t="e">
-        <v>#N/A</v>
+      <c r="R12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -1336,7 +1351,7 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -1351,31 +1366,31 @@
         <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H13">
-        <v>11</v>
-      </c>
-      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" t="s">
         <v>25</v>
       </c>
       <c r="K13" t="s">
         <v>26</v>
       </c>
       <c r="L13">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="M13">
-        <v>604194</v>
+        <v>605244</v>
       </c>
       <c r="N13" t="s">
         <v>27</v>
       </c>
       <c r="O13">
-        <v>2.98</v>
+        <v>91.5</v>
       </c>
       <c r="P13" t="s">
         <v>28</v>
@@ -1392,10 +1407,10 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
@@ -1412,26 +1427,26 @@
       <c r="H14">
         <v>10</v>
       </c>
-      <c r="I14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" s="1" t="s">
+      <c r="I14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" t="s">
         <v>25</v>
       </c>
       <c r="K14" t="s">
         <v>26</v>
       </c>
       <c r="L14">
-        <v>46213</v>
+        <v>46244</v>
       </c>
       <c r="M14">
-        <v>589870</v>
+        <v>603608</v>
       </c>
       <c r="N14" t="s">
         <v>27</v>
       </c>
       <c r="O14">
-        <v>27.46</v>
+        <v>8.77</v>
       </c>
       <c r="P14" t="s">
         <v>36</v>
@@ -1439,8 +1454,8 @@
       <c r="Q14" t="s">
         <v>29</v>
       </c>
-      <c r="R14" t="s">
-        <v>26</v>
+      <c r="R14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -1448,7 +1463,7 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -1463,31 +1478,31 @@
         <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H15">
-        <v>28</v>
-      </c>
-      <c r="I15" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" t="s">
         <v>25</v>
       </c>
       <c r="K15" t="s">
         <v>26</v>
       </c>
       <c r="L15">
-        <v>46231</v>
+        <v>46245</v>
       </c>
       <c r="M15">
-        <v>598334</v>
+        <v>604194</v>
       </c>
       <c r="N15" t="s">
         <v>27</v>
       </c>
       <c r="O15">
-        <v>9.7899999999999991</v>
+        <v>2.98</v>
       </c>
       <c r="P15" t="s">
         <v>36</v>
@@ -1495,8 +1510,8 @@
       <c r="Q15" t="s">
         <v>29</v>
       </c>
-      <c r="R15" t="s">
-        <v>26</v>
+      <c r="R15">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -1504,10 +1519,10 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -1519,31 +1534,31 @@
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H16">
-        <v>20</v>
-      </c>
-      <c r="I16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>25</v>
       </c>
       <c r="K16" t="s">
         <v>26</v>
       </c>
       <c r="L16">
-        <v>46223</v>
+        <v>46213</v>
       </c>
       <c r="M16">
-        <v>594209</v>
+        <v>589870</v>
       </c>
       <c r="N16" t="s">
         <v>27</v>
       </c>
       <c r="O16">
-        <v>41.75</v>
+        <v>27.46</v>
       </c>
       <c r="P16" t="s">
         <v>36</v>
@@ -1551,8 +1566,8 @@
       <c r="Q16" t="s">
         <v>29</v>
       </c>
-      <c r="R16" t="s">
-        <v>26</v>
+      <c r="R16">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1560,7 +1575,7 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
         <v>19</v>
@@ -1575,15 +1590,15 @@
         <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H17">
         <v>28</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" t="s">
         <v>25</v>
       </c>
       <c r="K17" t="s">
@@ -1593,13 +1608,13 @@
         <v>46231</v>
       </c>
       <c r="M17">
-        <v>598353</v>
+        <v>598334</v>
       </c>
       <c r="N17" t="s">
         <v>27</v>
       </c>
       <c r="O17">
-        <v>6.9</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="P17" t="s">
         <v>36</v>
@@ -1607,8 +1622,8 @@
       <c r="Q17" t="s">
         <v>29</v>
       </c>
-      <c r="R17" t="s">
-        <v>26</v>
+      <c r="R17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1616,7 +1631,7 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
@@ -1631,40 +1646,40 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H18">
-        <v>2</v>
-      </c>
-      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>25</v>
       </c>
       <c r="K18" t="s">
         <v>26</v>
       </c>
       <c r="L18">
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="M18">
-        <v>585567</v>
+        <v>594209</v>
       </c>
       <c r="N18" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="O18">
-        <v>1.41</v>
+        <v>41.75</v>
       </c>
       <c r="P18" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q18" t="s">
-        <v>94</v>
-      </c>
-      <c r="R18" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1672,7 +1687,7 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
@@ -1687,40 +1702,40 @@
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="H19">
-        <v>2</v>
-      </c>
-      <c r="I19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" t="s">
         <v>25</v>
       </c>
       <c r="K19" t="s">
         <v>26</v>
       </c>
       <c r="L19">
-        <v>46205</v>
+        <v>46231</v>
       </c>
       <c r="M19">
-        <v>585435</v>
+        <v>598353</v>
       </c>
       <c r="N19" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="O19">
-        <v>34.979999999999997</v>
+        <v>6.9</v>
       </c>
       <c r="P19" t="s">
         <v>36</v>
       </c>
       <c r="Q19" t="s">
-        <v>95</v>
-      </c>
-      <c r="R19" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1728,7 +1743,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -1743,40 +1758,40 @@
         <v>22</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="H20">
-        <v>6</v>
-      </c>
-      <c r="I20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>25</v>
       </c>
       <c r="K20" t="s">
         <v>26</v>
       </c>
       <c r="L20">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="M20">
-        <v>587363</v>
+        <v>585567</v>
       </c>
       <c r="N20" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O20">
-        <v>7.85</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q20" t="s">
-        <v>29</v>
-      </c>
-      <c r="R20" t="s">
-        <v>26</v>
+        <v>94</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -1784,7 +1799,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -1799,15 +1814,15 @@
         <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H21">
         <v>2</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" t="s">
         <v>25</v>
       </c>
       <c r="K21" t="s">
@@ -1817,22 +1832,22 @@
         <v>46205</v>
       </c>
       <c r="M21">
-        <v>589815</v>
+        <v>585435</v>
       </c>
       <c r="N21" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="O21">
-        <v>30.92</v>
+        <v>34.979999999999997</v>
       </c>
       <c r="P21" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="Q21" t="s">
-        <v>29</v>
-      </c>
-      <c r="R21" t="s">
-        <v>26</v>
+        <v>95</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -1840,7 +1855,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
@@ -1855,31 +1870,31 @@
         <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H22">
-        <v>7</v>
-      </c>
-      <c r="I22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" t="s">
         <v>25</v>
       </c>
       <c r="K22" t="s">
         <v>26</v>
       </c>
       <c r="L22">
-        <v>46241</v>
+        <v>46209</v>
       </c>
       <c r="M22">
-        <v>602969</v>
+        <v>587363</v>
       </c>
       <c r="N22" t="s">
         <v>27</v>
       </c>
       <c r="O22">
-        <v>6.12</v>
+        <v>7.85</v>
       </c>
       <c r="P22" t="s">
         <v>36</v>
@@ -1887,8 +1902,8 @@
       <c r="Q22" t="s">
         <v>29</v>
       </c>
-      <c r="R22" t="s">
-        <v>26</v>
+      <c r="R22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -1896,7 +1911,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
@@ -1911,40 +1926,40 @@
         <v>22</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H23">
-        <v>21</v>
-      </c>
-      <c r="I23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>25</v>
       </c>
       <c r="K23" t="s">
         <v>26</v>
       </c>
       <c r="L23">
-        <v>46224</v>
+        <v>46205</v>
       </c>
       <c r="M23">
-        <v>593210</v>
+        <v>589815</v>
       </c>
       <c r="N23" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>30.92</v>
       </c>
       <c r="P23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Q23" t="s">
-        <v>96</v>
-      </c>
-      <c r="R23" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -1952,7 +1967,7 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -1970,28 +1985,28 @@
         <v>44</v>
       </c>
       <c r="H24">
-        <v>5</v>
-      </c>
-      <c r="I24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>25</v>
       </c>
       <c r="K24" t="s">
         <v>26</v>
       </c>
       <c r="L24">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="M24">
-        <v>601537</v>
+        <v>602969</v>
       </c>
       <c r="N24" t="s">
         <v>27</v>
       </c>
       <c r="O24">
-        <v>4.63</v>
+        <v>6.12</v>
       </c>
       <c r="P24" t="s">
         <v>36</v>
@@ -1999,8 +2014,8 @@
       <c r="Q24" t="s">
         <v>29</v>
       </c>
-      <c r="R24" t="s">
-        <v>26</v>
+      <c r="R24">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2008,7 +2023,7 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -2026,37 +2041,37 @@
         <v>33</v>
       </c>
       <c r="H25">
-        <v>8</v>
-      </c>
-      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" t="s">
         <v>25</v>
       </c>
       <c r="K25" t="s">
         <v>26</v>
       </c>
       <c r="L25">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="M25">
-        <v>588663</v>
+        <v>593210</v>
       </c>
       <c r="N25" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O25">
-        <v>35.78</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="s">
         <v>56</v>
       </c>
       <c r="Q25" t="s">
-        <v>29</v>
-      </c>
-      <c r="R25" t="s">
-        <v>26</v>
+        <v>96</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -2064,7 +2079,7 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
@@ -2079,31 +2094,31 @@
         <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H26">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>34</v>
-      </c>
-      <c r="J26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" t="s">
         <v>25</v>
       </c>
       <c r="K26" t="s">
         <v>26</v>
       </c>
       <c r="L26">
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="M26">
-        <v>591629</v>
+        <v>601537</v>
       </c>
       <c r="N26" t="s">
         <v>27</v>
       </c>
       <c r="O26">
-        <v>10.44</v>
+        <v>4.63</v>
       </c>
       <c r="P26" t="s">
         <v>36</v>
@@ -2111,8 +2126,8 @@
       <c r="Q26" t="s">
         <v>29</v>
       </c>
-      <c r="R26" t="s">
-        <v>26</v>
+      <c r="R26">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -2120,7 +2135,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -2138,37 +2153,149 @@
         <v>33</v>
       </c>
       <c r="H27">
-        <v>24</v>
-      </c>
-      <c r="I27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>25</v>
       </c>
       <c r="K27" t="s">
         <v>26</v>
       </c>
       <c r="L27">
-        <v>46227</v>
+        <v>46211</v>
       </c>
       <c r="M27">
-        <v>582148</v>
+        <v>588663</v>
       </c>
       <c r="N27" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="O27">
-        <v>7.87</v>
+        <v>35.78</v>
       </c>
       <c r="P27" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="Q27" t="s">
         <v>29</v>
       </c>
-      <c r="R27" t="s">
+      <c r="R27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" t="s">
         <v>26</v>
+      </c>
+      <c r="L28">
+        <v>46218</v>
+      </c>
+      <c r="M28">
+        <v>591629</v>
+      </c>
+      <c r="N28" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28">
+        <v>10.44</v>
+      </c>
+      <c r="P28" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>29</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29">
+        <v>24</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J29" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29">
+        <v>46227</v>
+      </c>
+      <c r="M29">
+        <v>582148</v>
+      </c>
+      <c r="N29" t="s">
+        <v>60</v>
+      </c>
+      <c r="O29">
+        <v>7.87</v>
+      </c>
+      <c r="P29" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>29</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2424,31 +2551,31 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>71.608999999999995</v>
+        <v>97.844999999999999</v>
       </c>
       <c r="E7">
-        <v>62.838799999998997</v>
+        <v>112.4224</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I7">
-        <v>0.9</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="J7">
-        <v>1.5333333333333334</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L7">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2465,28 +2592,28 @@
         <v>86</v>
       </c>
       <c r="E8">
-        <v>75.433699999998993</v>
+        <v>116.89269999999999</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I8">
-        <v>0.55000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="J8">
-        <v>0.53333333333333333</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2503,28 +2630,28 @@
         <v>86</v>
       </c>
       <c r="E9">
-        <v>126.43339999999999</v>
+        <v>234.36929999999998</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I9">
-        <v>0.25</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J9">
-        <v>0.9</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L9">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C6DE12-E055-4BF8-9745-5229D892F594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70880C88-20CA-49E6-9A81-6A075DDE57AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="103">
   <si>
     <t>Usuário</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>LITORAL FRUTOS DO MAR, INDUSTRIA E COMERCIO DE ALIMENTOS LTD</t>
+  </si>
+  <si>
+    <t>DANIELLE CASTELO MARTINS MACIEL</t>
   </si>
 </sst>
 </file>
@@ -668,10 +671,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -696,10 +700,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -708,7 +712,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -752,10 +756,10 @@
       <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
       <c r="J2" t="s">
@@ -764,7 +768,7 @@
       <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>46245</v>
       </c>
       <c r="M2">
@@ -777,7 +781,7 @@
         <v>8.3699999999999992</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="Q2" t="s">
         <v>29</v>
@@ -808,10 +812,10 @@
       <c r="G3" t="s">
         <v>100</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>13</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>24</v>
       </c>
       <c r="J3" t="s">
@@ -820,7 +824,7 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>46247</v>
       </c>
       <c r="M3">
@@ -844,10 +848,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -856,19 +860,19 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4">
-        <v>28</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
@@ -876,26 +880,26 @@
       <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="L4">
-        <v>46231</v>
+      <c r="L4" s="1">
+        <v>46248</v>
       </c>
       <c r="M4">
-        <v>593213</v>
+        <v>606392</v>
       </c>
       <c r="N4" t="s">
         <v>27</v>
       </c>
       <c r="O4">
-        <v>3.66</v>
+        <v>4.55</v>
       </c>
       <c r="P4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="s">
         <v>29</v>
       </c>
-      <c r="R4">
-        <v>1</v>
+      <c r="R4" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -903,7 +907,7 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -920,10 +924,10 @@
       <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="H5">
-        <v>22</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="H5" s="1">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
         <v>34</v>
       </c>
       <c r="J5" t="s">
@@ -932,17 +936,17 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5">
-        <v>46225</v>
+      <c r="L5" s="1">
+        <v>46231</v>
       </c>
       <c r="M5">
-        <v>595396</v>
+        <v>593213</v>
       </c>
       <c r="N5" t="s">
         <v>27</v>
       </c>
       <c r="O5">
-        <v>11.66</v>
+        <v>3.66</v>
       </c>
       <c r="P5" t="s">
         <v>36</v>
@@ -950,8 +954,8 @@
       <c r="Q5" t="s">
         <v>29</v>
       </c>
-      <c r="R5">
-        <v>1</v>
+      <c r="R5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -959,7 +963,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -976,10 +980,10 @@
       <c r="G6" t="s">
         <v>33</v>
       </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="H6" s="1">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
         <v>34</v>
       </c>
       <c r="J6" t="s">
@@ -988,17 +992,17 @@
       <c r="K6" t="s">
         <v>26</v>
       </c>
-      <c r="L6">
-        <v>46210</v>
+      <c r="L6" s="1">
+        <v>46225</v>
       </c>
       <c r="M6">
-        <v>588146</v>
+        <v>595396</v>
       </c>
       <c r="N6" t="s">
         <v>27</v>
       </c>
       <c r="O6">
-        <v>67.37</v>
+        <v>11.66</v>
       </c>
       <c r="P6" t="s">
         <v>36</v>
@@ -1006,8 +1010,8 @@
       <c r="Q6" t="s">
         <v>29</v>
       </c>
-      <c r="R6">
-        <v>1</v>
+      <c r="R6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1015,7 +1019,7 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -1032,11 +1036,11 @@
       <c r="G7" t="s">
         <v>33</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>7</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>24</v>
+      <c r="I7" t="s">
+        <v>34</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
@@ -1044,17 +1048,17 @@
       <c r="K7" t="s">
         <v>26</v>
       </c>
-      <c r="L7">
-        <v>46241</v>
+      <c r="L7" s="1">
+        <v>46210</v>
       </c>
       <c r="M7">
-        <v>603017</v>
+        <v>588146</v>
       </c>
       <c r="N7" t="s">
         <v>27</v>
       </c>
       <c r="O7">
-        <v>1.89</v>
+        <v>67.37</v>
       </c>
       <c r="P7" t="s">
         <v>36</v>
@@ -1062,8 +1066,8 @@
       <c r="Q7" t="s">
         <v>29</v>
       </c>
-      <c r="R7">
-        <v>1</v>
+      <c r="R7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1071,7 +1075,7 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -1088,10 +1092,10 @@
       <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8" s="1" t="s">
+      <c r="H8" s="1">
+        <v>7</v>
+      </c>
+      <c r="I8" t="s">
         <v>24</v>
       </c>
       <c r="J8" t="s">
@@ -1100,17 +1104,17 @@
       <c r="K8" t="s">
         <v>26</v>
       </c>
-      <c r="L8">
-        <v>46240</v>
+      <c r="L8" s="1">
+        <v>46241</v>
       </c>
       <c r="M8">
-        <v>601944</v>
+        <v>603017</v>
       </c>
       <c r="N8" t="s">
         <v>27</v>
       </c>
       <c r="O8">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="P8" t="s">
         <v>36</v>
@@ -1118,8 +1122,8 @@
       <c r="Q8" t="s">
         <v>29</v>
       </c>
-      <c r="R8">
-        <v>1</v>
+      <c r="R8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1127,7 +1131,7 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -1142,13 +1146,13 @@
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9">
-        <v>15</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="H9" s="1">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
       </c>
       <c r="J9" t="s">
         <v>25</v>
@@ -1156,17 +1160,17 @@
       <c r="K9" t="s">
         <v>26</v>
       </c>
-      <c r="L9">
-        <v>46218</v>
+      <c r="L9" s="1">
+        <v>46240</v>
       </c>
       <c r="M9">
-        <v>591481</v>
+        <v>601944</v>
       </c>
       <c r="N9" t="s">
         <v>27</v>
       </c>
       <c r="O9">
-        <v>10</v>
+        <v>1.96</v>
       </c>
       <c r="P9" t="s">
         <v>36</v>
@@ -1174,8 +1178,8 @@
       <c r="Q9" t="s">
         <v>29</v>
       </c>
-      <c r="R9">
-        <v>1</v>
+      <c r="R9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1183,7 +1187,7 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -1198,13 +1202,13 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
+      </c>
+      <c r="H10" s="1">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
       </c>
       <c r="J10" t="s">
         <v>25</v>
@@ -1212,17 +1216,17 @@
       <c r="K10" t="s">
         <v>26</v>
       </c>
-      <c r="L10">
-        <v>46238</v>
+      <c r="L10" s="1">
+        <v>46218</v>
       </c>
       <c r="M10">
-        <v>601025</v>
+        <v>591481</v>
       </c>
       <c r="N10" t="s">
         <v>27</v>
       </c>
       <c r="O10">
-        <v>41.62</v>
+        <v>10</v>
       </c>
       <c r="P10" t="s">
         <v>36</v>
@@ -1230,8 +1234,8 @@
       <c r="Q10" t="s">
         <v>29</v>
       </c>
-      <c r="R10">
-        <v>1</v>
+      <c r="R10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1239,7 +1243,7 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -1254,12 +1258,12 @@
         <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
         <v>24</v>
       </c>
       <c r="J11" t="s">
@@ -1268,26 +1272,26 @@
       <c r="K11" t="s">
         <v>26</v>
       </c>
-      <c r="L11">
-        <v>46237</v>
+      <c r="L11" s="1">
+        <v>46238</v>
       </c>
       <c r="M11">
-        <v>601583</v>
+        <v>601025</v>
       </c>
       <c r="N11" t="s">
         <v>27</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>41.62</v>
       </c>
       <c r="P11" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="s">
         <v>29</v>
       </c>
-      <c r="R11">
-        <v>1</v>
+      <c r="R11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1295,7 +1299,7 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -1310,13 +1314,13 @@
         <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12">
-        <v>16</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3</v>
+      </c>
+      <c r="I12" t="s">
+        <v>24</v>
       </c>
       <c r="J12" t="s">
         <v>25</v>
@@ -1324,26 +1328,26 @@
       <c r="K12" t="s">
         <v>26</v>
       </c>
-      <c r="L12">
-        <v>46219</v>
+      <c r="L12" s="1">
+        <v>46237</v>
       </c>
       <c r="M12">
-        <v>594789</v>
+        <v>601583</v>
       </c>
       <c r="N12" t="s">
         <v>27</v>
       </c>
       <c r="O12">
-        <v>10.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q12" t="s">
         <v>29</v>
       </c>
-      <c r="R12">
-        <v>1</v>
+      <c r="R12" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -1351,7 +1355,7 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -1366,13 +1370,13 @@
         <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13">
-        <v>13</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
+      </c>
+      <c r="H13" s="1">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>34</v>
       </c>
       <c r="J13" t="s">
         <v>25</v>
@@ -1380,26 +1384,26 @@
       <c r="K13" t="s">
         <v>26</v>
       </c>
-      <c r="L13">
-        <v>46247</v>
+      <c r="L13" s="1">
+        <v>46219</v>
       </c>
       <c r="M13">
-        <v>605244</v>
+        <v>594789</v>
       </c>
       <c r="N13" t="s">
         <v>27</v>
       </c>
       <c r="O13">
-        <v>91.5</v>
+        <v>10.75</v>
       </c>
       <c r="P13" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q13" t="s">
         <v>29</v>
       </c>
-      <c r="R13" t="e">
-        <v>#N/A</v>
+      <c r="R13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1407,7 +1411,7 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -1422,12 +1426,12 @@
         <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14">
-        <v>10</v>
-      </c>
-      <c r="I14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="1">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
         <v>24</v>
       </c>
       <c r="J14" t="s">
@@ -1436,26 +1440,26 @@
       <c r="K14" t="s">
         <v>26</v>
       </c>
-      <c r="L14">
-        <v>46244</v>
+      <c r="L14" s="1">
+        <v>46247</v>
       </c>
       <c r="M14">
-        <v>603608</v>
+        <v>605244</v>
       </c>
       <c r="N14" t="s">
         <v>27</v>
       </c>
       <c r="O14">
-        <v>8.77</v>
+        <v>91.5</v>
       </c>
       <c r="P14" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q14" t="s">
         <v>29</v>
       </c>
-      <c r="R14">
-        <v>1</v>
+      <c r="R14" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -1463,7 +1467,7 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -1480,10 +1484,10 @@
       <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H15">
-        <v>11</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
         <v>24</v>
       </c>
       <c r="J15" t="s">
@@ -1492,17 +1496,17 @@
       <c r="K15" t="s">
         <v>26</v>
       </c>
-      <c r="L15">
-        <v>46245</v>
+      <c r="L15" s="1">
+        <v>46244</v>
       </c>
       <c r="M15">
-        <v>604194</v>
+        <v>603608</v>
       </c>
       <c r="N15" t="s">
         <v>27</v>
       </c>
       <c r="O15">
-        <v>2.98</v>
+        <v>8.77</v>
       </c>
       <c r="P15" t="s">
         <v>36</v>
@@ -1510,8 +1514,8 @@
       <c r="Q15" t="s">
         <v>29</v>
       </c>
-      <c r="R15">
-        <v>1</v>
+      <c r="R15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -1519,10 +1523,10 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -1536,11 +1540,11 @@
       <c r="G16" t="s">
         <v>33</v>
       </c>
-      <c r="H16">
-        <v>10</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>34</v>
+      <c r="H16" s="1">
+        <v>11</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
       </c>
       <c r="J16" t="s">
         <v>25</v>
@@ -1548,17 +1552,17 @@
       <c r="K16" t="s">
         <v>26</v>
       </c>
-      <c r="L16">
-        <v>46213</v>
+      <c r="L16" s="1">
+        <v>46245</v>
       </c>
       <c r="M16">
-        <v>589870</v>
+        <v>604194</v>
       </c>
       <c r="N16" t="s">
         <v>27</v>
       </c>
       <c r="O16">
-        <v>27.46</v>
+        <v>2.98</v>
       </c>
       <c r="P16" t="s">
         <v>36</v>
@@ -1566,8 +1570,8 @@
       <c r="Q16" t="s">
         <v>29</v>
       </c>
-      <c r="R16">
-        <v>1</v>
+      <c r="R16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1575,10 +1579,10 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -1590,12 +1594,12 @@
         <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17">
-        <v>28</v>
-      </c>
-      <c r="I17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="1">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
         <v>34</v>
       </c>
       <c r="J17" t="s">
@@ -1604,17 +1608,17 @@
       <c r="K17" t="s">
         <v>26</v>
       </c>
-      <c r="L17">
-        <v>46231</v>
+      <c r="L17" s="1">
+        <v>46213</v>
       </c>
       <c r="M17">
-        <v>598334</v>
+        <v>589870</v>
       </c>
       <c r="N17" t="s">
         <v>27</v>
       </c>
       <c r="O17">
-        <v>9.7899999999999991</v>
+        <v>27.46</v>
       </c>
       <c r="P17" t="s">
         <v>36</v>
@@ -1622,8 +1626,8 @@
       <c r="Q17" t="s">
         <v>29</v>
       </c>
-      <c r="R17">
-        <v>1</v>
+      <c r="R17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1631,7 +1635,7 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
@@ -1648,10 +1652,10 @@
       <c r="G18" t="s">
         <v>44</v>
       </c>
-      <c r="H18">
-        <v>20</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="1">
+        <v>28</v>
+      </c>
+      <c r="I18" t="s">
         <v>34</v>
       </c>
       <c r="J18" t="s">
@@ -1660,17 +1664,17 @@
       <c r="K18" t="s">
         <v>26</v>
       </c>
-      <c r="L18">
-        <v>46223</v>
+      <c r="L18" s="1">
+        <v>46231</v>
       </c>
       <c r="M18">
-        <v>594209</v>
+        <v>598334</v>
       </c>
       <c r="N18" t="s">
         <v>27</v>
       </c>
       <c r="O18">
-        <v>41.75</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="P18" t="s">
         <v>36</v>
@@ -1678,8 +1682,8 @@
       <c r="Q18" t="s">
         <v>29</v>
       </c>
-      <c r="R18">
-        <v>1</v>
+      <c r="R18" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1687,7 +1691,7 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
@@ -1702,12 +1706,12 @@
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19">
-        <v>28</v>
-      </c>
-      <c r="I19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" t="s">
         <v>34</v>
       </c>
       <c r="J19" t="s">
@@ -1716,17 +1720,17 @@
       <c r="K19" t="s">
         <v>26</v>
       </c>
-      <c r="L19">
-        <v>46231</v>
+      <c r="L19" s="1">
+        <v>46223</v>
       </c>
       <c r="M19">
-        <v>598353</v>
+        <v>594209</v>
       </c>
       <c r="N19" t="s">
         <v>27</v>
       </c>
       <c r="O19">
-        <v>6.9</v>
+        <v>41.75</v>
       </c>
       <c r="P19" t="s">
         <v>36</v>
@@ -1734,8 +1738,8 @@
       <c r="Q19" t="s">
         <v>29</v>
       </c>
-      <c r="R19">
-        <v>1</v>
+      <c r="R19" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1743,7 +1747,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -1758,12 +1762,12 @@
         <v>22</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20">
-        <v>2</v>
-      </c>
-      <c r="I20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="1">
+        <v>28</v>
+      </c>
+      <c r="I20" t="s">
         <v>34</v>
       </c>
       <c r="J20" t="s">
@@ -1772,26 +1776,26 @@
       <c r="K20" t="s">
         <v>26</v>
       </c>
-      <c r="L20">
-        <v>46205</v>
+      <c r="L20" s="1">
+        <v>46231</v>
       </c>
       <c r="M20">
-        <v>585567</v>
+        <v>598353</v>
       </c>
       <c r="N20" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="O20">
-        <v>1.41</v>
+        <v>6.9</v>
       </c>
       <c r="P20" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q20" t="s">
-        <v>94</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="R20" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -1799,7 +1803,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -1816,10 +1820,10 @@
       <c r="G21" t="s">
         <v>55</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>2</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>34</v>
       </c>
       <c r="J21" t="s">
@@ -1828,26 +1832,26 @@
       <c r="K21" t="s">
         <v>26</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>46205</v>
       </c>
       <c r="M21">
-        <v>585435</v>
+        <v>585567</v>
       </c>
       <c r="N21" t="s">
         <v>45</v>
       </c>
       <c r="O21">
-        <v>34.979999999999997</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q21" t="s">
-        <v>95</v>
-      </c>
-      <c r="R21">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="R21" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -1855,7 +1859,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
@@ -1870,12 +1874,12 @@
         <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22">
-        <v>6</v>
-      </c>
-      <c r="I22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
         <v>34</v>
       </c>
       <c r="J22" t="s">
@@ -1884,26 +1888,26 @@
       <c r="K22" t="s">
         <v>26</v>
       </c>
-      <c r="L22">
-        <v>46209</v>
+      <c r="L22" s="1">
+        <v>46205</v>
       </c>
       <c r="M22">
-        <v>587363</v>
+        <v>585435</v>
       </c>
       <c r="N22" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O22">
-        <v>7.85</v>
+        <v>34.979999999999997</v>
       </c>
       <c r="P22" t="s">
         <v>36</v>
       </c>
       <c r="Q22" t="s">
-        <v>29</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
+        <v>95</v>
+      </c>
+      <c r="R22" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -1911,7 +1915,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
@@ -1926,12 +1930,12 @@
         <v>22</v>
       </c>
       <c r="G23" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23">
-        <v>2</v>
-      </c>
-      <c r="I23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="1">
+        <v>6</v>
+      </c>
+      <c r="I23" t="s">
         <v>34</v>
       </c>
       <c r="J23" t="s">
@@ -1940,26 +1944,26 @@
       <c r="K23" t="s">
         <v>26</v>
       </c>
-      <c r="L23">
-        <v>46205</v>
+      <c r="L23" s="1">
+        <v>46209</v>
       </c>
       <c r="M23">
-        <v>589815</v>
+        <v>587363</v>
       </c>
       <c r="N23" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="O23">
-        <v>30.92</v>
+        <v>7.85</v>
       </c>
       <c r="P23" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="Q23" t="s">
         <v>29</v>
       </c>
-      <c r="R23">
-        <v>1</v>
+      <c r="R23" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -1967,7 +1971,7 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -1984,11 +1988,11 @@
       <c r="G24" t="s">
         <v>44</v>
       </c>
-      <c r="H24">
-        <v>7</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>24</v>
+      <c r="H24" s="1">
+        <v>2</v>
+      </c>
+      <c r="I24" t="s">
+        <v>34</v>
       </c>
       <c r="J24" t="s">
         <v>25</v>
@@ -1996,26 +2000,26 @@
       <c r="K24" t="s">
         <v>26</v>
       </c>
-      <c r="L24">
-        <v>46241</v>
+      <c r="L24" s="1">
+        <v>46205</v>
       </c>
       <c r="M24">
-        <v>602969</v>
+        <v>589815</v>
       </c>
       <c r="N24" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O24">
-        <v>6.12</v>
+        <v>30.92</v>
       </c>
       <c r="P24" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="Q24" t="s">
         <v>29</v>
       </c>
-      <c r="R24">
-        <v>1</v>
+      <c r="R24" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2023,7 +2027,7 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -2038,13 +2042,13 @@
         <v>22</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25">
-        <v>21</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="H25" s="1">
+        <v>7</v>
+      </c>
+      <c r="I25" t="s">
+        <v>24</v>
       </c>
       <c r="J25" t="s">
         <v>25</v>
@@ -2052,26 +2056,26 @@
       <c r="K25" t="s">
         <v>26</v>
       </c>
-      <c r="L25">
-        <v>46224</v>
+      <c r="L25" s="1">
+        <v>46241</v>
       </c>
       <c r="M25">
-        <v>593210</v>
+        <v>602969</v>
       </c>
       <c r="N25" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>6.12</v>
       </c>
       <c r="P25" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q25" t="s">
-        <v>96</v>
-      </c>
-      <c r="R25">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="R25" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -2079,7 +2083,7 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
@@ -2094,13 +2098,13 @@
         <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26">
-        <v>5</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
+      </c>
+      <c r="H26" s="1">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s">
+        <v>34</v>
       </c>
       <c r="J26" t="s">
         <v>25</v>
@@ -2108,26 +2112,26 @@
       <c r="K26" t="s">
         <v>26</v>
       </c>
-      <c r="L26">
-        <v>46239</v>
+      <c r="L26" s="1">
+        <v>46224</v>
       </c>
       <c r="M26">
-        <v>601537</v>
+        <v>593210</v>
       </c>
       <c r="N26" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O26">
-        <v>4.63</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q26" t="s">
-        <v>29</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="R26" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -2135,7 +2139,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -2150,13 +2154,13 @@
         <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27">
-        <v>8</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5</v>
+      </c>
+      <c r="I27" t="s">
+        <v>24</v>
       </c>
       <c r="J27" t="s">
         <v>25</v>
@@ -2164,26 +2168,26 @@
       <c r="K27" t="s">
         <v>26</v>
       </c>
-      <c r="L27">
-        <v>46211</v>
+      <c r="L27" s="1">
+        <v>46239</v>
       </c>
       <c r="M27">
-        <v>588663</v>
+        <v>601537</v>
       </c>
       <c r="N27" t="s">
         <v>27</v>
       </c>
       <c r="O27">
-        <v>35.78</v>
+        <v>4.63</v>
       </c>
       <c r="P27" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q27" t="s">
         <v>29</v>
       </c>
-      <c r="R27">
-        <v>1</v>
+      <c r="R27" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -2191,7 +2195,7 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
@@ -2208,10 +2212,10 @@
       <c r="G28" t="s">
         <v>33</v>
       </c>
-      <c r="H28">
-        <v>15</v>
-      </c>
-      <c r="I28" s="1" t="s">
+      <c r="H28" s="1">
+        <v>8</v>
+      </c>
+      <c r="I28" t="s">
         <v>34</v>
       </c>
       <c r="J28" t="s">
@@ -2220,17 +2224,17 @@
       <c r="K28" t="s">
         <v>26</v>
       </c>
-      <c r="L28">
-        <v>46218</v>
+      <c r="L28" s="1">
+        <v>46211</v>
       </c>
       <c r="M28">
-        <v>591629</v>
+        <v>588663</v>
       </c>
       <c r="N28" t="s">
         <v>27</v>
       </c>
       <c r="O28">
-        <v>10.44</v>
+        <v>35.78</v>
       </c>
       <c r="P28" t="s">
         <v>36</v>
@@ -2238,8 +2242,8 @@
       <c r="Q28" t="s">
         <v>29</v>
       </c>
-      <c r="R28">
-        <v>1</v>
+      <c r="R28" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -2247,7 +2251,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
         <v>19</v>
@@ -2264,10 +2268,10 @@
       <c r="G29" t="s">
         <v>33</v>
       </c>
-      <c r="H29">
-        <v>24</v>
-      </c>
-      <c r="I29" s="1" t="s">
+      <c r="H29" s="1">
+        <v>15</v>
+      </c>
+      <c r="I29" t="s">
         <v>34</v>
       </c>
       <c r="J29" t="s">
@@ -2276,26 +2280,79 @@
       <c r="K29" t="s">
         <v>26</v>
       </c>
-      <c r="L29">
-        <v>46227</v>
+      <c r="L29" s="1">
+        <v>46218</v>
       </c>
       <c r="M29">
-        <v>582148</v>
+        <v>591629</v>
       </c>
       <c r="N29" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="O29">
-        <v>7.87</v>
+        <v>10.44</v>
       </c>
       <c r="P29" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="Q29" t="s">
         <v>29</v>
       </c>
-      <c r="R29">
-        <v>1</v>
+      <c r="R29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="1">
+        <v>24</v>
+      </c>
+      <c r="I30" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="1">
+        <v>46227</v>
+      </c>
+      <c r="M30">
+        <v>582148</v>
+      </c>
+      <c r="N30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O30">
+        <v>7.87</v>
+      </c>
+      <c r="P30" t="s">
+        <v>61</v>
+      </c>
+      <c r="R30" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2551,31 +2608,31 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>97.844999999999999</v>
+        <v>112.48399999999999</v>
       </c>
       <c r="E7">
-        <v>112.4224</v>
+        <v>159.7595</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G7">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H7">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I7">
-        <v>0.76666666666666672</v>
+        <v>0.7</v>
       </c>
       <c r="J7">
-        <v>1.3333333333333333</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="K7">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L7">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2592,28 +2649,28 @@
         <v>86</v>
       </c>
       <c r="E8">
-        <v>116.89269999999999</v>
+        <v>153.90360000000001</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I8">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J8">
-        <v>0.55555555555555558</v>
+        <v>0.6</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L8">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2630,28 +2687,28 @@
         <v>86</v>
       </c>
       <c r="E9">
-        <v>234.36929999999998</v>
+        <v>356.66750000000002</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G9">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I9">
-        <v>0.53333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="J9">
-        <v>0.9555555555555556</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="K9">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="L9">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70880C88-20CA-49E6-9A81-6A075DDE57AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66AC95C-CBC0-4A5C-B876-8DCCED8A1873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="105">
   <si>
     <t>Usuário</t>
   </si>
@@ -347,6 +347,12 @@
   </si>
   <si>
     <t>DANIELLE CASTELO MARTINS MACIEL</t>
+  </si>
+  <si>
+    <t>POSSUI USINA PROPRIA</t>
+  </si>
+  <si>
+    <t>CLARICE LUNARDI</t>
   </si>
 </sst>
 </file>
@@ -671,11 +677,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -697,10 +703,10 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -709,7 +715,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -736,10 +742,10 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
@@ -748,54 +754,54 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="1">
-        <v>11</v>
+      <c r="G2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L2" s="1">
-        <v>46245</v>
+        <v>46205</v>
       </c>
       <c r="M2">
-        <v>604128</v>
+        <v>585567</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O2">
-        <v>8.3699999999999992</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="s">
         <v>56</v>
       </c>
       <c r="Q2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" t="e">
-        <v>#N/A</v>
+        <v>94</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -804,54 +810,54 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="1">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="1">
-        <v>46247</v>
+        <v>46205</v>
       </c>
       <c r="M3">
-        <v>605287</v>
+        <v>585435</v>
       </c>
       <c r="N3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O3">
-        <v>61.58</v>
+        <v>34.979999999999997</v>
       </c>
       <c r="P3" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" t="e">
-        <v>#N/A</v>
+        <v>95</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -860,46 +866,46 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="1">
-        <v>46248</v>
+        <v>46205</v>
       </c>
       <c r="M4">
-        <v>606392</v>
+        <v>589815</v>
       </c>
       <c r="N4" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O4">
-        <v>4.55</v>
+        <v>30.92</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="s">
         <v>29</v>
       </c>
-      <c r="R4" t="e">
-        <v>#N/A</v>
+      <c r="R4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -907,7 +913,7 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -921,11 +927,11 @@
       <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="1">
-        <v>28</v>
+      <c r="H5">
+        <v>6</v>
       </c>
       <c r="I5" t="s">
         <v>34</v>
@@ -933,20 +939,20 @@
       <c r="J5" t="s">
         <v>25</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="1">
-        <v>46231</v>
+        <v>46209</v>
       </c>
       <c r="M5">
-        <v>593213</v>
+        <v>587363</v>
       </c>
       <c r="N5" t="s">
         <v>27</v>
       </c>
       <c r="O5">
-        <v>3.66</v>
+        <v>7.85</v>
       </c>
       <c r="P5" t="s">
         <v>36</v>
@@ -954,8 +960,8 @@
       <c r="Q5" t="s">
         <v>29</v>
       </c>
-      <c r="R5" t="s">
-        <v>26</v>
+      <c r="R5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -963,7 +969,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -977,11 +983,11 @@
       <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="1">
-        <v>22</v>
+      <c r="H6">
+        <v>7</v>
       </c>
       <c r="I6" t="s">
         <v>34</v>
@@ -989,20 +995,20 @@
       <c r="J6" t="s">
         <v>25</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L6" s="1">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="M6">
-        <v>595396</v>
+        <v>588146</v>
       </c>
       <c r="N6" t="s">
         <v>27</v>
       </c>
       <c r="O6">
-        <v>11.66</v>
+        <v>67.37</v>
       </c>
       <c r="P6" t="s">
         <v>36</v>
@@ -1010,8 +1016,8 @@
       <c r="Q6" t="s">
         <v>29</v>
       </c>
-      <c r="R6" t="s">
-        <v>26</v>
+      <c r="R6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1019,7 +1025,7 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -1033,11 +1039,11 @@
       <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="1">
-        <v>7</v>
+      <c r="H7">
+        <v>8</v>
       </c>
       <c r="I7" t="s">
         <v>34</v>
@@ -1045,20 +1051,20 @@
       <c r="J7" t="s">
         <v>25</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L7" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="M7">
-        <v>588146</v>
+        <v>588663</v>
       </c>
       <c r="N7" t="s">
         <v>27</v>
       </c>
       <c r="O7">
-        <v>67.37</v>
+        <v>35.78</v>
       </c>
       <c r="P7" t="s">
         <v>36</v>
@@ -1066,8 +1072,8 @@
       <c r="Q7" t="s">
         <v>29</v>
       </c>
-      <c r="R7" t="s">
-        <v>26</v>
+      <c r="R7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1075,10 +1081,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
@@ -1089,32 +1095,32 @@
       <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="1">
-        <v>7</v>
+      <c r="H8">
+        <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J8" t="s">
         <v>25</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="1">
-        <v>46241</v>
+        <v>46213</v>
       </c>
       <c r="M8">
-        <v>603017</v>
+        <v>589870</v>
       </c>
       <c r="N8" t="s">
         <v>27</v>
       </c>
       <c r="O8">
-        <v>1.89</v>
+        <v>27.46</v>
       </c>
       <c r="P8" t="s">
         <v>36</v>
@@ -1122,8 +1128,8 @@
       <c r="Q8" t="s">
         <v>29</v>
       </c>
-      <c r="R8" t="s">
-        <v>26</v>
+      <c r="R8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1131,7 +1137,7 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -1145,32 +1151,32 @@
       <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="1">
-        <v>6</v>
+      <c r="G9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J9" t="s">
         <v>25</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="1">
-        <v>46240</v>
+        <v>46218</v>
       </c>
       <c r="M9">
-        <v>601944</v>
+        <v>591481</v>
       </c>
       <c r="N9" t="s">
         <v>27</v>
       </c>
       <c r="O9">
-        <v>1.96</v>
+        <v>10</v>
       </c>
       <c r="P9" t="s">
         <v>36</v>
@@ -1178,8 +1184,8 @@
       <c r="Q9" t="s">
         <v>29</v>
       </c>
-      <c r="R9" t="s">
-        <v>26</v>
+      <c r="R9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1187,7 +1193,7 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -1201,10 +1207,10 @@
       <c r="F10" t="s">
         <v>22</v>
       </c>
-      <c r="G10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="G10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10">
         <v>15</v>
       </c>
       <c r="I10" t="s">
@@ -1213,20 +1219,20 @@
       <c r="J10" t="s">
         <v>25</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L10" s="1">
         <v>46218</v>
       </c>
       <c r="M10">
-        <v>591481</v>
+        <v>591629</v>
       </c>
       <c r="N10" t="s">
         <v>27</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <v>10.44</v>
       </c>
       <c r="P10" t="s">
         <v>36</v>
@@ -1234,8 +1240,8 @@
       <c r="Q10" t="s">
         <v>29</v>
       </c>
-      <c r="R10" t="s">
-        <v>26</v>
+      <c r="R10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1243,7 +1249,7 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -1257,32 +1263,32 @@
       <c r="F11" t="s">
         <v>22</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="1">
-        <v>4</v>
+      <c r="H11">
+        <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J11" t="s">
         <v>25</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L11" s="1">
-        <v>46238</v>
+        <v>46219</v>
       </c>
       <c r="M11">
-        <v>601025</v>
+        <v>594789</v>
       </c>
       <c r="N11" t="s">
         <v>27</v>
       </c>
       <c r="O11">
-        <v>41.62</v>
+        <v>10.75</v>
       </c>
       <c r="P11" t="s">
         <v>36</v>
@@ -1290,8 +1296,8 @@
       <c r="Q11" t="s">
         <v>29</v>
       </c>
-      <c r="R11" t="s">
-        <v>26</v>
+      <c r="R11">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1299,7 +1305,7 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -1313,41 +1319,41 @@
       <c r="F12" t="s">
         <v>22</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="1">
-        <v>3</v>
+      <c r="H12">
+        <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J12" t="s">
         <v>25</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="1">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="M12">
-        <v>601583</v>
+        <v>594209</v>
       </c>
       <c r="N12" t="s">
         <v>27</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>41.75</v>
       </c>
       <c r="P12" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q12" t="s">
         <v>29</v>
       </c>
-      <c r="R12" t="s">
-        <v>26</v>
+      <c r="R12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -1355,7 +1361,7 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -1369,11 +1375,11 @@
       <c r="F13" t="s">
         <v>22</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="1">
-        <v>16</v>
+      <c r="H13">
+        <v>21</v>
       </c>
       <c r="I13" t="s">
         <v>34</v>
@@ -1381,29 +1387,29 @@
       <c r="J13" t="s">
         <v>25</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L13" s="1">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="M13">
-        <v>594789</v>
+        <v>593210</v>
       </c>
       <c r="N13" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O13">
-        <v>10.75</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q13" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" t="s">
-        <v>26</v>
+        <v>96</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1411,7 +1417,7 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -1425,41 +1431,41 @@
       <c r="F14" t="s">
         <v>22</v>
       </c>
-      <c r="G14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="1">
-        <v>13</v>
+      <c r="G14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14">
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J14" t="s">
         <v>25</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="1">
-        <v>46247</v>
+        <v>46225</v>
       </c>
       <c r="M14">
-        <v>605244</v>
+        <v>595396</v>
       </c>
       <c r="N14" t="s">
         <v>27</v>
       </c>
       <c r="O14">
-        <v>91.5</v>
+        <v>11.66</v>
       </c>
       <c r="P14" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q14" t="s">
         <v>29</v>
       </c>
-      <c r="R14" t="e">
-        <v>#N/A</v>
+      <c r="R14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -1467,7 +1473,7 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -1481,41 +1487,41 @@
       <c r="F15" t="s">
         <v>22</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="1">
-        <v>10</v>
+      <c r="H15">
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J15" t="s">
         <v>25</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L15" s="1">
-        <v>46244</v>
+        <v>46227</v>
       </c>
       <c r="M15">
-        <v>603608</v>
+        <v>582148</v>
       </c>
       <c r="N15" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O15">
-        <v>8.77</v>
+        <v>7.87</v>
       </c>
       <c r="P15" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="Q15" t="s">
         <v>29</v>
       </c>
-      <c r="R15" t="s">
-        <v>26</v>
+      <c r="R15">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -1523,7 +1529,7 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -1537,32 +1543,32 @@
       <c r="F16" t="s">
         <v>22</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="1">
-        <v>11</v>
+      <c r="H16">
+        <v>28</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
         <v>25</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L16" s="1">
-        <v>46245</v>
+        <v>46231</v>
       </c>
       <c r="M16">
-        <v>604194</v>
+        <v>593213</v>
       </c>
       <c r="N16" t="s">
         <v>27</v>
       </c>
       <c r="O16">
-        <v>2.98</v>
+        <v>3.66</v>
       </c>
       <c r="P16" t="s">
         <v>36</v>
@@ -1570,8 +1576,8 @@
       <c r="Q16" t="s">
         <v>29</v>
       </c>
-      <c r="R16" t="s">
-        <v>26</v>
+      <c r="R16">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1579,10 +1585,10 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -1593,11 +1599,11 @@
       <c r="F17" t="s">
         <v>22</v>
       </c>
-      <c r="G17" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="1">
-        <v>10</v>
+      <c r="G17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17">
+        <v>28</v>
       </c>
       <c r="I17" t="s">
         <v>34</v>
@@ -1605,29 +1611,29 @@
       <c r="J17" t="s">
         <v>25</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L17" s="1">
-        <v>46213</v>
+        <v>46231</v>
       </c>
       <c r="M17">
-        <v>589870</v>
+        <v>598334</v>
       </c>
       <c r="N17" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O17">
-        <v>27.46</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="P17" t="s">
         <v>36</v>
       </c>
       <c r="Q17" t="s">
-        <v>29</v>
-      </c>
-      <c r="R17" t="s">
-        <v>26</v>
+        <v>103</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1635,7 +1641,7 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
@@ -1649,10 +1655,10 @@
       <c r="F18" t="s">
         <v>22</v>
       </c>
-      <c r="G18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="G18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18">
         <v>28</v>
       </c>
       <c r="I18" t="s">
@@ -1661,20 +1667,20 @@
       <c r="J18" t="s">
         <v>25</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="1">
         <v>46231</v>
       </c>
       <c r="M18">
-        <v>598334</v>
+        <v>598353</v>
       </c>
       <c r="N18" t="s">
         <v>27</v>
       </c>
       <c r="O18">
-        <v>9.7899999999999991</v>
+        <v>6.9</v>
       </c>
       <c r="P18" t="s">
         <v>36</v>
@@ -1682,8 +1688,8 @@
       <c r="Q18" t="s">
         <v>29</v>
       </c>
-      <c r="R18" t="s">
-        <v>26</v>
+      <c r="R18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1691,7 +1697,7 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
@@ -1705,41 +1711,41 @@
       <c r="F19" t="s">
         <v>22</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="1">
-        <v>20</v>
+      <c r="H19">
+        <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J19" t="s">
         <v>25</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="1">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="M19">
-        <v>594209</v>
+        <v>601583</v>
       </c>
       <c r="N19" t="s">
         <v>27</v>
       </c>
       <c r="O19">
-        <v>41.75</v>
+        <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q19" t="s">
         <v>29</v>
       </c>
-      <c r="R19" t="s">
-        <v>26</v>
+      <c r="R19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1747,7 +1753,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -1761,32 +1767,32 @@
       <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="G20" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="1">
-        <v>28</v>
+      <c r="G20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J20" t="s">
         <v>25</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L20" s="1">
-        <v>46231</v>
+        <v>46238</v>
       </c>
       <c r="M20">
-        <v>598353</v>
+        <v>601025</v>
       </c>
       <c r="N20" t="s">
         <v>27</v>
       </c>
       <c r="O20">
-        <v>6.9</v>
+        <v>41.62</v>
       </c>
       <c r="P20" t="s">
         <v>36</v>
@@ -1794,8 +1800,8 @@
       <c r="Q20" t="s">
         <v>29</v>
       </c>
-      <c r="R20" t="s">
-        <v>26</v>
+      <c r="R20">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -1803,7 +1809,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -1817,41 +1823,41 @@
       <c r="F21" t="s">
         <v>22</v>
       </c>
-      <c r="G21" t="s">
-        <v>55</v>
-      </c>
-      <c r="H21" s="1">
-        <v>2</v>
+      <c r="G21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21">
+        <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J21" t="s">
         <v>25</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="1">
-        <v>46205</v>
+        <v>46239</v>
       </c>
       <c r="M21">
-        <v>585567</v>
+        <v>601537</v>
       </c>
       <c r="N21" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="O21">
-        <v>1.41</v>
+        <v>4.63</v>
       </c>
       <c r="P21" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q21" t="s">
-        <v>94</v>
-      </c>
-      <c r="R21" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -1859,7 +1865,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
@@ -1873,41 +1879,41 @@
       <c r="F22" t="s">
         <v>22</v>
       </c>
-      <c r="G22" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="1">
-        <v>2</v>
+      <c r="G22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22">
+        <v>6</v>
       </c>
       <c r="I22" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J22" t="s">
         <v>25</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L22" s="1">
-        <v>46205</v>
+        <v>46240</v>
       </c>
       <c r="M22">
-        <v>585435</v>
+        <v>601944</v>
       </c>
       <c r="N22" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="O22">
-        <v>34.979999999999997</v>
+        <v>1.96</v>
       </c>
       <c r="P22" t="s">
         <v>36</v>
       </c>
       <c r="Q22" t="s">
-        <v>95</v>
-      </c>
-      <c r="R22" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -1915,7 +1921,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
@@ -1929,32 +1935,32 @@
       <c r="F23" t="s">
         <v>22</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="1">
-        <v>6</v>
+      <c r="H23">
+        <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J23" t="s">
         <v>25</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L23" s="1">
-        <v>46209</v>
+        <v>46241</v>
       </c>
       <c r="M23">
-        <v>587363</v>
+        <v>603017</v>
       </c>
       <c r="N23" t="s">
         <v>27</v>
       </c>
       <c r="O23">
-        <v>7.85</v>
+        <v>1.89</v>
       </c>
       <c r="P23" t="s">
         <v>36</v>
@@ -1962,8 +1968,8 @@
       <c r="Q23" t="s">
         <v>29</v>
       </c>
-      <c r="R23" t="s">
-        <v>26</v>
+      <c r="R23">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -1971,7 +1977,7 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -1985,41 +1991,41 @@
       <c r="F24" t="s">
         <v>22</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="1">
-        <v>2</v>
+      <c r="H24">
+        <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J24" t="s">
         <v>25</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="1">
-        <v>46205</v>
+        <v>46241</v>
       </c>
       <c r="M24">
-        <v>589815</v>
+        <v>602969</v>
       </c>
       <c r="N24" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="O24">
-        <v>30.92</v>
+        <v>6.12</v>
       </c>
       <c r="P24" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="Q24" t="s">
         <v>29</v>
       </c>
-      <c r="R24" t="s">
-        <v>26</v>
+      <c r="R24">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2027,7 +2033,7 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -2041,11 +2047,11 @@
       <c r="F25" t="s">
         <v>22</v>
       </c>
-      <c r="G25" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" s="1">
-        <v>7</v>
+      <c r="G25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25">
+        <v>10</v>
       </c>
       <c r="I25" t="s">
         <v>24</v>
@@ -2053,20 +2059,20 @@
       <c r="J25" t="s">
         <v>25</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L25" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="M25">
-        <v>602969</v>
+        <v>603608</v>
       </c>
       <c r="N25" t="s">
         <v>27</v>
       </c>
       <c r="O25">
-        <v>6.12</v>
+        <v>8.77</v>
       </c>
       <c r="P25" t="s">
         <v>36</v>
@@ -2074,16 +2080,16 @@
       <c r="Q25" t="s">
         <v>29</v>
       </c>
-      <c r="R25" t="s">
-        <v>26</v>
+      <c r="R25">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
@@ -2092,46 +2098,46 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s">
         <v>22</v>
       </c>
-      <c r="G26" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="1">
-        <v>21</v>
+      <c r="G26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26">
+        <v>11</v>
       </c>
       <c r="I26" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J26" t="s">
         <v>25</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L26" s="1">
-        <v>46224</v>
+        <v>46245</v>
       </c>
       <c r="M26">
-        <v>593210</v>
+        <v>604128</v>
       </c>
       <c r="N26" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="P26" t="s">
         <v>56</v>
       </c>
       <c r="Q26" t="s">
-        <v>96</v>
-      </c>
-      <c r="R26" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R26" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -2139,7 +2145,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -2153,11 +2159,11 @@
       <c r="F27" t="s">
         <v>22</v>
       </c>
-      <c r="G27" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="1">
-        <v>5</v>
+      <c r="G27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27">
+        <v>11</v>
       </c>
       <c r="I27" t="s">
         <v>24</v>
@@ -2165,20 +2171,20 @@
       <c r="J27" t="s">
         <v>25</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L27" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="M27">
-        <v>601537</v>
+        <v>604194</v>
       </c>
       <c r="N27" t="s">
         <v>27</v>
       </c>
       <c r="O27">
-        <v>4.63</v>
+        <v>2.98</v>
       </c>
       <c r="P27" t="s">
         <v>36</v>
@@ -2186,16 +2192,16 @@
       <c r="Q27" t="s">
         <v>29</v>
       </c>
-      <c r="R27" t="s">
-        <v>26</v>
+      <c r="R27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
@@ -2204,46 +2210,46 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" t="s">
-        <v>33</v>
-      </c>
-      <c r="H28" s="1">
-        <v>8</v>
+        <v>99</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H28">
+        <v>13</v>
       </c>
       <c r="I28" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J28" t="s">
         <v>25</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L28" s="1">
-        <v>46211</v>
+        <v>46247</v>
       </c>
       <c r="M28">
-        <v>588663</v>
+        <v>605287</v>
       </c>
       <c r="N28" t="s">
         <v>27</v>
       </c>
       <c r="O28">
-        <v>35.78</v>
+        <v>61.58</v>
       </c>
       <c r="P28" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q28" t="s">
         <v>29</v>
       </c>
-      <c r="R28" t="s">
-        <v>26</v>
+      <c r="R28" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -2251,7 +2257,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
         <v>19</v>
@@ -2265,49 +2271,49 @@
       <c r="F29" t="s">
         <v>22</v>
       </c>
-      <c r="G29" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="1">
-        <v>15</v>
+      <c r="G29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29">
+        <v>13</v>
       </c>
       <c r="I29" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J29" t="s">
         <v>25</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="1">
-        <v>46218</v>
+        <v>46247</v>
       </c>
       <c r="M29">
-        <v>591629</v>
+        <v>605244</v>
       </c>
       <c r="N29" t="s">
         <v>27</v>
       </c>
       <c r="O29">
-        <v>10.44</v>
+        <v>91.5</v>
       </c>
       <c r="P29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q29" t="s">
         <v>29</v>
       </c>
-      <c r="R29" t="s">
-        <v>26</v>
+      <c r="R29" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -2316,43 +2322,96 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30">
+        <v>14</v>
+      </c>
+      <c r="I30" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="1">
+        <v>46248</v>
+      </c>
+      <c r="M30">
+        <v>606392</v>
+      </c>
+      <c r="N30" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30">
+        <v>4.55</v>
+      </c>
+      <c r="P30" t="s">
+        <v>28</v>
+      </c>
+      <c r="R30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
         <v>32</v>
       </c>
-      <c r="F30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="F31" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H31">
+        <v>17</v>
+      </c>
+      <c r="I31" t="s">
         <v>24</v>
       </c>
-      <c r="I30" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="1">
-        <v>46227</v>
-      </c>
-      <c r="M30">
-        <v>582148</v>
-      </c>
-      <c r="N30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O30">
-        <v>7.87</v>
-      </c>
-      <c r="P30" t="s">
-        <v>61</v>
-      </c>
-      <c r="R30" t="s">
-        <v>26</v>
+      <c r="J31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="1">
+        <v>46251</v>
+      </c>
+      <c r="M31">
+        <v>606908</v>
+      </c>
+      <c r="N31" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="P31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R31" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -2608,31 +2667,31 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>112.48399999999999</v>
+        <v>121.46199999999999</v>
       </c>
       <c r="E7">
-        <v>159.7595</v>
+        <v>170.4811</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="J7">
-        <v>1.1666666666666667</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="K7">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L7">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2649,28 +2708,28 @@
         <v>86</v>
       </c>
       <c r="E8">
-        <v>153.90360000000001</v>
+        <v>242.07859999999999</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G8">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J8">
         <v>0.6</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L8">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2687,28 +2746,28 @@
         <v>86</v>
       </c>
       <c r="E9">
-        <v>356.66750000000002</v>
+        <v>450.55970000000002</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I9">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="J9">
-        <v>0.93333333333333335</v>
+        <v>0.89333333333333331</v>
       </c>
       <c r="K9">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L9">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66AC95C-CBC0-4A5C-B876-8DCCED8A1873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FA261C-DCA3-4A4E-9C7C-DCFC544ADCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="107">
   <si>
     <t>Usuário</t>
   </si>
@@ -353,6 +353,12 @@
   </si>
   <si>
     <t>CLARICE LUNARDI</t>
+  </si>
+  <si>
+    <t>VIVIANE ELISA DE ABREU</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
   </si>
 </sst>
 </file>
@@ -677,11 +683,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -700,10 +706,10 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -712,13 +718,13 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -756,10 +762,10 @@
       <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>55</v>
       </c>
       <c r="H2">
@@ -768,13 +774,13 @@
       <c r="I2" t="s">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2">
         <v>46205</v>
       </c>
       <c r="M2">
@@ -792,8 +798,8 @@
       <c r="Q2" t="s">
         <v>94</v>
       </c>
-      <c r="R2">
-        <v>1</v>
+      <c r="R2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -812,10 +818,10 @@
       <c r="E3" t="s">
         <v>32</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>55</v>
       </c>
       <c r="H3">
@@ -824,13 +830,13 @@
       <c r="I3" t="s">
         <v>34</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3">
         <v>46205</v>
       </c>
       <c r="M3">
@@ -848,8 +854,8 @@
       <c r="Q3" t="s">
         <v>95</v>
       </c>
-      <c r="R3">
-        <v>1</v>
+      <c r="R3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -868,10 +874,10 @@
       <c r="E4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>44</v>
       </c>
       <c r="H4">
@@ -880,13 +886,13 @@
       <c r="I4" t="s">
         <v>34</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4">
         <v>46205</v>
       </c>
       <c r="M4">
@@ -904,8 +910,8 @@
       <c r="Q4" t="s">
         <v>29</v>
       </c>
-      <c r="R4">
-        <v>1</v>
+      <c r="R4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -924,10 +930,10 @@
       <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>33</v>
       </c>
       <c r="H5">
@@ -936,13 +942,13 @@
       <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5">
         <v>46209</v>
       </c>
       <c r="M5">
@@ -960,8 +966,8 @@
       <c r="Q5" t="s">
         <v>29</v>
       </c>
-      <c r="R5">
-        <v>1</v>
+      <c r="R5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -980,10 +986,10 @@
       <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>33</v>
       </c>
       <c r="H6">
@@ -992,13 +998,13 @@
       <c r="I6" t="s">
         <v>34</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6">
         <v>46210</v>
       </c>
       <c r="M6">
@@ -1011,13 +1017,13 @@
         <v>67.37</v>
       </c>
       <c r="P6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="s">
         <v>29</v>
       </c>
-      <c r="R6">
-        <v>1</v>
+      <c r="R6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1036,10 +1042,10 @@
       <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>33</v>
       </c>
       <c r="H7">
@@ -1048,13 +1054,13 @@
       <c r="I7" t="s">
         <v>34</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7">
         <v>46211</v>
       </c>
       <c r="M7">
@@ -1072,8 +1078,8 @@
       <c r="Q7" t="s">
         <v>29</v>
       </c>
-      <c r="R7">
-        <v>1</v>
+      <c r="R7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1092,10 +1098,10 @@
       <c r="E8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>33</v>
       </c>
       <c r="H8">
@@ -1104,13 +1110,13 @@
       <c r="I8" t="s">
         <v>34</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8">
         <v>46213</v>
       </c>
       <c r="M8">
@@ -1128,8 +1134,8 @@
       <c r="Q8" t="s">
         <v>29</v>
       </c>
-      <c r="R8">
-        <v>1</v>
+      <c r="R8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1148,10 +1154,10 @@
       <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>41</v>
       </c>
       <c r="H9">
@@ -1160,13 +1166,13 @@
       <c r="I9" t="s">
         <v>34</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9">
         <v>46218</v>
       </c>
       <c r="M9">
@@ -1184,8 +1190,8 @@
       <c r="Q9" t="s">
         <v>29</v>
       </c>
-      <c r="R9">
-        <v>1</v>
+      <c r="R9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1204,10 +1210,10 @@
       <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>33</v>
       </c>
       <c r="H10">
@@ -1216,13 +1222,13 @@
       <c r="I10" t="s">
         <v>34</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10">
         <v>46218</v>
       </c>
       <c r="M10">
@@ -1240,8 +1246,8 @@
       <c r="Q10" t="s">
         <v>29</v>
       </c>
-      <c r="R10">
-        <v>1</v>
+      <c r="R10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1260,10 +1266,10 @@
       <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>33</v>
       </c>
       <c r="H11">
@@ -1272,13 +1278,13 @@
       <c r="I11" t="s">
         <v>34</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11">
         <v>46219</v>
       </c>
       <c r="M11">
@@ -1296,8 +1302,8 @@
       <c r="Q11" t="s">
         <v>29</v>
       </c>
-      <c r="R11">
-        <v>1</v>
+      <c r="R11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1316,10 +1322,10 @@
       <c r="E12" t="s">
         <v>32</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>44</v>
       </c>
       <c r="H12">
@@ -1328,13 +1334,13 @@
       <c r="I12" t="s">
         <v>34</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12">
         <v>46223</v>
       </c>
       <c r="M12">
@@ -1352,8 +1358,8 @@
       <c r="Q12" t="s">
         <v>29</v>
       </c>
-      <c r="R12">
-        <v>1</v>
+      <c r="R12" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -1372,10 +1378,10 @@
       <c r="E13" t="s">
         <v>32</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>33</v>
       </c>
       <c r="H13">
@@ -1384,13 +1390,13 @@
       <c r="I13" t="s">
         <v>34</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13">
         <v>46224</v>
       </c>
       <c r="M13">
@@ -1408,8 +1414,8 @@
       <c r="Q13" t="s">
         <v>96</v>
       </c>
-      <c r="R13">
-        <v>1</v>
+      <c r="R13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1428,10 +1434,10 @@
       <c r="E14" t="s">
         <v>32</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>33</v>
       </c>
       <c r="H14">
@@ -1440,13 +1446,13 @@
       <c r="I14" t="s">
         <v>34</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14">
         <v>46225</v>
       </c>
       <c r="M14">
@@ -1459,13 +1465,13 @@
         <v>11.66</v>
       </c>
       <c r="P14" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q14" t="s">
         <v>29</v>
       </c>
-      <c r="R14">
-        <v>1</v>
+      <c r="R14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -1484,10 +1490,10 @@
       <c r="E15" t="s">
         <v>32</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>33</v>
       </c>
       <c r="H15">
@@ -1496,13 +1502,13 @@
       <c r="I15" t="s">
         <v>34</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15">
         <v>46227</v>
       </c>
       <c r="M15">
@@ -1520,8 +1526,8 @@
       <c r="Q15" t="s">
         <v>29</v>
       </c>
-      <c r="R15">
-        <v>1</v>
+      <c r="R15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -1540,10 +1546,10 @@
       <c r="E16" t="s">
         <v>32</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>33</v>
       </c>
       <c r="H16">
@@ -1552,13 +1558,13 @@
       <c r="I16" t="s">
         <v>34</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16">
         <v>46231</v>
       </c>
       <c r="M16">
@@ -1576,8 +1582,8 @@
       <c r="Q16" t="s">
         <v>29</v>
       </c>
-      <c r="R16">
-        <v>1</v>
+      <c r="R16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1596,10 +1602,10 @@
       <c r="E17" t="s">
         <v>32</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>44</v>
       </c>
       <c r="H17">
@@ -1608,13 +1614,13 @@
       <c r="I17" t="s">
         <v>34</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17">
         <v>46231</v>
       </c>
       <c r="M17">
@@ -1632,8 +1638,8 @@
       <c r="Q17" t="s">
         <v>103</v>
       </c>
-      <c r="R17">
-        <v>1</v>
+      <c r="R17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1652,10 +1658,10 @@
       <c r="E18" t="s">
         <v>32</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>23</v>
       </c>
       <c r="H18">
@@ -1664,13 +1670,13 @@
       <c r="I18" t="s">
         <v>34</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18">
         <v>46231</v>
       </c>
       <c r="M18">
@@ -1688,8 +1694,8 @@
       <c r="Q18" t="s">
         <v>29</v>
       </c>
-      <c r="R18">
-        <v>1</v>
+      <c r="R18" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1708,10 +1714,10 @@
       <c r="E19" t="s">
         <v>32</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>44</v>
       </c>
       <c r="H19">
@@ -1720,13 +1726,13 @@
       <c r="I19" t="s">
         <v>24</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19">
         <v>46237</v>
       </c>
       <c r="M19">
@@ -1744,8 +1750,8 @@
       <c r="Q19" t="s">
         <v>29</v>
       </c>
-      <c r="R19">
-        <v>1</v>
+      <c r="R19" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1764,10 +1770,10 @@
       <c r="E20" t="s">
         <v>32</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>33</v>
       </c>
       <c r="H20">
@@ -1776,13 +1782,13 @@
       <c r="I20" t="s">
         <v>24</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20">
         <v>46238</v>
       </c>
       <c r="M20">
@@ -1800,8 +1806,8 @@
       <c r="Q20" t="s">
         <v>29</v>
       </c>
-      <c r="R20">
-        <v>1</v>
+      <c r="R20" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -1820,10 +1826,10 @@
       <c r="E21" t="s">
         <v>32</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>44</v>
       </c>
       <c r="H21">
@@ -1832,13 +1838,13 @@
       <c r="I21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21">
         <v>46239</v>
       </c>
       <c r="M21">
@@ -1856,8 +1862,8 @@
       <c r="Q21" t="s">
         <v>29</v>
       </c>
-      <c r="R21">
-        <v>1</v>
+      <c r="R21" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -1876,10 +1882,10 @@
       <c r="E22" t="s">
         <v>32</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>33</v>
       </c>
       <c r="H22">
@@ -1888,13 +1894,13 @@
       <c r="I22" t="s">
         <v>24</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22">
         <v>46240</v>
       </c>
       <c r="M22">
@@ -1912,8 +1918,8 @@
       <c r="Q22" t="s">
         <v>29</v>
       </c>
-      <c r="R22">
-        <v>1</v>
+      <c r="R22" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -1932,10 +1938,10 @@
       <c r="E23" t="s">
         <v>32</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>33</v>
       </c>
       <c r="H23">
@@ -1944,13 +1950,13 @@
       <c r="I23" t="s">
         <v>24</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23">
         <v>46241</v>
       </c>
       <c r="M23">
@@ -1968,8 +1974,8 @@
       <c r="Q23" t="s">
         <v>29</v>
       </c>
-      <c r="R23">
-        <v>1</v>
+      <c r="R23" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -1988,10 +1994,10 @@
       <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>44</v>
       </c>
       <c r="H24">
@@ -2000,13 +2006,13 @@
       <c r="I24" t="s">
         <v>24</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24">
         <v>46241</v>
       </c>
       <c r="M24">
@@ -2024,8 +2030,8 @@
       <c r="Q24" t="s">
         <v>29</v>
       </c>
-      <c r="R24">
-        <v>1</v>
+      <c r="R24" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2044,10 +2050,10 @@
       <c r="E25" t="s">
         <v>32</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>33</v>
       </c>
       <c r="H25">
@@ -2056,13 +2062,13 @@
       <c r="I25" t="s">
         <v>24</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25">
         <v>46244</v>
       </c>
       <c r="M25">
@@ -2080,8 +2086,8 @@
       <c r="Q25" t="s">
         <v>29</v>
       </c>
-      <c r="R25">
-        <v>1</v>
+      <c r="R25" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -2100,10 +2106,10 @@
       <c r="E26" t="s">
         <v>21</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>23</v>
       </c>
       <c r="H26">
@@ -2112,13 +2118,13 @@
       <c r="I26" t="s">
         <v>24</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26">
         <v>46245</v>
       </c>
       <c r="M26">
@@ -2156,10 +2162,10 @@
       <c r="E27" t="s">
         <v>32</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>33</v>
       </c>
       <c r="H27">
@@ -2168,13 +2174,13 @@
       <c r="I27" t="s">
         <v>24</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27">
         <v>46245</v>
       </c>
       <c r="M27">
@@ -2192,8 +2198,8 @@
       <c r="Q27" t="s">
         <v>29</v>
       </c>
-      <c r="R27">
-        <v>1</v>
+      <c r="R27" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -2212,10 +2218,10 @@
       <c r="E28" t="s">
         <v>98</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>100</v>
       </c>
       <c r="H28">
@@ -2224,13 +2230,13 @@
       <c r="I28" t="s">
         <v>24</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L28">
         <v>46247</v>
       </c>
       <c r="M28">
@@ -2248,8 +2254,8 @@
       <c r="Q28" t="s">
         <v>29</v>
       </c>
-      <c r="R28" t="e">
-        <v>#N/A</v>
+      <c r="R28" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -2268,10 +2274,10 @@
       <c r="E29" t="s">
         <v>32</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>44</v>
       </c>
       <c r="H29">
@@ -2280,13 +2286,13 @@
       <c r="I29" t="s">
         <v>24</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29">
         <v>46247</v>
       </c>
       <c r="M29">
@@ -2299,13 +2305,13 @@
         <v>91.5</v>
       </c>
       <c r="P29" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q29" t="s">
         <v>29</v>
       </c>
-      <c r="R29" t="e">
-        <v>#N/A</v>
+      <c r="R29" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -2324,10 +2330,10 @@
       <c r="E30" t="s">
         <v>98</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>100</v>
       </c>
       <c r="H30">
@@ -2336,13 +2342,13 @@
       <c r="I30" t="s">
         <v>24</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30">
         <v>46248</v>
       </c>
       <c r="M30">
@@ -2352,13 +2358,13 @@
         <v>27</v>
       </c>
       <c r="O30">
-        <v>4.55</v>
+        <v>5.13</v>
       </c>
       <c r="P30" t="s">
-        <v>28</v>
-      </c>
-      <c r="R30" t="e">
-        <v>#N/A</v>
+        <v>36</v>
+      </c>
+      <c r="R30" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -2377,10 +2383,10 @@
       <c r="E31" t="s">
         <v>32</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>33</v>
       </c>
       <c r="H31">
@@ -2389,13 +2395,13 @@
       <c r="I31" t="s">
         <v>24</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L31">
         <v>46251</v>
       </c>
       <c r="M31">
@@ -2411,6 +2417,59 @@
         <v>28</v>
       </c>
       <c r="R31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32">
+        <v>18</v>
+      </c>
+      <c r="I32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32">
+        <v>46252</v>
+      </c>
+      <c r="M32">
+        <v>581722</v>
+      </c>
+      <c r="N32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O32">
+        <v>21.24</v>
+      </c>
+      <c r="P32" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2421,7 +2480,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -2768,6 +2827,120 @@
       </c>
       <c r="L9">
         <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>99.364399999999009</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>30</v>
+      </c>
+      <c r="H10">
+        <v>27</v>
+      </c>
+      <c r="I10">
+        <v>1.35</v>
+      </c>
+      <c r="J10">
+        <v>1.2666666666666666</v>
+      </c>
+      <c r="K10">
+        <v>11</v>
+      </c>
+      <c r="L10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11">
+        <v>93.6023</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>0.7</v>
+      </c>
+      <c r="J11">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K11">
+        <v>11</v>
+      </c>
+      <c r="L11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12">
+        <v>99.93010000000001</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>0.15</v>
+      </c>
+      <c r="J12">
+        <v>1.5</v>
+      </c>
+      <c r="K12">
+        <v>42</v>
+      </c>
+      <c r="L12">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FA261C-DCA3-4A4E-9C7C-DCFC544ADCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="109">
   <si>
     <t>Usuário</t>
   </si>
@@ -359,6 +359,12 @@
   </si>
   <si>
     <t>Semana 3</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>JORGE ANTONIO DINIZ</t>
   </si>
 </sst>
 </file>
@@ -683,11 +689,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -703,10 +709,10 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -715,13 +721,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -759,10 +765,10 @@
       <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
       <c r="G2" t="s">
@@ -771,13 +777,13 @@
       <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
       <c r="L2">
@@ -815,10 +821,10 @@
       <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3" t="s">
@@ -827,13 +833,13 @@
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
       <c r="L3">
@@ -871,10 +877,10 @@
       <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
@@ -883,13 +889,13 @@
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>26</v>
       </c>
       <c r="L4">
@@ -927,10 +933,10 @@
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
@@ -939,13 +945,13 @@
       <c r="H5">
         <v>6</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>26</v>
       </c>
       <c r="L5">
@@ -983,10 +989,10 @@
       <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>22</v>
       </c>
       <c r="G6" t="s">
@@ -995,13 +1001,13 @@
       <c r="H6">
         <v>7</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>26</v>
       </c>
       <c r="L6">
@@ -1039,10 +1045,10 @@
       <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>22</v>
       </c>
       <c r="G7" t="s">
@@ -1051,13 +1057,13 @@
       <c r="H7">
         <v>8</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>26</v>
       </c>
       <c r="L7">
@@ -1095,10 +1101,10 @@
       <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>22</v>
       </c>
       <c r="G8" t="s">
@@ -1107,13 +1113,13 @@
       <c r="H8">
         <v>10</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>26</v>
       </c>
       <c r="L8">
@@ -1151,10 +1157,10 @@
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" t="s">
@@ -1163,13 +1169,13 @@
       <c r="H9">
         <v>15</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" t="s">
         <v>26</v>
       </c>
       <c r="L9">
@@ -1207,10 +1213,10 @@
       <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10" t="s">
@@ -1219,13 +1225,13 @@
       <c r="H10">
         <v>15</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>26</v>
       </c>
       <c r="L10">
@@ -1263,10 +1269,10 @@
       <c r="D11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>22</v>
       </c>
       <c r="G11" t="s">
@@ -1275,13 +1281,13 @@
       <c r="H11">
         <v>16</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" t="s">
         <v>26</v>
       </c>
       <c r="L11">
@@ -1319,10 +1325,10 @@
       <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>22</v>
       </c>
       <c r="G12" t="s">
@@ -1331,13 +1337,13 @@
       <c r="H12">
         <v>20</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" t="s">
         <v>26</v>
       </c>
       <c r="L12">
@@ -1375,10 +1381,10 @@
       <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13" t="s">
@@ -1387,13 +1393,13 @@
       <c r="H13">
         <v>21</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" t="s">
         <v>26</v>
       </c>
       <c r="L13">
@@ -1431,10 +1437,10 @@
       <c r="D14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14" t="s">
@@ -1443,13 +1449,13 @@
       <c r="H14">
         <v>22</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" t="s">
         <v>26</v>
       </c>
       <c r="L14">
@@ -1487,10 +1493,10 @@
       <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>22</v>
       </c>
       <c r="G15" t="s">
@@ -1499,13 +1505,13 @@
       <c r="H15">
         <v>24</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" t="s">
         <v>26</v>
       </c>
       <c r="L15">
@@ -1543,10 +1549,10 @@
       <c r="D16" t="s">
         <v>20</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>22</v>
       </c>
       <c r="G16" t="s">
@@ -1555,13 +1561,13 @@
       <c r="H16">
         <v>28</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" t="s">
         <v>26</v>
       </c>
       <c r="L16">
@@ -1599,10 +1605,10 @@
       <c r="D17" t="s">
         <v>20</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>22</v>
       </c>
       <c r="G17" t="s">
@@ -1611,13 +1617,13 @@
       <c r="H17">
         <v>28</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" t="s">
         <v>26</v>
       </c>
       <c r="L17">
@@ -1655,10 +1661,10 @@
       <c r="D18" t="s">
         <v>20</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
@@ -1667,13 +1673,13 @@
       <c r="H18">
         <v>28</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" t="s">
         <v>26</v>
       </c>
       <c r="L18">
@@ -1711,10 +1717,10 @@
       <c r="D19" t="s">
         <v>20</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>22</v>
       </c>
       <c r="G19" t="s">
@@ -1723,13 +1729,13 @@
       <c r="H19">
         <v>3</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" t="s">
         <v>26</v>
       </c>
       <c r="L19">
@@ -1767,10 +1773,10 @@
       <c r="D20" t="s">
         <v>20</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>22</v>
       </c>
       <c r="G20" t="s">
@@ -1779,13 +1785,13 @@
       <c r="H20">
         <v>4</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" t="s">
         <v>26</v>
       </c>
       <c r="L20">
@@ -1823,10 +1829,10 @@
       <c r="D21" t="s">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>22</v>
       </c>
       <c r="G21" t="s">
@@ -1835,13 +1841,13 @@
       <c r="H21">
         <v>5</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" t="s">
         <v>26</v>
       </c>
       <c r="L21">
@@ -1879,10 +1885,10 @@
       <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>22</v>
       </c>
       <c r="G22" t="s">
@@ -1891,13 +1897,13 @@
       <c r="H22">
         <v>6</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" t="s">
         <v>26</v>
       </c>
       <c r="L22">
@@ -1935,10 +1941,10 @@
       <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>22</v>
       </c>
       <c r="G23" t="s">
@@ -1947,13 +1953,13 @@
       <c r="H23">
         <v>7</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" t="s">
         <v>26</v>
       </c>
       <c r="L23">
@@ -1991,10 +1997,10 @@
       <c r="D24" t="s">
         <v>20</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>22</v>
       </c>
       <c r="G24" t="s">
@@ -2003,13 +2009,13 @@
       <c r="H24">
         <v>7</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" t="s">
         <v>26</v>
       </c>
       <c r="L24">
@@ -2047,10 +2053,10 @@
       <c r="D25" t="s">
         <v>20</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>22</v>
       </c>
       <c r="G25" t="s">
@@ -2059,13 +2065,13 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" t="s">
         <v>26</v>
       </c>
       <c r="L25">
@@ -2103,10 +2109,10 @@
       <c r="D26" t="s">
         <v>20</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>22</v>
       </c>
       <c r="G26" t="s">
@@ -2115,13 +2121,13 @@
       <c r="H26">
         <v>11</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" t="s">
         <v>26</v>
       </c>
       <c r="L26">
@@ -2159,10 +2165,10 @@
       <c r="D27" t="s">
         <v>20</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>22</v>
       </c>
       <c r="G27" t="s">
@@ -2171,13 +2177,13 @@
       <c r="H27">
         <v>11</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" t="s">
         <v>26</v>
       </c>
       <c r="L27">
@@ -2215,10 +2221,10 @@
       <c r="D28" t="s">
         <v>20</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>99</v>
       </c>
       <c r="G28" t="s">
@@ -2227,13 +2233,13 @@
       <c r="H28">
         <v>13</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" t="s">
         <v>26</v>
       </c>
       <c r="L28">
@@ -2271,10 +2277,10 @@
       <c r="D29" t="s">
         <v>20</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>22</v>
       </c>
       <c r="G29" t="s">
@@ -2283,13 +2289,13 @@
       <c r="H29">
         <v>13</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" t="s">
         <v>26</v>
       </c>
       <c r="L29">
@@ -2327,10 +2333,10 @@
       <c r="D30" t="s">
         <v>20</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>99</v>
       </c>
       <c r="G30" t="s">
@@ -2339,13 +2345,13 @@
       <c r="H30">
         <v>14</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" t="s">
         <v>26</v>
       </c>
       <c r="L30">
@@ -2380,10 +2386,10 @@
       <c r="D31" t="s">
         <v>20</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>22</v>
       </c>
       <c r="G31" t="s">
@@ -2392,13 +2398,13 @@
       <c r="H31">
         <v>17</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" t="s">
         <v>26</v>
       </c>
       <c r="L31">
@@ -2433,10 +2439,10 @@
       <c r="D32" t="s">
         <v>20</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>22</v>
       </c>
       <c r="G32" t="s">
@@ -2445,13 +2451,13 @@
       <c r="H32">
         <v>18</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" t="s">
         <v>26</v>
       </c>
       <c r="L32">
@@ -2470,6 +2476,112 @@
         <v>28</v>
       </c>
       <c r="R32" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" t="s">
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <v>19</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33">
+        <v>46253</v>
+      </c>
+      <c r="M33">
+        <v>608180</v>
+      </c>
+      <c r="N33" t="s">
+        <v>27</v>
+      </c>
+      <c r="O33">
+        <v>2.67</v>
+      </c>
+      <c r="P33" t="s">
+        <v>28</v>
+      </c>
+      <c r="R33" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34">
+        <v>19</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34">
+        <v>46253</v>
+      </c>
+      <c r="M34">
+        <v>608150</v>
+      </c>
+      <c r="N34" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34">
+        <v>4.54</v>
+      </c>
+      <c r="P34" t="s">
+        <v>28</v>
+      </c>
+      <c r="R34" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgg\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A89BF798-208A-4BB3-9327-8E3BBFF0B36F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="120">
   <si>
     <t>Usuário</t>
   </si>
@@ -361,10 +361,43 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>d</t>
-  </si>
-  <si>
     <t>JORGE ANTONIO DINIZ</t>
+  </si>
+  <si>
+    <t>AJUSTE DE DOCUMENTAÇÃO</t>
+  </si>
+  <si>
+    <t>CARLOS PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>MARIA CIRLIANE GILDO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ELIEZER SOARES CAVALCANTE</t>
+  </si>
+  <si>
+    <t>ANALISE DE CRÉDITO</t>
+  </si>
+  <si>
+    <t>HISSA DEMETRIO FABRIC DE BISCOITOS EIREL</t>
+  </si>
+  <si>
+    <t>ANA RIBEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>NICOLAS RENAN TOMAZ LOPES</t>
+  </si>
+  <si>
+    <t>Eusébio</t>
+  </si>
+  <si>
+    <t>MODA EXPRESS 001 COMERCIO DE VESTUARIO LTDA</t>
+  </si>
+  <si>
+    <t>ANTONIA ROSÁLIA MEDEIROS DE SOUSA</t>
+  </si>
+  <si>
+    <t>NELIO LANA DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -689,11 +722,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -706,10 +739,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -718,13 +751,13 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -762,10 +795,10 @@
       <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
       <c r="F2" t="s">
@@ -774,13 +807,13 @@
       <c r="G2" t="s">
         <v>55</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>25</v>
       </c>
       <c r="K2" t="s">
@@ -818,10 +851,10 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>32</v>
       </c>
       <c r="F3" t="s">
@@ -830,13 +863,13 @@
       <c r="G3" t="s">
         <v>55</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>25</v>
       </c>
       <c r="K3" t="s">
@@ -874,10 +907,10 @@
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>32</v>
       </c>
       <c r="F4" t="s">
@@ -886,13 +919,13 @@
       <c r="G4" t="s">
         <v>44</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>25</v>
       </c>
       <c r="K4" t="s">
@@ -930,10 +963,10 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>32</v>
       </c>
       <c r="F5" t="s">
@@ -942,13 +975,13 @@
       <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>6</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>25</v>
       </c>
       <c r="K5" t="s">
@@ -986,10 +1019,10 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>32</v>
       </c>
       <c r="F6" t="s">
@@ -998,13 +1031,13 @@
       <c r="G6" t="s">
         <v>33</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>7</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>25</v>
       </c>
       <c r="K6" t="s">
@@ -1042,10 +1075,10 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
       <c r="F7" t="s">
@@ -1054,13 +1087,13 @@
       <c r="G7" t="s">
         <v>33</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>25</v>
       </c>
       <c r="K7" t="s">
@@ -1098,10 +1131,10 @@
       <c r="C8" t="s">
         <v>50</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
         <v>32</v>
       </c>
       <c r="F8" t="s">
@@ -1110,13 +1143,13 @@
       <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>25</v>
       </c>
       <c r="K8" t="s">
@@ -1154,10 +1187,10 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
       </c>
       <c r="F9" t="s">
@@ -1166,13 +1199,13 @@
       <c r="G9" t="s">
         <v>41</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>15</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>25</v>
       </c>
       <c r="K9" t="s">
@@ -1210,10 +1243,10 @@
       <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
       </c>
       <c r="F10" t="s">
@@ -1222,13 +1255,13 @@
       <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>25</v>
       </c>
       <c r="K10" t="s">
@@ -1266,10 +1299,10 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
       <c r="F11" t="s">
@@ -1278,13 +1311,13 @@
       <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" t="s">
         <v>25</v>
       </c>
       <c r="K11" t="s">
@@ -1322,10 +1355,10 @@
       <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
         <v>32</v>
       </c>
       <c r="F12" t="s">
@@ -1334,13 +1367,13 @@
       <c r="G12" t="s">
         <v>44</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>25</v>
       </c>
       <c r="K12" t="s">
@@ -1378,10 +1411,10 @@
       <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
         <v>32</v>
       </c>
       <c r="F13" t="s">
@@ -1390,13 +1423,13 @@
       <c r="G13" t="s">
         <v>33</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>21</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" t="s">
         <v>25</v>
       </c>
       <c r="K13" t="s">
@@ -1434,10 +1467,10 @@
       <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
         <v>32</v>
       </c>
       <c r="F14" t="s">
@@ -1446,13 +1479,13 @@
       <c r="G14" t="s">
         <v>33</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>22</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" t="s">
         <v>25</v>
       </c>
       <c r="K14" t="s">
@@ -1490,10 +1523,10 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
         <v>32</v>
       </c>
       <c r="F15" t="s">
@@ -1502,13 +1535,13 @@
       <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" t="s">
         <v>25</v>
       </c>
       <c r="K15" t="s">
@@ -1546,10 +1579,10 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
         <v>32</v>
       </c>
       <c r="F16" t="s">
@@ -1558,13 +1591,13 @@
       <c r="G16" t="s">
         <v>33</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>28</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>25</v>
       </c>
       <c r="K16" t="s">
@@ -1602,10 +1635,10 @@
       <c r="C17" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
         <v>32</v>
       </c>
       <c r="F17" t="s">
@@ -1614,13 +1647,13 @@
       <c r="G17" t="s">
         <v>44</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" t="s">
         <v>25</v>
       </c>
       <c r="K17" t="s">
@@ -1658,10 +1691,10 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="D18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
         <v>32</v>
       </c>
       <c r="F18" t="s">
@@ -1670,13 +1703,13 @@
       <c r="G18" t="s">
         <v>23</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>25</v>
       </c>
       <c r="K18" t="s">
@@ -1714,10 +1747,10 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
         <v>32</v>
       </c>
       <c r="F19" t="s">
@@ -1726,13 +1759,13 @@
       <c r="G19" t="s">
         <v>44</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" t="s">
         <v>25</v>
       </c>
       <c r="K19" t="s">
@@ -1770,10 +1803,10 @@
       <c r="C20" t="s">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
         <v>32</v>
       </c>
       <c r="F20" t="s">
@@ -1782,13 +1815,13 @@
       <c r="G20" t="s">
         <v>33</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>25</v>
       </c>
       <c r="K20" t="s">
@@ -1826,10 +1859,10 @@
       <c r="C21" t="s">
         <v>19</v>
       </c>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
         <v>32</v>
       </c>
       <c r="F21" t="s">
@@ -1838,13 +1871,13 @@
       <c r="G21" t="s">
         <v>44</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>5</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" t="s">
         <v>25</v>
       </c>
       <c r="K21" t="s">
@@ -1882,10 +1915,10 @@
       <c r="C22" t="s">
         <v>19</v>
       </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
         <v>32</v>
       </c>
       <c r="F22" t="s">
@@ -1894,13 +1927,13 @@
       <c r="G22" t="s">
         <v>33</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>6</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" t="s">
         <v>25</v>
       </c>
       <c r="K22" t="s">
@@ -1938,10 +1971,10 @@
       <c r="C23" t="s">
         <v>19</v>
       </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="D23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
         <v>32</v>
       </c>
       <c r="F23" t="s">
@@ -1950,13 +1983,13 @@
       <c r="G23" t="s">
         <v>33</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>7</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>25</v>
       </c>
       <c r="K23" t="s">
@@ -1994,10 +2027,10 @@
       <c r="C24" t="s">
         <v>19</v>
       </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="D24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
         <v>32</v>
       </c>
       <c r="F24" t="s">
@@ -2006,13 +2039,13 @@
       <c r="G24" t="s">
         <v>44</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>7</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>25</v>
       </c>
       <c r="K24" t="s">
@@ -2050,10 +2083,10 @@
       <c r="C25" t="s">
         <v>19</v>
       </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="D25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
         <v>32</v>
       </c>
       <c r="F25" t="s">
@@ -2062,13 +2095,13 @@
       <c r="G25" t="s">
         <v>33</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" t="s">
         <v>25</v>
       </c>
       <c r="K25" t="s">
@@ -2106,10 +2139,10 @@
       <c r="C26" t="s">
         <v>19</v>
       </c>
-      <c r="D26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="D26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
         <v>21</v>
       </c>
       <c r="F26" t="s">
@@ -2118,13 +2151,13 @@
       <c r="G26" t="s">
         <v>23</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>11</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" t="s">
         <v>25</v>
       </c>
       <c r="K26" t="s">
@@ -2162,10 +2195,10 @@
       <c r="C27" t="s">
         <v>19</v>
       </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="D27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
         <v>32</v>
       </c>
       <c r="F27" t="s">
@@ -2174,13 +2207,13 @@
       <c r="G27" t="s">
         <v>33</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>11</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>25</v>
       </c>
       <c r="K27" t="s">
@@ -2218,10 +2251,10 @@
       <c r="C28" t="s">
         <v>19</v>
       </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="D28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
         <v>98</v>
       </c>
       <c r="F28" t="s">
@@ -2230,13 +2263,13 @@
       <c r="G28" t="s">
         <v>100</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>13</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" t="s">
         <v>25</v>
       </c>
       <c r="K28" t="s">
@@ -2274,10 +2307,10 @@
       <c r="C29" t="s">
         <v>19</v>
       </c>
-      <c r="D29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="D29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
         <v>32</v>
       </c>
       <c r="F29" t="s">
@@ -2286,13 +2319,13 @@
       <c r="G29" t="s">
         <v>44</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>13</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" t="s">
         <v>25</v>
       </c>
       <c r="K29" t="s">
@@ -2330,10 +2363,10 @@
       <c r="C30" t="s">
         <v>19</v>
       </c>
-      <c r="D30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="D30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
         <v>98</v>
       </c>
       <c r="F30" t="s">
@@ -2342,13 +2375,13 @@
       <c r="G30" t="s">
         <v>100</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>14</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" t="s">
         <v>25</v>
       </c>
       <c r="K30" t="s">
@@ -2367,7 +2400,7 @@
         <v>5.13</v>
       </c>
       <c r="P30" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="R30" t="s">
         <v>26</v>
@@ -2383,10 +2416,10 @@
       <c r="C31" t="s">
         <v>19</v>
       </c>
-      <c r="D31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="D31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
         <v>32</v>
       </c>
       <c r="F31" t="s">
@@ -2395,13 +2428,13 @@
       <c r="G31" t="s">
         <v>33</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" t="s">
         <v>25</v>
       </c>
       <c r="K31" t="s">
@@ -2420,10 +2453,10 @@
         <v>37.299999999999997</v>
       </c>
       <c r="P31" t="s">
-        <v>28</v>
-      </c>
-      <c r="R31" t="e">
-        <v>#N/A</v>
+        <v>36</v>
+      </c>
+      <c r="R31" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -2436,10 +2469,10 @@
       <c r="C32" t="s">
         <v>19</v>
       </c>
-      <c r="D32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="D32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
         <v>32</v>
       </c>
       <c r="F32" t="s">
@@ -2448,13 +2481,13 @@
       <c r="G32" t="s">
         <v>33</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" t="s">
         <v>25</v>
       </c>
       <c r="K32" t="s">
@@ -2475,8 +2508,8 @@
       <c r="P32" t="s">
         <v>28</v>
       </c>
-      <c r="R32" t="e">
-        <v>#N/A</v>
+      <c r="R32" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -2484,15 +2517,15 @@
         <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
       </c>
-      <c r="D33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="D33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
         <v>98</v>
       </c>
       <c r="F33" t="s">
@@ -2501,13 +2534,13 @@
       <c r="G33" t="s">
         <v>100</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>19</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" t="s">
         <v>25</v>
       </c>
       <c r="K33" t="s">
@@ -2537,15 +2570,15 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
         <v>19</v>
       </c>
-      <c r="D34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="D34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
         <v>32</v>
       </c>
       <c r="F34" t="s">
@@ -2554,13 +2587,13 @@
       <c r="G34" t="s">
         <v>44</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>19</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" t="s">
         <v>25</v>
       </c>
       <c r="K34" t="s">
@@ -2582,6 +2615,430 @@
         <v>28</v>
       </c>
       <c r="R34" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" s="1">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35">
+        <v>46254</v>
+      </c>
+      <c r="M35">
+        <v>608550</v>
+      </c>
+      <c r="N35" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35">
+        <v>9.1</v>
+      </c>
+      <c r="P35" t="s">
+        <v>28</v>
+      </c>
+      <c r="R35" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>98</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" t="s">
+        <v>100</v>
+      </c>
+      <c r="H36" s="1">
+        <v>21</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36">
+        <v>46255</v>
+      </c>
+      <c r="M36">
+        <v>605051</v>
+      </c>
+      <c r="N36" t="s">
+        <v>45</v>
+      </c>
+      <c r="O36">
+        <v>5.89</v>
+      </c>
+      <c r="P36" t="s">
+        <v>112</v>
+      </c>
+      <c r="R36" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" t="s">
+        <v>100</v>
+      </c>
+      <c r="H37" s="1">
+        <v>21</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37">
+        <v>46255</v>
+      </c>
+      <c r="M37">
+        <v>557624</v>
+      </c>
+      <c r="N37" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37" t="s">
+        <v>56</v>
+      </c>
+      <c r="R37" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="1">
+        <v>21</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38">
+        <v>46255</v>
+      </c>
+      <c r="M38">
+        <v>609384</v>
+      </c>
+      <c r="N38" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38">
+        <v>2.14</v>
+      </c>
+      <c r="P38" t="s">
+        <v>28</v>
+      </c>
+      <c r="R38" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>98</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+      <c r="G39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="1">
+        <v>21</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39">
+        <v>46255</v>
+      </c>
+      <c r="M39">
+        <v>609414</v>
+      </c>
+      <c r="N39" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39">
+        <v>26.48</v>
+      </c>
+      <c r="P39" t="s">
+        <v>28</v>
+      </c>
+      <c r="R39" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>98</v>
+      </c>
+      <c r="F40" t="s">
+        <v>99</v>
+      </c>
+      <c r="G40" t="s">
+        <v>100</v>
+      </c>
+      <c r="H40" s="1">
+        <v>21</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" t="s">
+        <v>26</v>
+      </c>
+      <c r="L40">
+        <v>46255</v>
+      </c>
+      <c r="M40">
+        <v>604864</v>
+      </c>
+      <c r="N40" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40">
+        <v>19.47</v>
+      </c>
+      <c r="P40" t="s">
+        <v>36</v>
+      </c>
+      <c r="R40" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
+        <v>98</v>
+      </c>
+      <c r="F41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G41" t="s">
+        <v>100</v>
+      </c>
+      <c r="H41" s="1">
+        <v>21</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41">
+        <v>46255</v>
+      </c>
+      <c r="M41">
+        <v>605070</v>
+      </c>
+      <c r="N41" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41">
+        <v>3.19</v>
+      </c>
+      <c r="P41" t="s">
+        <v>36</v>
+      </c>
+      <c r="R41" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="1">
+        <v>21</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42">
+        <v>46255</v>
+      </c>
+      <c r="M42">
+        <v>609512</v>
+      </c>
+      <c r="N42" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42">
+        <v>7.06</v>
+      </c>
+      <c r="P42" t="s">
+        <v>28</v>
+      </c>
+      <c r="R42" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2952,31 +3409,31 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>164.92499999999998</v>
       </c>
       <c r="E10">
-        <v>99.364399999999009</v>
+        <v>198.66729999999998</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G10">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H10">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I10">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="J10">
-        <v>1.2666666666666666</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="K10">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="L10">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -2993,28 +3450,28 @@
         <v>86</v>
       </c>
       <c r="E11">
-        <v>93.6023</v>
+        <v>201.11429999999999</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G11">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H11">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="I11">
-        <v>0.7</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="J11">
-        <v>0.83333333333333337</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="K11">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L11">
-        <v>25</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -3031,28 +3488,28 @@
         <v>86</v>
       </c>
       <c r="E12">
-        <v>99.93010000000001</v>
+        <v>168.17070000000001</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G12">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I12">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="J12">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K12">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L12">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3140,4 +3597,308 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
+    <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <xsd:import namespace="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cefda5ab-fc9a-44ce-8da7-9655a4827298" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="12" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="39c4b66d-fcb2-4727-8ac1-aa661c0d9717" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="56aee56a-c72d-444c-b43d-3bc54f84985f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4f9d03b5-8c03-44e8-9bdf-5ab801b25987}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="56aee56a-c72d-444c-b43d-3bc54f84985f">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCD2A909-53DD-4636-B6FE-381AEBE261B8}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A89BF798-208A-4BB3-9327-8E3BBFF0B36F}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82DE1B4F-07C8-40A4-B813-D7F37EB34D75}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="122">
   <si>
     <t>Usuário</t>
   </si>
@@ -398,6 +398,12 @@
   </si>
   <si>
     <t>NELIO LANA DA SILVA</t>
+  </si>
+  <si>
+    <t>NEGOCIAÇÃO QUENTE</t>
+  </si>
+  <si>
+    <t>GENI NATALIA DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -722,11 +728,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -736,10 +742,10 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -748,13 +754,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -792,10 +798,10 @@
       <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
       <c r="E2" t="s">
@@ -804,13 +810,13 @@
       <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>55</v>
       </c>
       <c r="H2" s="1">
         <v>2</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>34</v>
       </c>
       <c r="J2" t="s">
@@ -848,10 +854,10 @@
       <c r="B3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
@@ -860,13 +866,13 @@
       <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>34</v>
       </c>
       <c r="J3" t="s">
@@ -904,10 +910,10 @@
       <c r="B4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
@@ -916,13 +922,13 @@
       <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="1">
         <v>2</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>34</v>
       </c>
       <c r="J4" t="s">
@@ -960,10 +966,10 @@
       <c r="B5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
       <c r="E5" t="s">
@@ -972,13 +978,13 @@
       <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="1">
         <v>6</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>34</v>
       </c>
       <c r="J5" t="s">
@@ -1016,10 +1022,10 @@
       <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
@@ -1028,13 +1034,13 @@
       <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="1">
         <v>7</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>34</v>
       </c>
       <c r="J6" t="s">
@@ -1072,10 +1078,10 @@
       <c r="B7" t="s">
         <v>65</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
       <c r="E7" t="s">
@@ -1084,13 +1090,13 @@
       <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="1">
         <v>8</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>34</v>
       </c>
       <c r="J7" t="s">
@@ -1128,10 +1134,10 @@
       <c r="B8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8" t="s">
@@ -1140,13 +1146,13 @@
       <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="1">
         <v>10</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>34</v>
       </c>
       <c r="J8" t="s">
@@ -1184,10 +1190,10 @@
       <c r="B9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
@@ -1196,13 +1202,13 @@
       <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H9" s="1">
         <v>15</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>34</v>
       </c>
       <c r="J9" t="s">
@@ -1240,10 +1246,10 @@
       <c r="B10" t="s">
         <v>66</v>
       </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
         <v>20</v>
       </c>
       <c r="E10" t="s">
@@ -1252,13 +1258,13 @@
       <c r="F10" t="s">
         <v>22</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="1">
         <v>15</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>34</v>
       </c>
       <c r="J10" t="s">
@@ -1296,10 +1302,10 @@
       <c r="B11" t="s">
         <v>46</v>
       </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
         <v>20</v>
       </c>
       <c r="E11" t="s">
@@ -1308,13 +1314,13 @@
       <c r="F11" t="s">
         <v>22</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="1">
         <v>16</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>34</v>
       </c>
       <c r="J11" t="s">
@@ -1352,10 +1358,10 @@
       <c r="B12" t="s">
         <v>52</v>
       </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
         <v>20</v>
       </c>
       <c r="E12" t="s">
@@ -1364,13 +1370,13 @@
       <c r="F12" t="s">
         <v>22</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>34</v>
       </c>
       <c r="J12" t="s">
@@ -1408,10 +1414,10 @@
       <c r="B13" t="s">
         <v>63</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
@@ -1420,13 +1426,13 @@
       <c r="F13" t="s">
         <v>22</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="1">
         <v>21</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>34</v>
       </c>
       <c r="J13" t="s">
@@ -1464,10 +1470,10 @@
       <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
         <v>20</v>
       </c>
       <c r="E14" t="s">
@@ -1476,13 +1482,13 @@
       <c r="F14" t="s">
         <v>22</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="1">
         <v>22</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>34</v>
       </c>
       <c r="J14" t="s">
@@ -1520,10 +1526,10 @@
       <c r="B15" t="s">
         <v>67</v>
       </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
         <v>20</v>
       </c>
       <c r="E15" t="s">
@@ -1532,13 +1538,13 @@
       <c r="F15" t="s">
         <v>22</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="1">
         <v>24</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>34</v>
       </c>
       <c r="J15" t="s">
@@ -1576,10 +1582,10 @@
       <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
         <v>20</v>
       </c>
       <c r="E16" t="s">
@@ -1588,13 +1594,13 @@
       <c r="F16" t="s">
         <v>22</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H16" s="1">
         <v>28</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" t="s">
         <v>34</v>
       </c>
       <c r="J16" t="s">
@@ -1616,7 +1622,7 @@
         <v>3.66</v>
       </c>
       <c r="P16" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q16" t="s">
         <v>29</v>
@@ -1632,10 +1638,10 @@
       <c r="B17" t="s">
         <v>51</v>
       </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
         <v>20</v>
       </c>
       <c r="E17" t="s">
@@ -1644,13 +1650,13 @@
       <c r="F17" t="s">
         <v>22</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H17" s="1">
         <v>28</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" t="s">
         <v>34</v>
       </c>
       <c r="J17" t="s">
@@ -1688,10 +1694,10 @@
       <c r="B18" t="s">
         <v>53</v>
       </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
         <v>20</v>
       </c>
       <c r="E18" t="s">
@@ -1700,13 +1706,13 @@
       <c r="F18" t="s">
         <v>22</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="1">
         <v>28</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>34</v>
       </c>
       <c r="J18" t="s">
@@ -1744,10 +1750,10 @@
       <c r="B19" t="s">
         <v>43</v>
       </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
         <v>20</v>
       </c>
       <c r="E19" t="s">
@@ -1756,13 +1762,13 @@
       <c r="F19" t="s">
         <v>22</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H19" s="1">
         <v>3</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>24</v>
       </c>
       <c r="J19" t="s">
@@ -1800,10 +1806,10 @@
       <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
         <v>20</v>
       </c>
       <c r="E20" t="s">
@@ -1812,13 +1818,13 @@
       <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="1">
         <v>4</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>24</v>
       </c>
       <c r="J20" t="s">
@@ -1840,7 +1846,7 @@
         <v>41.62</v>
       </c>
       <c r="P20" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q20" t="s">
         <v>29</v>
@@ -1856,10 +1862,10 @@
       <c r="B21" t="s">
         <v>64</v>
       </c>
-      <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
         <v>20</v>
       </c>
       <c r="E21" t="s">
@@ -1868,13 +1874,13 @@
       <c r="F21" t="s">
         <v>22</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H21" s="1">
         <v>5</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>24</v>
       </c>
       <c r="J21" t="s">
@@ -1912,10 +1918,10 @@
       <c r="B22" t="s">
         <v>39</v>
       </c>
-      <c r="C22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
         <v>20</v>
       </c>
       <c r="E22" t="s">
@@ -1924,13 +1930,13 @@
       <c r="F22" t="s">
         <v>22</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H22" s="1">
         <v>6</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" t="s">
         <v>24</v>
       </c>
       <c r="J22" t="s">
@@ -1968,10 +1974,10 @@
       <c r="B23" t="s">
         <v>38</v>
       </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
@@ -1980,13 +1986,13 @@
       <c r="F23" t="s">
         <v>22</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H23" s="1">
         <v>7</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>24</v>
       </c>
       <c r="J23" t="s">
@@ -2024,10 +2030,10 @@
       <c r="B24" t="s">
         <v>62</v>
       </c>
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" t="s">
         <v>20</v>
       </c>
       <c r="E24" t="s">
@@ -2036,13 +2042,13 @@
       <c r="F24" t="s">
         <v>22</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H24" s="1">
         <v>7</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" t="s">
         <v>24</v>
       </c>
       <c r="J24" t="s">
@@ -2080,10 +2086,10 @@
       <c r="B25" t="s">
         <v>47</v>
       </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
         <v>20</v>
       </c>
       <c r="E25" t="s">
@@ -2092,13 +2098,13 @@
       <c r="F25" t="s">
         <v>22</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H25" s="1">
         <v>10</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" t="s">
         <v>24</v>
       </c>
       <c r="J25" t="s">
@@ -2120,7 +2126,7 @@
         <v>8.77</v>
       </c>
       <c r="P25" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q25" t="s">
         <v>29</v>
@@ -2136,10 +2142,10 @@
       <c r="B26" t="s">
         <v>18</v>
       </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
         <v>20</v>
       </c>
       <c r="E26" t="s">
@@ -2148,13 +2154,13 @@
       <c r="F26" t="s">
         <v>22</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="1">
         <v>11</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" t="s">
         <v>24</v>
       </c>
       <c r="J26" t="s">
@@ -2192,10 +2198,10 @@
       <c r="B27" t="s">
         <v>48</v>
       </c>
-      <c r="C27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
@@ -2204,13 +2210,13 @@
       <c r="F27" t="s">
         <v>22</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H27" s="1">
         <v>11</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" t="s">
         <v>24</v>
       </c>
       <c r="J27" t="s">
@@ -2248,10 +2254,10 @@
       <c r="B28" t="s">
         <v>97</v>
       </c>
-      <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
         <v>20</v>
       </c>
       <c r="E28" t="s">
@@ -2260,13 +2266,13 @@
       <c r="F28" t="s">
         <v>99</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H28" s="1">
         <v>13</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" t="s">
         <v>24</v>
       </c>
       <c r="J28" t="s">
@@ -2304,10 +2310,10 @@
       <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
         <v>20</v>
       </c>
       <c r="E29" t="s">
@@ -2316,13 +2322,13 @@
       <c r="F29" t="s">
         <v>22</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H29" s="1">
         <v>13</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" t="s">
         <v>24</v>
       </c>
       <c r="J29" t="s">
@@ -2360,10 +2366,10 @@
       <c r="B30" t="s">
         <v>102</v>
       </c>
-      <c r="C30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
         <v>20</v>
       </c>
       <c r="E30" t="s">
@@ -2372,13 +2378,13 @@
       <c r="F30" t="s">
         <v>99</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H30" s="1">
         <v>14</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" t="s">
         <v>24</v>
       </c>
       <c r="J30" t="s">
@@ -2413,10 +2419,10 @@
       <c r="B31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
         <v>20</v>
       </c>
       <c r="E31" t="s">
@@ -2425,13 +2431,13 @@
       <c r="F31" t="s">
         <v>22</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H31" s="1">
         <v>17</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" t="s">
         <v>24</v>
       </c>
       <c r="J31" t="s">
@@ -2466,10 +2472,10 @@
       <c r="B32" t="s">
         <v>105</v>
       </c>
-      <c r="C32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
         <v>20</v>
       </c>
       <c r="E32" t="s">
@@ -2478,13 +2484,13 @@
       <c r="F32" t="s">
         <v>22</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H32" s="1">
         <v>18</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" t="s">
         <v>24</v>
       </c>
       <c r="J32" t="s">
@@ -2519,10 +2525,10 @@
       <c r="B33" t="s">
         <v>109</v>
       </c>
-      <c r="C33" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
         <v>20</v>
       </c>
       <c r="E33" t="s">
@@ -2531,13 +2537,13 @@
       <c r="F33" t="s">
         <v>99</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H33" s="1">
         <v>19</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" t="s">
         <v>24</v>
       </c>
       <c r="J33" t="s">
@@ -2561,8 +2567,8 @@
       <c r="P33" t="s">
         <v>28</v>
       </c>
-      <c r="R33" t="e">
-        <v>#N/A</v>
+      <c r="R33" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -2572,10 +2578,10 @@
       <c r="B34" t="s">
         <v>107</v>
       </c>
-      <c r="C34" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
         <v>20</v>
       </c>
       <c r="E34" t="s">
@@ -2584,13 +2590,13 @@
       <c r="F34" t="s">
         <v>22</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H34" s="1">
         <v>19</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" t="s">
         <v>24</v>
       </c>
       <c r="J34" t="s">
@@ -2612,7 +2618,7 @@
         <v>4.54</v>
       </c>
       <c r="P34" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R34" t="e">
         <v>#N/A</v>
@@ -2625,10 +2631,10 @@
       <c r="B35" t="s">
         <v>110</v>
       </c>
-      <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
         <v>20</v>
       </c>
       <c r="E35" t="s">
@@ -2637,13 +2643,13 @@
       <c r="F35" t="s">
         <v>99</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H35" s="1">
         <v>20</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" t="s">
         <v>24</v>
       </c>
       <c r="J35" t="s">
@@ -2667,8 +2673,8 @@
       <c r="P35" t="s">
         <v>28</v>
       </c>
-      <c r="R35" t="e">
-        <v>#N/A</v>
+      <c r="R35" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -2678,10 +2684,10 @@
       <c r="B36" t="s">
         <v>111</v>
       </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
         <v>20</v>
       </c>
       <c r="E36" t="s">
@@ -2690,13 +2696,13 @@
       <c r="F36" t="s">
         <v>99</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H36" s="1">
         <v>21</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" t="s">
         <v>24</v>
       </c>
       <c r="J36" t="s">
@@ -2720,8 +2726,8 @@
       <c r="P36" t="s">
         <v>112</v>
       </c>
-      <c r="R36" t="e">
-        <v>#N/A</v>
+      <c r="R36" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -2731,10 +2737,10 @@
       <c r="B37" t="s">
         <v>113</v>
       </c>
-      <c r="C37" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
         <v>20</v>
       </c>
       <c r="E37" t="s">
@@ -2743,13 +2749,13 @@
       <c r="F37" t="s">
         <v>99</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H37" s="1">
         <v>21</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" t="s">
         <v>24</v>
       </c>
       <c r="J37" t="s">
@@ -2773,8 +2779,8 @@
       <c r="P37" t="s">
         <v>56</v>
       </c>
-      <c r="R37" t="e">
-        <v>#N/A</v>
+      <c r="R37" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -2784,10 +2790,10 @@
       <c r="B38" t="s">
         <v>114</v>
       </c>
-      <c r="C38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
         <v>20</v>
       </c>
       <c r="E38" t="s">
@@ -2796,13 +2802,13 @@
       <c r="F38" t="s">
         <v>99</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H38" s="1">
         <v>21</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" t="s">
         <v>24</v>
       </c>
       <c r="J38" t="s">
@@ -2826,8 +2832,8 @@
       <c r="P38" t="s">
         <v>28</v>
       </c>
-      <c r="R38" t="e">
-        <v>#N/A</v>
+      <c r="R38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -2837,10 +2843,10 @@
       <c r="B39" t="s">
         <v>115</v>
       </c>
-      <c r="C39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
         <v>20</v>
       </c>
       <c r="E39" t="s">
@@ -2849,13 +2855,13 @@
       <c r="F39" t="s">
         <v>99</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H39" s="1">
         <v>21</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" t="s">
         <v>24</v>
       </c>
       <c r="J39" t="s">
@@ -2890,10 +2896,10 @@
       <c r="B40" t="s">
         <v>117</v>
       </c>
-      <c r="C40" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
         <v>20</v>
       </c>
       <c r="E40" t="s">
@@ -2902,13 +2908,13 @@
       <c r="F40" t="s">
         <v>99</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H40" s="1">
         <v>21</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" t="s">
         <v>24</v>
       </c>
       <c r="J40" t="s">
@@ -2930,7 +2936,7 @@
         <v>19.47</v>
       </c>
       <c r="P40" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="R40" t="e">
         <v>#N/A</v>
@@ -2943,10 +2949,10 @@
       <c r="B41" t="s">
         <v>118</v>
       </c>
-      <c r="C41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
         <v>20</v>
       </c>
       <c r="E41" t="s">
@@ -2955,13 +2961,13 @@
       <c r="F41" t="s">
         <v>99</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H41" s="1">
         <v>21</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" t="s">
         <v>24</v>
       </c>
       <c r="J41" t="s">
@@ -2985,8 +2991,8 @@
       <c r="P41" t="s">
         <v>36</v>
       </c>
-      <c r="R41" t="e">
-        <v>#N/A</v>
+      <c r="R41" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -2996,10 +3002,10 @@
       <c r="B42" t="s">
         <v>119</v>
       </c>
-      <c r="C42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
         <v>20</v>
       </c>
       <c r="E42" t="s">
@@ -3008,13 +3014,13 @@
       <c r="F42" t="s">
         <v>22</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H42" s="1">
         <v>21</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" t="s">
         <v>24</v>
       </c>
       <c r="J42" t="s">
@@ -3039,6 +3045,59 @@
         <v>28</v>
       </c>
       <c r="R42" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H43" s="1">
+        <v>24</v>
+      </c>
+      <c r="I43" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43">
+        <v>46258</v>
+      </c>
+      <c r="M43">
+        <v>610104</v>
+      </c>
+      <c r="N43" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="P43" t="s">
+        <v>28</v>
+      </c>
+      <c r="R43" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3409,31 +3468,31 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>164.92499999999998</v>
+        <v>241.82899999999998</v>
       </c>
       <c r="E10">
-        <v>198.66729999999998</v>
+        <v>233.8639</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H10">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I10">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="J10">
-        <v>1.1333333333333333</v>
+        <v>1.0933333333333333</v>
       </c>
       <c r="K10">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L10">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -3450,28 +3509,28 @@
         <v>86</v>
       </c>
       <c r="E11">
-        <v>201.11429999999999</v>
+        <v>244.2174</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G11">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H11">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I11">
-        <v>0.92500000000000004</v>
+        <v>0.82</v>
       </c>
       <c r="J11">
-        <v>0.91666666666666663</v>
+        <v>0.84</v>
       </c>
       <c r="K11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L11">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -3488,28 +3547,28 @@
         <v>86</v>
       </c>
       <c r="E12">
-        <v>168.17070000000001</v>
+        <v>196.87350000000001</v>
       </c>
       <c r="F12">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G12">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I12">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="J12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="K12">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L12">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3600,15 +3659,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -3869,6 +3919,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3881,15 +3940,30 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCD2A909-53DD-4636-B6FE-381AEBE261B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCD2A909-53DD-4636-B6FE-381AEBE261B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82DE1B4F-07C8-40A4-B813-D7F37EB34D75}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B04468-8681-48F8-A749-FFC5F0DD0D1D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="Rotas" sheetId="3" r:id="rId2"/>
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$R$43</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="128">
   <si>
     <t>Usuário</t>
   </si>
@@ -404,6 +407,24 @@
   </si>
   <si>
     <t>GENI NATALIA DA SILVA</t>
+  </si>
+  <si>
+    <t>CNPJ BAIXADO OU INATIVO NA RF</t>
+  </si>
+  <si>
+    <t>ROSILENE ALVES DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>INELEGÍVEL CONCORRÊNCIA RETORNO 90 DIAS</t>
+  </si>
+  <si>
+    <t>METAIS SOUZA RESENDE LTDA</t>
+  </si>
+  <si>
+    <t>KATIA CILENE PEREIRA AGUILAR</t>
+  </si>
+  <si>
+    <t>GERSON FEREIRA DE CARVALHO</t>
   </si>
 </sst>
 </file>
@@ -445,9 +466,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,11 +750,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -757,7 +781,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -813,7 +837,7 @@
       <c r="G2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>2</v>
       </c>
       <c r="I2" t="s">
@@ -869,7 +893,7 @@
       <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>2</v>
       </c>
       <c r="I3" t="s">
@@ -925,7 +949,7 @@
       <c r="G4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>2</v>
       </c>
       <c r="I4" t="s">
@@ -981,7 +1005,7 @@
       <c r="G5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>6</v>
       </c>
       <c r="I5" t="s">
@@ -1037,7 +1061,7 @@
       <c r="G6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>7</v>
       </c>
       <c r="I6" t="s">
@@ -1093,7 +1117,7 @@
       <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>8</v>
       </c>
       <c r="I7" t="s">
@@ -1149,7 +1173,7 @@
       <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <v>10</v>
       </c>
       <c r="I8" t="s">
@@ -1205,7 +1229,7 @@
       <c r="G9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="2">
         <v>15</v>
       </c>
       <c r="I9" t="s">
@@ -1261,7 +1285,7 @@
       <c r="G10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="2">
         <v>15</v>
       </c>
       <c r="I10" t="s">
@@ -1317,7 +1341,7 @@
       <c r="G11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="2">
         <v>16</v>
       </c>
       <c r="I11" t="s">
@@ -1373,7 +1397,7 @@
       <c r="G12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s">
@@ -1429,7 +1453,7 @@
       <c r="G13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s">
@@ -1485,7 +1509,7 @@
       <c r="G14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="2">
         <v>22</v>
       </c>
       <c r="I14" t="s">
@@ -1541,7 +1565,7 @@
       <c r="G15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="2">
         <v>24</v>
       </c>
       <c r="I15" t="s">
@@ -1597,7 +1621,7 @@
       <c r="G16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="2">
         <v>28</v>
       </c>
       <c r="I16" t="s">
@@ -1653,7 +1677,7 @@
       <c r="G17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="2">
         <v>28</v>
       </c>
       <c r="I17" t="s">
@@ -1709,7 +1733,7 @@
       <c r="G18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="2">
         <v>28</v>
       </c>
       <c r="I18" t="s">
@@ -1765,7 +1789,7 @@
       <c r="G19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="2">
         <v>3</v>
       </c>
       <c r="I19" t="s">
@@ -1821,7 +1845,7 @@
       <c r="G20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="2">
         <v>4</v>
       </c>
       <c r="I20" t="s">
@@ -1877,7 +1901,7 @@
       <c r="G21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="2">
         <v>5</v>
       </c>
       <c r="I21" t="s">
@@ -1933,7 +1957,7 @@
       <c r="G22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="2">
         <v>6</v>
       </c>
       <c r="I22" t="s">
@@ -1989,7 +2013,7 @@
       <c r="G23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="2">
         <v>7</v>
       </c>
       <c r="I23" t="s">
@@ -2045,7 +2069,7 @@
       <c r="G24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="2">
         <v>7</v>
       </c>
       <c r="I24" t="s">
@@ -2101,7 +2125,7 @@
       <c r="G25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="2">
         <v>10</v>
       </c>
       <c r="I25" t="s">
@@ -2157,7 +2181,7 @@
       <c r="G26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="2">
         <v>11</v>
       </c>
       <c r="I26" t="s">
@@ -2213,7 +2237,7 @@
       <c r="G27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="2">
         <v>11</v>
       </c>
       <c r="I27" t="s">
@@ -2269,7 +2293,7 @@
       <c r="G28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="2">
         <v>13</v>
       </c>
       <c r="I28" t="s">
@@ -2325,7 +2349,7 @@
       <c r="G29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="2">
         <v>13</v>
       </c>
       <c r="I29" t="s">
@@ -2381,7 +2405,7 @@
       <c r="G30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="2">
         <v>14</v>
       </c>
       <c r="I30" t="s">
@@ -2407,6 +2431,9 @@
       </c>
       <c r="P30" t="s">
         <v>108</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>29</v>
       </c>
       <c r="R30" t="s">
         <v>26</v>
@@ -2434,7 +2461,7 @@
       <c r="G31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="2">
         <v>17</v>
       </c>
       <c r="I31" t="s">
@@ -2460,6 +2487,9 @@
       </c>
       <c r="P31" t="s">
         <v>36</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>29</v>
       </c>
       <c r="R31" t="s">
         <v>26</v>
@@ -2487,7 +2517,7 @@
       <c r="G32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="2">
         <v>18</v>
       </c>
       <c r="I32" t="s">
@@ -2513,6 +2543,9 @@
       </c>
       <c r="P32" t="s">
         <v>28</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>29</v>
       </c>
       <c r="R32" t="s">
         <v>26</v>
@@ -2540,7 +2573,7 @@
       <c r="G33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33" s="2">
         <v>19</v>
       </c>
       <c r="I33" t="s">
@@ -2566,6 +2599,9 @@
       </c>
       <c r="P33" t="s">
         <v>28</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>29</v>
       </c>
       <c r="R33" t="s">
         <v>26</v>
@@ -2593,7 +2629,7 @@
       <c r="G34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="2">
         <v>19</v>
       </c>
       <c r="I34" t="s">
@@ -2620,8 +2656,11 @@
       <c r="P34" t="s">
         <v>36</v>
       </c>
-      <c r="R34" t="e">
-        <v>#N/A</v>
+      <c r="Q34" t="s">
+        <v>29</v>
+      </c>
+      <c r="R34" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -2646,7 +2685,7 @@
       <c r="G35" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="2">
         <v>20</v>
       </c>
       <c r="I35" t="s">
@@ -2672,6 +2711,9 @@
       </c>
       <c r="P35" t="s">
         <v>28</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>29</v>
       </c>
       <c r="R35" t="s">
         <v>26</v>
@@ -2699,7 +2741,7 @@
       <c r="G36" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="2">
         <v>21</v>
       </c>
       <c r="I36" t="s">
@@ -2725,6 +2767,9 @@
       </c>
       <c r="P36" t="s">
         <v>112</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>122</v>
       </c>
       <c r="R36" t="s">
         <v>26</v>
@@ -2752,7 +2797,7 @@
       <c r="G37" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="2">
         <v>21</v>
       </c>
       <c r="I37" t="s">
@@ -2778,6 +2823,9 @@
       </c>
       <c r="P37" t="s">
         <v>56</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>29</v>
       </c>
       <c r="R37" t="s">
         <v>26</v>
@@ -2805,7 +2853,7 @@
       <c r="G38" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="2">
         <v>21</v>
       </c>
       <c r="I38" t="s">
@@ -2831,6 +2879,9 @@
       </c>
       <c r="P38" t="s">
         <v>28</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>29</v>
       </c>
       <c r="R38" t="s">
         <v>26</v>
@@ -2858,7 +2909,7 @@
       <c r="G39" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="2">
         <v>21</v>
       </c>
       <c r="I39" t="s">
@@ -2880,13 +2931,16 @@
         <v>27</v>
       </c>
       <c r="O39">
-        <v>26.48</v>
+        <v>10.9</v>
       </c>
       <c r="P39" t="s">
-        <v>28</v>
-      </c>
-      <c r="R39" t="e">
-        <v>#N/A</v>
+        <v>36</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>29</v>
+      </c>
+      <c r="R39" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -2911,7 +2965,7 @@
       <c r="G40" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="2">
         <v>21</v>
       </c>
       <c r="I40" t="s">
@@ -2938,8 +2992,11 @@
       <c r="P40" t="s">
         <v>120</v>
       </c>
-      <c r="R40" t="e">
-        <v>#N/A</v>
+      <c r="Q40" t="s">
+        <v>29</v>
+      </c>
+      <c r="R40" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -2964,7 +3021,7 @@
       <c r="G41" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="2">
         <v>21</v>
       </c>
       <c r="I41" t="s">
@@ -2990,6 +3047,9 @@
       </c>
       <c r="P41" t="s">
         <v>36</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>29</v>
       </c>
       <c r="R41" t="s">
         <v>26</v>
@@ -3017,7 +3077,7 @@
       <c r="G42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="2">
         <v>21</v>
       </c>
       <c r="I42" t="s">
@@ -3039,10 +3099,13 @@
         <v>27</v>
       </c>
       <c r="O42">
-        <v>7.06</v>
+        <v>7.15</v>
       </c>
       <c r="P42" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>29</v>
       </c>
       <c r="R42" t="e">
         <v>#N/A</v>
@@ -3070,7 +3133,7 @@
       <c r="G43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="2">
         <v>24</v>
       </c>
       <c r="I43" t="s">
@@ -3095,13 +3158,241 @@
         <v>9.2200000000000006</v>
       </c>
       <c r="P43" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>29</v>
+      </c>
+      <c r="R43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="2">
+        <v>25</v>
+      </c>
+      <c r="I44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" t="s">
+        <v>26</v>
+      </c>
+      <c r="L44">
+        <v>46259</v>
+      </c>
+      <c r="M44">
+        <v>610626</v>
+      </c>
+      <c r="N44" t="s">
+        <v>45</v>
+      </c>
+      <c r="O44">
+        <v>4.63</v>
+      </c>
+      <c r="P44" t="s">
         <v>28</v>
       </c>
-      <c r="R43" t="e">
+      <c r="Q44" t="s">
+        <v>124</v>
+      </c>
+      <c r="R44" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="2">
+        <v>25</v>
+      </c>
+      <c r="I45" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45">
+        <v>46259</v>
+      </c>
+      <c r="M45">
+        <v>605659</v>
+      </c>
+      <c r="N45" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45">
+        <v>20.53</v>
+      </c>
+      <c r="P45" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>29</v>
+      </c>
+      <c r="R45" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H46" s="2">
+        <v>25</v>
+      </c>
+      <c r="I46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46">
+        <v>46259</v>
+      </c>
+      <c r="M46">
+        <v>610910</v>
+      </c>
+      <c r="N46" t="s">
+        <v>27</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>29</v>
+      </c>
+      <c r="R46" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="2">
+        <v>25</v>
+      </c>
+      <c r="I47" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47">
+        <v>46259</v>
+      </c>
+      <c r="M47">
+        <v>610596</v>
+      </c>
+      <c r="N47" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47">
+        <v>4.17</v>
+      </c>
+      <c r="P47" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>29</v>
+      </c>
+      <c r="R47" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:R43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B04468-8681-48F8-A749-FFC5F0DD0D1D}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F81BDD5-EDD8-43F9-81F4-7407F41B422B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$R$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$P$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="131">
   <si>
     <t>Usuário</t>
   </si>
@@ -425,6 +425,15 @@
   </si>
   <si>
     <t>GERSON FEREIRA DE CARVALHO</t>
+  </si>
+  <si>
+    <t>ROBERTA LIMA DE SOUZA</t>
+  </si>
+  <si>
+    <t>JOAO FARLEY PINHEIRO FERREIRA</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
   </si>
 </sst>
 </file>
@@ -466,10 +475,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -750,23 +758,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -775,13 +783,13 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -819,10 +827,10 @@
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
@@ -831,13 +839,13 @@
       <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2" t="s">
@@ -875,10 +883,10 @@
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
@@ -887,13 +895,13 @@
       <c r="E3" t="s">
         <v>32</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" t="s">
@@ -931,10 +939,10 @@
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
@@ -943,13 +951,13 @@
       <c r="E4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" t="s">
@@ -987,10 +995,10 @@
       <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
@@ -999,13 +1007,13 @@
       <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <v>6</v>
       </c>
       <c r="I5" t="s">
@@ -1043,10 +1051,10 @@
       <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
@@ -1055,13 +1063,13 @@
       <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <v>7</v>
       </c>
       <c r="I6" t="s">
@@ -1099,10 +1107,10 @@
       <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
@@ -1111,13 +1119,13 @@
       <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7">
         <v>8</v>
       </c>
       <c r="I7" t="s">
@@ -1155,10 +1163,10 @@
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>50</v>
       </c>
       <c r="D8" t="s">
@@ -1167,13 +1175,13 @@
       <c r="E8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8">
         <v>10</v>
       </c>
       <c r="I8" t="s">
@@ -1211,10 +1219,10 @@
       <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
@@ -1223,13 +1231,13 @@
       <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9">
         <v>15</v>
       </c>
       <c r="I9" t="s">
@@ -1267,10 +1275,10 @@
       <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
@@ -1279,13 +1287,13 @@
       <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10">
         <v>15</v>
       </c>
       <c r="I10" t="s">
@@ -1323,10 +1331,10 @@
       <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11" t="s">
@@ -1335,13 +1343,13 @@
       <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11">
         <v>16</v>
       </c>
       <c r="I11" t="s">
@@ -1379,10 +1387,10 @@
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
@@ -1391,13 +1399,13 @@
       <c r="E12" t="s">
         <v>32</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12">
         <v>20</v>
       </c>
       <c r="I12" t="s">
@@ -1435,10 +1443,10 @@
       <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
@@ -1447,13 +1455,13 @@
       <c r="E13" t="s">
         <v>32</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13">
         <v>21</v>
       </c>
       <c r="I13" t="s">
@@ -1491,10 +1499,10 @@
       <c r="A14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14" t="s">
@@ -1503,13 +1511,13 @@
       <c r="E14" t="s">
         <v>32</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14">
         <v>22</v>
       </c>
       <c r="I14" t="s">
@@ -1547,10 +1555,10 @@
       <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
@@ -1559,13 +1567,13 @@
       <c r="E15" t="s">
         <v>32</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" t="s">
@@ -1603,10 +1611,10 @@
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
@@ -1615,13 +1623,13 @@
       <c r="E16" t="s">
         <v>32</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16">
         <v>28</v>
       </c>
       <c r="I16" t="s">
@@ -1659,10 +1667,10 @@
       <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>19</v>
       </c>
       <c r="D17" t="s">
@@ -1671,13 +1679,13 @@
       <c r="E17" t="s">
         <v>32</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>28</v>
       </c>
       <c r="I17" t="s">
@@ -1715,10 +1723,10 @@
       <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>19</v>
       </c>
       <c r="D18" t="s">
@@ -1727,13 +1735,13 @@
       <c r="E18" t="s">
         <v>32</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18">
         <v>28</v>
       </c>
       <c r="I18" t="s">
@@ -1771,10 +1779,10 @@
       <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>19</v>
       </c>
       <c r="D19" t="s">
@@ -1783,13 +1791,13 @@
       <c r="E19" t="s">
         <v>32</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19">
         <v>3</v>
       </c>
       <c r="I19" t="s">
@@ -1827,10 +1835,10 @@
       <c r="A20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>19</v>
       </c>
       <c r="D20" t="s">
@@ -1839,13 +1847,13 @@
       <c r="E20" t="s">
         <v>32</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20">
         <v>4</v>
       </c>
       <c r="I20" t="s">
@@ -1883,10 +1891,10 @@
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>19</v>
       </c>
       <c r="D21" t="s">
@@ -1895,13 +1903,13 @@
       <c r="E21" t="s">
         <v>32</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21">
         <v>5</v>
       </c>
       <c r="I21" t="s">
@@ -1939,10 +1947,10 @@
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" t="s">
@@ -1951,13 +1959,13 @@
       <c r="E22" t="s">
         <v>32</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22">
         <v>6</v>
       </c>
       <c r="I22" t="s">
@@ -1995,10 +2003,10 @@
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>19</v>
       </c>
       <c r="D23" t="s">
@@ -2007,13 +2015,13 @@
       <c r="E23" t="s">
         <v>32</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23">
         <v>7</v>
       </c>
       <c r="I23" t="s">
@@ -2051,10 +2059,10 @@
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>19</v>
       </c>
       <c r="D24" t="s">
@@ -2063,13 +2071,13 @@
       <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24">
         <v>7</v>
       </c>
       <c r="I24" t="s">
@@ -2107,10 +2115,10 @@
       <c r="A25" t="s">
         <v>30</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>19</v>
       </c>
       <c r="D25" t="s">
@@ -2119,13 +2127,13 @@
       <c r="E25" t="s">
         <v>32</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25">
         <v>10</v>
       </c>
       <c r="I25" t="s">
@@ -2163,10 +2171,10 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>19</v>
       </c>
       <c r="D26" t="s">
@@ -2175,13 +2183,13 @@
       <c r="E26" t="s">
         <v>21</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26">
         <v>11</v>
       </c>
       <c r="I26" t="s">
@@ -2219,10 +2227,10 @@
       <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>19</v>
       </c>
       <c r="D27" t="s">
@@ -2231,13 +2239,13 @@
       <c r="E27" t="s">
         <v>32</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>33</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27">
         <v>11</v>
       </c>
       <c r="I27" t="s">
@@ -2275,10 +2283,10 @@
       <c r="A28" t="s">
         <v>74</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>19</v>
       </c>
       <c r="D28" t="s">
@@ -2287,13 +2295,13 @@
       <c r="E28" t="s">
         <v>98</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>100</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28">
         <v>13</v>
       </c>
       <c r="I28" t="s">
@@ -2331,10 +2339,10 @@
       <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>19</v>
       </c>
       <c r="D29" t="s">
@@ -2343,13 +2351,13 @@
       <c r="E29" t="s">
         <v>32</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>44</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29">
         <v>13</v>
       </c>
       <c r="I29" t="s">
@@ -2387,10 +2395,10 @@
       <c r="A30" t="s">
         <v>74</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>19</v>
       </c>
       <c r="D30" t="s">
@@ -2399,13 +2407,13 @@
       <c r="E30" t="s">
         <v>98</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>100</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30">
         <v>14</v>
       </c>
       <c r="I30" t="s">
@@ -2443,10 +2451,10 @@
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31" t="s">
@@ -2455,13 +2463,13 @@
       <c r="E31" t="s">
         <v>32</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31">
         <v>17</v>
       </c>
       <c r="I31" t="s">
@@ -2499,10 +2507,10 @@
       <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>19</v>
       </c>
       <c r="D32" t="s">
@@ -2511,13 +2519,13 @@
       <c r="E32" t="s">
         <v>32</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32">
         <v>18</v>
       </c>
       <c r="I32" t="s">
@@ -2542,7 +2550,7 @@
         <v>21.24</v>
       </c>
       <c r="P32" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q32" t="s">
         <v>29</v>
@@ -2555,10 +2563,10 @@
       <c r="A33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>19</v>
       </c>
       <c r="D33" t="s">
@@ -2567,13 +2575,13 @@
       <c r="E33" t="s">
         <v>98</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>100</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33">
         <v>19</v>
       </c>
       <c r="I33" t="s">
@@ -2611,10 +2619,10 @@
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>19</v>
       </c>
       <c r="D34" t="s">
@@ -2623,13 +2631,13 @@
       <c r="E34" t="s">
         <v>32</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>44</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34">
         <v>19</v>
       </c>
       <c r="I34" t="s">
@@ -2667,10 +2675,10 @@
       <c r="A35" t="s">
         <v>74</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>19</v>
       </c>
       <c r="D35" t="s">
@@ -2679,13 +2687,13 @@
       <c r="E35" t="s">
         <v>98</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>100</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35">
         <v>20</v>
       </c>
       <c r="I35" t="s">
@@ -2723,10 +2731,10 @@
       <c r="A36" t="s">
         <v>74</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>19</v>
       </c>
       <c r="D36" t="s">
@@ -2735,13 +2743,13 @@
       <c r="E36" t="s">
         <v>98</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36">
         <v>21</v>
       </c>
       <c r="I36" t="s">
@@ -2779,10 +2787,10 @@
       <c r="A37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" t="s">
@@ -2791,13 +2799,13 @@
       <c r="E37" t="s">
         <v>98</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" t="s">
         <v>100</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37">
         <v>21</v>
       </c>
       <c r="I37" t="s">
@@ -2835,10 +2843,10 @@
       <c r="A38" t="s">
         <v>74</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
@@ -2847,13 +2855,13 @@
       <c r="E38" t="s">
         <v>98</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>100</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38">
         <v>21</v>
       </c>
       <c r="I38" t="s">
@@ -2875,10 +2883,10 @@
         <v>27</v>
       </c>
       <c r="O38">
-        <v>2.14</v>
+        <v>3.39</v>
       </c>
       <c r="P38" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q38" t="s">
         <v>29</v>
@@ -2891,10 +2899,10 @@
       <c r="A39" t="s">
         <v>74</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>19</v>
       </c>
       <c r="D39" t="s">
@@ -2903,13 +2911,13 @@
       <c r="E39" t="s">
         <v>98</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" t="s">
         <v>116</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39">
         <v>21</v>
       </c>
       <c r="I39" t="s">
@@ -2947,10 +2955,10 @@
       <c r="A40" t="s">
         <v>74</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>19</v>
       </c>
       <c r="D40" t="s">
@@ -2959,13 +2967,13 @@
       <c r="E40" t="s">
         <v>98</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>100</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40">
         <v>21</v>
       </c>
       <c r="I40" t="s">
@@ -3003,10 +3011,10 @@
       <c r="A41" t="s">
         <v>74</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>19</v>
       </c>
       <c r="D41" t="s">
@@ -3015,13 +3023,13 @@
       <c r="E41" t="s">
         <v>98</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" t="s">
         <v>100</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41">
         <v>21</v>
       </c>
       <c r="I41" t="s">
@@ -3059,10 +3067,10 @@
       <c r="A42" t="s">
         <v>30</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>19</v>
       </c>
       <c r="D42" t="s">
@@ -3071,13 +3079,13 @@
       <c r="E42" t="s">
         <v>32</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42">
         <v>21</v>
       </c>
       <c r="I42" t="s">
@@ -3107,18 +3115,18 @@
       <c r="Q42" t="s">
         <v>29</v>
       </c>
-      <c r="R42" t="e">
-        <v>#N/A</v>
+      <c r="R42" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>30</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>19</v>
       </c>
       <c r="D43" t="s">
@@ -3127,13 +3135,13 @@
       <c r="E43" t="s">
         <v>32</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" t="s">
         <v>33</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43">
         <v>24</v>
       </c>
       <c r="I43" t="s">
@@ -3171,10 +3179,10 @@
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>19</v>
       </c>
       <c r="D44" t="s">
@@ -3183,13 +3191,13 @@
       <c r="E44" t="s">
         <v>21</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44">
         <v>25</v>
       </c>
       <c r="I44" t="s">
@@ -3227,10 +3235,10 @@
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>19</v>
       </c>
       <c r="D45" t="s">
@@ -3239,13 +3247,13 @@
       <c r="E45" t="s">
         <v>21</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45">
         <v>25</v>
       </c>
       <c r="I45" t="s">
@@ -3275,18 +3283,18 @@
       <c r="Q45" t="s">
         <v>29</v>
       </c>
-      <c r="R45" t="e">
-        <v>#N/A</v>
+      <c r="R45" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>30</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>19</v>
       </c>
       <c r="D46" t="s">
@@ -3295,13 +3303,13 @@
       <c r="E46" t="s">
         <v>32</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>44</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46">
         <v>25</v>
       </c>
       <c r="I46" t="s">
@@ -3323,7 +3331,7 @@
         <v>27</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>8.44</v>
       </c>
       <c r="P46" t="s">
         <v>28</v>
@@ -3339,10 +3347,10 @@
       <c r="A47" t="s">
         <v>30</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>19</v>
       </c>
       <c r="D47" t="s">
@@ -3351,13 +3359,13 @@
       <c r="E47" t="s">
         <v>32</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" t="s">
         <v>33</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47">
         <v>25</v>
       </c>
       <c r="I47" t="s">
@@ -3387,19 +3395,131 @@
       <c r="Q47" t="s">
         <v>29</v>
       </c>
-      <c r="R47" t="e">
+      <c r="R47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G48" t="s">
+        <v>100</v>
+      </c>
+      <c r="H48">
+        <v>27</v>
+      </c>
+      <c r="I48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48">
+        <v>46261</v>
+      </c>
+      <c r="M48">
+        <v>611732</v>
+      </c>
+      <c r="N48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O48">
+        <v>10.1</v>
+      </c>
+      <c r="P48" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>29</v>
+      </c>
+      <c r="R48" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49">
+        <v>27</v>
+      </c>
+      <c r="I49" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49">
+        <v>46261</v>
+      </c>
+      <c r="M49">
+        <v>611797</v>
+      </c>
+      <c r="N49" t="s">
+        <v>27</v>
+      </c>
+      <c r="O49">
+        <v>9.85</v>
+      </c>
+      <c r="P49" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>29</v>
+      </c>
+      <c r="R49" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -3860,6 +3980,120 @@
       </c>
       <c r="L12">
         <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>150.65600000000001</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+      <c r="G13">
+        <v>45</v>
+      </c>
+      <c r="H13">
+        <v>13</v>
+      </c>
+      <c r="I13">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="J13">
+        <v>1.0888888888888888</v>
+      </c>
+      <c r="K13">
+        <v>36</v>
+      </c>
+      <c r="L13">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14">
+        <v>205.94839999999999</v>
+      </c>
+      <c r="F14">
+        <v>30</v>
+      </c>
+      <c r="G14">
+        <v>45</v>
+      </c>
+      <c r="H14">
+        <v>30</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1.0444444444444445</v>
+      </c>
+      <c r="K14">
+        <v>17</v>
+      </c>
+      <c r="L14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15">
+        <v>139.89779999999999</v>
+      </c>
+      <c r="F15">
+        <v>30</v>
+      </c>
+      <c r="G15">
+        <v>45</v>
+      </c>
+      <c r="H15">
+        <v>12</v>
+      </c>
+      <c r="I15">
+        <v>0.4</v>
+      </c>
+      <c r="J15">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="K15">
+        <v>27</v>
+      </c>
+      <c r="L15">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -4211,15 +4445,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
@@ -4230,34 +4455,20 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCD2A909-53DD-4636-B6FE-381AEBE261B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4266,4 +4477,12 @@
     <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F81BDD5-EDD8-43F9-81F4-7407F41B422B}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37106C1C-F166-4CF5-9318-8F4F3D76AC80}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$N$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="133">
   <si>
     <t>Usuário</t>
   </si>
@@ -434,6 +434,12 @@
   </si>
   <si>
     <t>Semana 4</t>
+  </si>
+  <si>
+    <t>AGUARDANDO ASSINATURA</t>
+  </si>
+  <si>
+    <t>MARIA EVANILSA MENDONCA MOREIRA</t>
   </si>
 </sst>
 </file>
@@ -758,20 +764,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -780,10 +784,10 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -827,7 +831,7 @@
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>54</v>
       </c>
       <c r="C2" t="s">
@@ -836,10 +840,10 @@
       <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
       <c r="G2" t="s">
@@ -883,7 +887,7 @@
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
@@ -892,10 +896,10 @@
       <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3" t="s">
@@ -939,7 +943,7 @@
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4" t="s">
@@ -948,10 +952,10 @@
       <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
@@ -995,7 +999,7 @@
       <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5" t="s">
@@ -1004,10 +1008,10 @@
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
@@ -1051,7 +1055,7 @@
       <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>37</v>
       </c>
       <c r="C6" t="s">
@@ -1060,10 +1064,10 @@
       <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>22</v>
       </c>
       <c r="G6" t="s">
@@ -1107,7 +1111,7 @@
       <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7" t="s">
@@ -1116,10 +1120,10 @@
       <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>22</v>
       </c>
       <c r="G7" t="s">
@@ -1163,7 +1167,7 @@
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>49</v>
       </c>
       <c r="C8" t="s">
@@ -1172,10 +1176,10 @@
       <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>22</v>
       </c>
       <c r="G8" t="s">
@@ -1219,7 +1223,7 @@
       <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>40</v>
       </c>
       <c r="C9" t="s">
@@ -1228,10 +1232,10 @@
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" t="s">
@@ -1275,7 +1279,7 @@
       <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>66</v>
       </c>
       <c r="C10" t="s">
@@ -1284,10 +1288,10 @@
       <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10" t="s">
@@ -1331,7 +1335,7 @@
       <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>46</v>
       </c>
       <c r="C11" t="s">
@@ -1340,10 +1344,10 @@
       <c r="D11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>22</v>
       </c>
       <c r="G11" t="s">
@@ -1387,7 +1391,7 @@
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>52</v>
       </c>
       <c r="C12" t="s">
@@ -1396,10 +1400,10 @@
       <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>22</v>
       </c>
       <c r="G12" t="s">
@@ -1427,10 +1431,10 @@
         <v>27</v>
       </c>
       <c r="O12">
-        <v>41.75</v>
+        <v>41.35</v>
       </c>
       <c r="P12" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="s">
         <v>29</v>
@@ -1443,7 +1447,7 @@
       <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>63</v>
       </c>
       <c r="C13" t="s">
@@ -1452,10 +1456,10 @@
       <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13" t="s">
@@ -1499,7 +1503,7 @@
       <c r="A14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
@@ -1508,10 +1512,10 @@
       <c r="D14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14" t="s">
@@ -1555,7 +1559,7 @@
       <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>67</v>
       </c>
       <c r="C15" t="s">
@@ -1564,10 +1568,10 @@
       <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>22</v>
       </c>
       <c r="G15" t="s">
@@ -1611,7 +1615,7 @@
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" t="s">
@@ -1620,10 +1624,10 @@
       <c r="D16" t="s">
         <v>20</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>22</v>
       </c>
       <c r="G16" t="s">
@@ -1667,7 +1671,7 @@
       <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>51</v>
       </c>
       <c r="C17" t="s">
@@ -1676,10 +1680,10 @@
       <c r="D17" t="s">
         <v>20</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>22</v>
       </c>
       <c r="G17" t="s">
@@ -1723,7 +1727,7 @@
       <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>53</v>
       </c>
       <c r="C18" t="s">
@@ -1732,10 +1736,10 @@
       <c r="D18" t="s">
         <v>20</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
@@ -1779,7 +1783,7 @@
       <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>43</v>
       </c>
       <c r="C19" t="s">
@@ -1788,10 +1792,10 @@
       <c r="D19" t="s">
         <v>20</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>22</v>
       </c>
       <c r="G19" t="s">
@@ -1835,7 +1839,7 @@
       <c r="A20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20" t="s">
@@ -1844,10 +1848,10 @@
       <c r="D20" t="s">
         <v>20</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>22</v>
       </c>
       <c r="G20" t="s">
@@ -1891,7 +1895,7 @@
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>64</v>
       </c>
       <c r="C21" t="s">
@@ -1900,10 +1904,10 @@
       <c r="D21" t="s">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>22</v>
       </c>
       <c r="G21" t="s">
@@ -1947,7 +1951,7 @@
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>39</v>
       </c>
       <c r="C22" t="s">
@@ -1956,10 +1960,10 @@
       <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>22</v>
       </c>
       <c r="G22" t="s">
@@ -2003,7 +2007,7 @@
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>38</v>
       </c>
       <c r="C23" t="s">
@@ -2012,10 +2016,10 @@
       <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>22</v>
       </c>
       <c r="G23" t="s">
@@ -2059,7 +2063,7 @@
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>62</v>
       </c>
       <c r="C24" t="s">
@@ -2068,10 +2072,10 @@
       <c r="D24" t="s">
         <v>20</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>22</v>
       </c>
       <c r="G24" t="s">
@@ -2115,7 +2119,7 @@
       <c r="A25" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>47</v>
       </c>
       <c r="C25" t="s">
@@ -2124,10 +2128,10 @@
       <c r="D25" t="s">
         <v>20</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>22</v>
       </c>
       <c r="G25" t="s">
@@ -2171,7 +2175,7 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>18</v>
       </c>
       <c r="C26" t="s">
@@ -2180,10 +2184,10 @@
       <c r="D26" t="s">
         <v>20</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>22</v>
       </c>
       <c r="G26" t="s">
@@ -2227,7 +2231,7 @@
       <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
@@ -2236,10 +2240,10 @@
       <c r="D27" t="s">
         <v>20</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>22</v>
       </c>
       <c r="G27" t="s">
@@ -2283,7 +2287,7 @@
       <c r="A28" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>97</v>
       </c>
       <c r="C28" t="s">
@@ -2292,10 +2296,10 @@
       <c r="D28" t="s">
         <v>20</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>99</v>
       </c>
       <c r="G28" t="s">
@@ -2339,7 +2343,7 @@
       <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>101</v>
       </c>
       <c r="C29" t="s">
@@ -2348,10 +2352,10 @@
       <c r="D29" t="s">
         <v>20</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>22</v>
       </c>
       <c r="G29" t="s">
@@ -2395,7 +2399,7 @@
       <c r="A30" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>102</v>
       </c>
       <c r="C30" t="s">
@@ -2404,10 +2408,10 @@
       <c r="D30" t="s">
         <v>20</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>99</v>
       </c>
       <c r="G30" t="s">
@@ -2438,7 +2442,7 @@
         <v>5.13</v>
       </c>
       <c r="P30" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="Q30" t="s">
         <v>29</v>
@@ -2451,7 +2455,7 @@
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>104</v>
       </c>
       <c r="C31" t="s">
@@ -2460,10 +2464,10 @@
       <c r="D31" t="s">
         <v>20</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>22</v>
       </c>
       <c r="G31" t="s">
@@ -2507,7 +2511,7 @@
       <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>105</v>
       </c>
       <c r="C32" t="s">
@@ -2516,10 +2520,10 @@
       <c r="D32" t="s">
         <v>20</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>22</v>
       </c>
       <c r="G32" t="s">
@@ -2563,7 +2567,7 @@
       <c r="A33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
@@ -2572,10 +2576,10 @@
       <c r="D33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" t="s">
         <v>99</v>
       </c>
       <c r="G33" t="s">
@@ -2603,10 +2607,10 @@
         <v>27</v>
       </c>
       <c r="O33">
-        <v>2.67</v>
+        <v>3.73</v>
       </c>
       <c r="P33" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q33" t="s">
         <v>29</v>
@@ -2619,7 +2623,7 @@
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>107</v>
       </c>
       <c r="C34" t="s">
@@ -2628,10 +2632,10 @@
       <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" t="s">
         <v>22</v>
       </c>
       <c r="G34" t="s">
@@ -2675,7 +2679,7 @@
       <c r="A35" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>110</v>
       </c>
       <c r="C35" t="s">
@@ -2684,10 +2688,10 @@
       <c r="D35" t="s">
         <v>20</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" t="s">
         <v>99</v>
       </c>
       <c r="G35" t="s">
@@ -2731,7 +2735,7 @@
       <c r="A36" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>111</v>
       </c>
       <c r="C36" t="s">
@@ -2740,10 +2744,10 @@
       <c r="D36" t="s">
         <v>20</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" t="s">
         <v>99</v>
       </c>
       <c r="G36" t="s">
@@ -2787,7 +2791,7 @@
       <c r="A37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>113</v>
       </c>
       <c r="C37" t="s">
@@ -2796,10 +2800,10 @@
       <c r="D37" t="s">
         <v>20</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" t="s">
         <v>99</v>
       </c>
       <c r="G37" t="s">
@@ -2843,7 +2847,7 @@
       <c r="A38" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>114</v>
       </c>
       <c r="C38" t="s">
@@ -2852,10 +2856,10 @@
       <c r="D38" t="s">
         <v>20</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" t="s">
         <v>99</v>
       </c>
       <c r="G38" t="s">
@@ -2899,7 +2903,7 @@
       <c r="A39" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>115</v>
       </c>
       <c r="C39" t="s">
@@ -2908,10 +2912,10 @@
       <c r="D39" t="s">
         <v>20</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" t="s">
         <v>99</v>
       </c>
       <c r="G39" t="s">
@@ -2955,7 +2959,7 @@
       <c r="A40" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>117</v>
       </c>
       <c r="C40" t="s">
@@ -2964,10 +2968,10 @@
       <c r="D40" t="s">
         <v>20</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" t="s">
         <v>99</v>
       </c>
       <c r="G40" t="s">
@@ -3011,7 +3015,7 @@
       <c r="A41" t="s">
         <v>74</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>118</v>
       </c>
       <c r="C41" t="s">
@@ -3020,10 +3024,10 @@
       <c r="D41" t="s">
         <v>20</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" t="s">
         <v>99</v>
       </c>
       <c r="G41" t="s">
@@ -3067,7 +3071,7 @@
       <c r="A42" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>119</v>
       </c>
       <c r="C42" t="s">
@@ -3076,10 +3080,10 @@
       <c r="D42" t="s">
         <v>20</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" t="s">
         <v>22</v>
       </c>
       <c r="G42" t="s">
@@ -3123,7 +3127,7 @@
       <c r="A43" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>121</v>
       </c>
       <c r="C43" t="s">
@@ -3132,10 +3136,10 @@
       <c r="D43" t="s">
         <v>20</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" t="s">
         <v>22</v>
       </c>
       <c r="G43" t="s">
@@ -3179,7 +3183,7 @@
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>123</v>
       </c>
       <c r="C44" t="s">
@@ -3188,10 +3192,10 @@
       <c r="D44" t="s">
         <v>20</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" t="s">
         <v>22</v>
       </c>
       <c r="G44" t="s">
@@ -3235,7 +3239,7 @@
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>125</v>
       </c>
       <c r="C45" t="s">
@@ -3244,10 +3248,10 @@
       <c r="D45" t="s">
         <v>20</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" t="s">
         <v>22</v>
       </c>
       <c r="G45" t="s">
@@ -3291,7 +3295,7 @@
       <c r="A46" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>126</v>
       </c>
       <c r="C46" t="s">
@@ -3300,10 +3304,10 @@
       <c r="D46" t="s">
         <v>20</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" t="s">
         <v>22</v>
       </c>
       <c r="G46" t="s">
@@ -3339,15 +3343,15 @@
       <c r="Q46" t="s">
         <v>29</v>
       </c>
-      <c r="R46" t="e">
-        <v>#N/A</v>
+      <c r="R46" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>127</v>
       </c>
       <c r="C47" t="s">
@@ -3356,10 +3360,10 @@
       <c r="D47" t="s">
         <v>20</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" t="s">
         <v>22</v>
       </c>
       <c r="G47" t="s">
@@ -3403,7 +3407,7 @@
       <c r="A48" t="s">
         <v>74</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>128</v>
       </c>
       <c r="C48" t="s">
@@ -3412,10 +3416,10 @@
       <c r="D48" t="s">
         <v>20</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" t="s">
         <v>99</v>
       </c>
       <c r="G48" t="s">
@@ -3446,20 +3450,20 @@
         <v>10.1</v>
       </c>
       <c r="P48" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q48" t="s">
         <v>29</v>
       </c>
-      <c r="R48" t="e">
-        <v>#N/A</v>
+      <c r="R48" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>30</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>129</v>
       </c>
       <c r="C49" t="s">
@@ -3468,10 +3472,10 @@
       <c r="D49" t="s">
         <v>20</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" t="s">
         <v>22</v>
       </c>
       <c r="G49" t="s">
@@ -3511,8 +3515,64 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F50" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" t="s">
+        <v>100</v>
+      </c>
+      <c r="H50">
+        <v>28</v>
+      </c>
+      <c r="I50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50">
+        <v>46262</v>
+      </c>
+      <c r="M50">
+        <v>612663</v>
+      </c>
+      <c r="N50" t="s">
+        <v>27</v>
+      </c>
+      <c r="O50">
+        <v>2.89</v>
+      </c>
+      <c r="P50" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>29</v>
+      </c>
+      <c r="R50" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3993,31 +4053,31 @@
         <v>30</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>164.92499999999998</v>
       </c>
       <c r="E13">
-        <v>150.65600000000001</v>
+        <v>101.37611</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="G13">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H13">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I13">
-        <v>0.43333333333333335</v>
+        <v>0.31944444444444442</v>
       </c>
       <c r="J13">
-        <v>1.0888888888888888</v>
+        <v>1.0833333333333333</v>
       </c>
       <c r="K13">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L13">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -4034,28 +4094,28 @@
         <v>86</v>
       </c>
       <c r="E14">
-        <v>205.94839999999999</v>
+        <v>30.796590000000002</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="G14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H14">
         <v>30</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0.379746835443038</v>
       </c>
       <c r="J14">
-        <v>1.0444444444444445</v>
+        <v>0.95</v>
       </c>
       <c r="K14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="L14">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -4072,28 +4132,28 @@
         <v>86</v>
       </c>
       <c r="E15">
-        <v>139.89779999999999</v>
+        <v>24.521529999999998</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="G15">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H15">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I15">
-        <v>0.4</v>
+        <v>0.24358974358974358</v>
       </c>
       <c r="J15">
         <v>0.8666666666666667</v>
       </c>
       <c r="K15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L15">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -4445,6 +4505,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
@@ -4455,20 +4524,34 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4477,12 +4560,4 @@
     <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37106C1C-F166-4CF5-9318-8F4F3D76AC80}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684501D3-E894-4776-AEF0-4D375AC0655D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$N$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="133">
   <si>
     <t>Usuário</t>
   </si>
@@ -367,9 +367,6 @@
     <t>JORGE ANTONIO DINIZ</t>
   </si>
   <si>
-    <t>AJUSTE DE DOCUMENTAÇÃO</t>
-  </si>
-  <si>
     <t>CARLOS PEREIRA DA SILVA</t>
   </si>
   <si>
@@ -436,10 +433,13 @@
     <t>Semana 4</t>
   </si>
   <si>
-    <t>AGUARDANDO ASSINATURA</t>
-  </si>
-  <si>
     <t>MARIA EVANILSA MENDONCA MOREIRA</t>
+  </si>
+  <si>
+    <t>ADINOZETE ALVES DA SILVA</t>
+  </si>
+  <si>
+    <t>SEP</t>
   </si>
 </sst>
 </file>
@@ -764,11 +764,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -781,10 +782,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -805,7 +806,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -837,10 +838,10 @@
       <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
       <c r="F2" t="s">
@@ -861,7 +862,7 @@
       <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>46205</v>
       </c>
       <c r="M2">
@@ -893,10 +894,10 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>32</v>
       </c>
       <c r="F3" t="s">
@@ -917,7 +918,7 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>46205</v>
       </c>
       <c r="M3">
@@ -949,10 +950,10 @@
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>32</v>
       </c>
       <c r="F4" t="s">
@@ -973,7 +974,7 @@
       <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>46205</v>
       </c>
       <c r="M4">
@@ -1005,10 +1006,10 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>32</v>
       </c>
       <c r="F5" t="s">
@@ -1029,7 +1030,7 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>46209</v>
       </c>
       <c r="M5">
@@ -1042,7 +1043,7 @@
         <v>7.85</v>
       </c>
       <c r="P5" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="s">
         <v>29</v>
@@ -1061,10 +1062,10 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>32</v>
       </c>
       <c r="F6" t="s">
@@ -1085,7 +1086,7 @@
       <c r="K6" t="s">
         <v>26</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>46210</v>
       </c>
       <c r="M6">
@@ -1098,7 +1099,7 @@
         <v>67.37</v>
       </c>
       <c r="P6" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="s">
         <v>29</v>
@@ -1117,10 +1118,10 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
       <c r="F7" t="s">
@@ -1141,7 +1142,7 @@
       <c r="K7" t="s">
         <v>26</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>46211</v>
       </c>
       <c r="M7">
@@ -1173,10 +1174,10 @@
       <c r="C8" t="s">
         <v>50</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
         <v>32</v>
       </c>
       <c r="F8" t="s">
@@ -1197,7 +1198,7 @@
       <c r="K8" t="s">
         <v>26</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>46213</v>
       </c>
       <c r="M8">
@@ -1229,10 +1230,10 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
       </c>
       <c r="F9" t="s">
@@ -1253,7 +1254,7 @@
       <c r="K9" t="s">
         <v>26</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>46218</v>
       </c>
       <c r="M9">
@@ -1285,10 +1286,10 @@
       <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
       </c>
       <c r="F10" t="s">
@@ -1309,7 +1310,7 @@
       <c r="K10" t="s">
         <v>26</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>46218</v>
       </c>
       <c r="M10">
@@ -1341,10 +1342,10 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
       <c r="F11" t="s">
@@ -1365,7 +1366,7 @@
       <c r="K11" t="s">
         <v>26</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>46219</v>
       </c>
       <c r="M11">
@@ -1397,10 +1398,10 @@
       <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
         <v>32</v>
       </c>
       <c r="F12" t="s">
@@ -1421,20 +1422,20 @@
       <c r="K12" t="s">
         <v>26</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>46223</v>
       </c>
       <c r="M12">
         <v>594209</v>
       </c>
       <c r="N12" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O12">
         <v>41.35</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="Q12" t="s">
         <v>29</v>
@@ -1453,10 +1454,10 @@
       <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
         <v>32</v>
       </c>
       <c r="F13" t="s">
@@ -1477,7 +1478,7 @@
       <c r="K13" t="s">
         <v>26</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>46224</v>
       </c>
       <c r="M13">
@@ -1509,10 +1510,10 @@
       <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
         <v>32</v>
       </c>
       <c r="F14" t="s">
@@ -1533,7 +1534,7 @@
       <c r="K14" t="s">
         <v>26</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>46225</v>
       </c>
       <c r="M14">
@@ -1565,10 +1566,10 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
         <v>32</v>
       </c>
       <c r="F15" t="s">
@@ -1589,7 +1590,7 @@
       <c r="K15" t="s">
         <v>26</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>46227</v>
       </c>
       <c r="M15">
@@ -1621,10 +1622,10 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
         <v>32</v>
       </c>
       <c r="F16" t="s">
@@ -1645,7 +1646,7 @@
       <c r="K16" t="s">
         <v>26</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>46231</v>
       </c>
       <c r="M16">
@@ -1677,10 +1678,10 @@
       <c r="C17" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
         <v>32</v>
       </c>
       <c r="F17" t="s">
@@ -1701,7 +1702,7 @@
       <c r="K17" t="s">
         <v>26</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>46231</v>
       </c>
       <c r="M17">
@@ -1733,10 +1734,10 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="D18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
         <v>32</v>
       </c>
       <c r="F18" t="s">
@@ -1757,7 +1758,7 @@
       <c r="K18" t="s">
         <v>26</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>46231</v>
       </c>
       <c r="M18">
@@ -1789,10 +1790,10 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
         <v>32</v>
       </c>
       <c r="F19" t="s">
@@ -1813,7 +1814,7 @@
       <c r="K19" t="s">
         <v>26</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>46237</v>
       </c>
       <c r="M19">
@@ -1845,10 +1846,10 @@
       <c r="C20" t="s">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
         <v>32</v>
       </c>
       <c r="F20" t="s">
@@ -1869,7 +1870,7 @@
       <c r="K20" t="s">
         <v>26</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>46238</v>
       </c>
       <c r="M20">
@@ -1901,10 +1902,10 @@
       <c r="C21" t="s">
         <v>19</v>
       </c>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
         <v>32</v>
       </c>
       <c r="F21" t="s">
@@ -1925,7 +1926,7 @@
       <c r="K21" t="s">
         <v>26</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>46239</v>
       </c>
       <c r="M21">
@@ -1957,10 +1958,10 @@
       <c r="C22" t="s">
         <v>19</v>
       </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
         <v>32</v>
       </c>
       <c r="F22" t="s">
@@ -1981,7 +1982,7 @@
       <c r="K22" t="s">
         <v>26</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>46240</v>
       </c>
       <c r="M22">
@@ -2013,10 +2014,10 @@
       <c r="C23" t="s">
         <v>19</v>
       </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="D23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
         <v>32</v>
       </c>
       <c r="F23" t="s">
@@ -2037,7 +2038,7 @@
       <c r="K23" t="s">
         <v>26</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>46241</v>
       </c>
       <c r="M23">
@@ -2069,10 +2070,10 @@
       <c r="C24" t="s">
         <v>19</v>
       </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="D24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
         <v>32</v>
       </c>
       <c r="F24" t="s">
@@ -2093,7 +2094,7 @@
       <c r="K24" t="s">
         <v>26</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>46241</v>
       </c>
       <c r="M24">
@@ -2125,10 +2126,10 @@
       <c r="C25" t="s">
         <v>19</v>
       </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="D25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
         <v>32</v>
       </c>
       <c r="F25" t="s">
@@ -2149,7 +2150,7 @@
       <c r="K25" t="s">
         <v>26</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>46244</v>
       </c>
       <c r="M25">
@@ -2181,10 +2182,10 @@
       <c r="C26" t="s">
         <v>19</v>
       </c>
-      <c r="D26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="D26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
         <v>21</v>
       </c>
       <c r="F26" t="s">
@@ -2205,7 +2206,7 @@
       <c r="K26" t="s">
         <v>26</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>46245</v>
       </c>
       <c r="M26">
@@ -2237,10 +2238,10 @@
       <c r="C27" t="s">
         <v>19</v>
       </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="D27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
         <v>32</v>
       </c>
       <c r="F27" t="s">
@@ -2261,7 +2262,7 @@
       <c r="K27" t="s">
         <v>26</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>46245</v>
       </c>
       <c r="M27">
@@ -2293,10 +2294,10 @@
       <c r="C28" t="s">
         <v>19</v>
       </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="D28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
         <v>98</v>
       </c>
       <c r="F28" t="s">
@@ -2317,7 +2318,7 @@
       <c r="K28" t="s">
         <v>26</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>46247</v>
       </c>
       <c r="M28">
@@ -2349,10 +2350,10 @@
       <c r="C29" t="s">
         <v>19</v>
       </c>
-      <c r="D29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="D29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
         <v>32</v>
       </c>
       <c r="F29" t="s">
@@ -2373,7 +2374,7 @@
       <c r="K29" t="s">
         <v>26</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>46247</v>
       </c>
       <c r="M29">
@@ -2405,10 +2406,10 @@
       <c r="C30" t="s">
         <v>19</v>
       </c>
-      <c r="D30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="D30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
         <v>98</v>
       </c>
       <c r="F30" t="s">
@@ -2429,7 +2430,7 @@
       <c r="K30" t="s">
         <v>26</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>46248</v>
       </c>
       <c r="M30">
@@ -2442,7 +2443,7 @@
         <v>5.13</v>
       </c>
       <c r="P30" t="s">
-        <v>131</v>
+        <v>61</v>
       </c>
       <c r="Q30" t="s">
         <v>29</v>
@@ -2461,10 +2462,10 @@
       <c r="C31" t="s">
         <v>19</v>
       </c>
-      <c r="D31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="D31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
         <v>32</v>
       </c>
       <c r="F31" t="s">
@@ -2485,7 +2486,7 @@
       <c r="K31" t="s">
         <v>26</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="1">
         <v>46251</v>
       </c>
       <c r="M31">
@@ -2517,10 +2518,10 @@
       <c r="C32" t="s">
         <v>19</v>
       </c>
-      <c r="D32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="D32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
         <v>32</v>
       </c>
       <c r="F32" t="s">
@@ -2541,7 +2542,7 @@
       <c r="K32" t="s">
         <v>26</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="1">
         <v>46252</v>
       </c>
       <c r="M32">
@@ -2568,15 +2569,15 @@
         <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
       </c>
-      <c r="D33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="D33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
         <v>98</v>
       </c>
       <c r="F33" t="s">
@@ -2597,7 +2598,7 @@
       <c r="K33" t="s">
         <v>26</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="1">
         <v>46253</v>
       </c>
       <c r="M33">
@@ -2629,10 +2630,10 @@
       <c r="C34" t="s">
         <v>19</v>
       </c>
-      <c r="D34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="D34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
         <v>32</v>
       </c>
       <c r="F34" t="s">
@@ -2653,7 +2654,7 @@
       <c r="K34" t="s">
         <v>26</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="1">
         <v>46253</v>
       </c>
       <c r="M34">
@@ -2680,15 +2681,15 @@
         <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
         <v>19</v>
       </c>
-      <c r="D35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="D35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
         <v>98</v>
       </c>
       <c r="F35" t="s">
@@ -2709,7 +2710,7 @@
       <c r="K35" t="s">
         <v>26</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="1">
         <v>46254</v>
       </c>
       <c r="M35">
@@ -2736,15 +2737,15 @@
         <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
         <v>19</v>
       </c>
-      <c r="D36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="D36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
         <v>98</v>
       </c>
       <c r="F36" t="s">
@@ -2765,7 +2766,7 @@
       <c r="K36" t="s">
         <v>26</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="1">
         <v>46255</v>
       </c>
       <c r="M36">
@@ -2778,10 +2779,10 @@
         <v>5.89</v>
       </c>
       <c r="P36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R36" t="s">
         <v>26</v>
@@ -2792,15 +2793,15 @@
         <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
       </c>
-      <c r="D37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="D37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
         <v>98</v>
       </c>
       <c r="F37" t="s">
@@ -2821,7 +2822,7 @@
       <c r="K37" t="s">
         <v>26</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="1">
         <v>46255</v>
       </c>
       <c r="M37">
@@ -2848,15 +2849,15 @@
         <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="D38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="D38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
         <v>98</v>
       </c>
       <c r="F38" t="s">
@@ -2877,7 +2878,7 @@
       <c r="K38" t="s">
         <v>26</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="1">
         <v>46255</v>
       </c>
       <c r="M38">
@@ -2904,22 +2905,22 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
         <v>19</v>
       </c>
-      <c r="D39" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
         <v>98</v>
       </c>
       <c r="F39" t="s">
         <v>99</v>
       </c>
       <c r="G39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H39">
         <v>21</v>
@@ -2933,7 +2934,7 @@
       <c r="K39" t="s">
         <v>26</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="1">
         <v>46255</v>
       </c>
       <c r="M39">
@@ -2960,15 +2961,15 @@
         <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
       </c>
-      <c r="D40" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
         <v>98</v>
       </c>
       <c r="F40" t="s">
@@ -2989,7 +2990,7 @@
       <c r="K40" t="s">
         <v>26</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="1">
         <v>46255</v>
       </c>
       <c r="M40">
@@ -3002,7 +3003,7 @@
         <v>19.47</v>
       </c>
       <c r="P40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q40" t="s">
         <v>29</v>
@@ -3016,15 +3017,15 @@
         <v>74</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
         <v>19</v>
       </c>
-      <c r="D41" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="D41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
         <v>98</v>
       </c>
       <c r="F41" t="s">
@@ -3045,7 +3046,7 @@
       <c r="K41" t="s">
         <v>26</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="1">
         <v>46255</v>
       </c>
       <c r="M41">
@@ -3072,15 +3073,15 @@
         <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="D42" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
         <v>32</v>
       </c>
       <c r="F42" t="s">
@@ -3101,7 +3102,7 @@
       <c r="K42" t="s">
         <v>26</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="1">
         <v>46255</v>
       </c>
       <c r="M42">
@@ -3128,15 +3129,15 @@
         <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s">
         <v>19</v>
       </c>
-      <c r="D43" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="D43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
         <v>32</v>
       </c>
       <c r="F43" t="s">
@@ -3157,7 +3158,7 @@
       <c r="K43" t="s">
         <v>26</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="1">
         <v>46258</v>
       </c>
       <c r="M43">
@@ -3184,15 +3185,15 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s">
         <v>19</v>
       </c>
-      <c r="D44" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
         <v>21</v>
       </c>
       <c r="F44" t="s">
@@ -3213,7 +3214,7 @@
       <c r="K44" t="s">
         <v>26</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="1">
         <v>46259</v>
       </c>
       <c r="M44">
@@ -3229,7 +3230,7 @@
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R44" t="e">
         <v>#N/A</v>
@@ -3240,15 +3241,15 @@
         <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s">
         <v>19</v>
       </c>
-      <c r="D45" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="D45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
         <v>21</v>
       </c>
       <c r="F45" t="s">
@@ -3269,7 +3270,7 @@
       <c r="K45" t="s">
         <v>26</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="1">
         <v>46259</v>
       </c>
       <c r="M45">
@@ -3296,15 +3297,15 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>19</v>
       </c>
-      <c r="D46" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="D46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="s">
         <v>32</v>
       </c>
       <c r="F46" t="s">
@@ -3325,7 +3326,7 @@
       <c r="K46" t="s">
         <v>26</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="1">
         <v>46259</v>
       </c>
       <c r="M46">
@@ -3352,15 +3353,15 @@
         <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
         <v>19</v>
       </c>
-      <c r="D47" t="s">
-        <v>20</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="D47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
         <v>32</v>
       </c>
       <c r="F47" t="s">
@@ -3381,7 +3382,7 @@
       <c r="K47" t="s">
         <v>26</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="1">
         <v>46259</v>
       </c>
       <c r="M47">
@@ -3408,15 +3409,15 @@
         <v>74</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="D48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="1" t="s">
+      <c r="D48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
         <v>98</v>
       </c>
       <c r="F48" t="s">
@@ -3437,7 +3438,7 @@
       <c r="K48" t="s">
         <v>26</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="1">
         <v>46261</v>
       </c>
       <c r="M48">
@@ -3464,15 +3465,15 @@
         <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" t="s">
         <v>19</v>
       </c>
-      <c r="D49" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="D49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" t="s">
         <v>32</v>
       </c>
       <c r="F49" t="s">
@@ -3493,7 +3494,7 @@
       <c r="K49" t="s">
         <v>26</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="1">
         <v>46261</v>
       </c>
       <c r="M49">
@@ -3511,8 +3512,8 @@
       <c r="Q49" t="s">
         <v>29</v>
       </c>
-      <c r="R49" t="e">
-        <v>#N/A</v>
+      <c r="R49" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -3520,15 +3521,15 @@
         <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
         <v>19</v>
       </c>
-      <c r="D50" t="s">
-        <v>20</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="D50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
         <v>98</v>
       </c>
       <c r="F50" t="s">
@@ -3549,7 +3550,7 @@
       <c r="K50" t="s">
         <v>26</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="1">
         <v>46262</v>
       </c>
       <c r="M50">
@@ -3567,12 +3568,68 @@
       <c r="Q50" t="s">
         <v>29</v>
       </c>
-      <c r="R50" t="e">
+      <c r="R50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>132</v>
+      </c>
+      <c r="J51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M51">
+        <v>614020</v>
+      </c>
+      <c r="N51" t="s">
+        <v>27</v>
+      </c>
+      <c r="O51">
+        <v>2.33</v>
+      </c>
+      <c r="P51" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>29</v>
+      </c>
+      <c r="R51" t="e">
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4047,37 +4104,37 @@
         <v>46235</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
       </c>
       <c r="D13">
-        <v>164.92499999999998</v>
+        <v>241.82899999999998</v>
       </c>
       <c r="E13">
-        <v>101.37611</v>
+        <v>117.62927000000001</v>
       </c>
       <c r="F13">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G13">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H13">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I13">
-        <v>0.31944444444444442</v>
+        <v>0.6</v>
       </c>
       <c r="J13">
-        <v>1.0833333333333333</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="K13">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L13">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -4085,7 +4142,7 @@
         <v>46235</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
         <v>85</v>
@@ -4094,28 +4151,28 @@
         <v>86</v>
       </c>
       <c r="E14">
-        <v>30.796590000000002</v>
+        <v>37.135120000000001</v>
       </c>
       <c r="F14">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I14">
-        <v>0.379746835443038</v>
+        <v>0.7</v>
       </c>
       <c r="J14">
-        <v>0.95</v>
+        <v>0.85333333333333339</v>
       </c>
       <c r="K14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L14">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -4123,7 +4180,7 @@
         <v>46235</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
         <v>87</v>
@@ -4132,28 +4189,28 @@
         <v>86</v>
       </c>
       <c r="E15">
-        <v>24.521529999999998</v>
+        <v>32.418210000000002</v>
       </c>
       <c r="F15">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G15">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H15">
         <v>19</v>
       </c>
       <c r="I15">
-        <v>0.24358974358974358</v>
+        <v>0.38</v>
       </c>
       <c r="J15">
-        <v>0.8666666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="K15">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L15">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4244,6 +4301,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -4504,27 +4581,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4541,23 +4617,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684501D3-E894-4776-AEF0-4D375AC0655D}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF8BB44E-307D-4A1A-94C6-5A6439E2F26C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$K$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="141">
   <si>
     <t>Usuário</t>
   </si>
@@ -440,6 +440,30 @@
   </si>
   <si>
     <t>SEP</t>
+  </si>
+  <si>
+    <t>AGUARDANDO ASSINATURA</t>
+  </si>
+  <si>
+    <t>VALIDAR DOCUMENTAÇÃO</t>
+  </si>
+  <si>
+    <t>RESTRIÇÕES DE CRÉDITO</t>
+  </si>
+  <si>
+    <t>MIKAEL DE SOUZA LIMA</t>
+  </si>
+  <si>
+    <t>LEANDRO DIOGO PACHECO ARAUJO</t>
+  </si>
+  <si>
+    <t>FERNANDO MIGUEL DA SILVA</t>
+  </si>
+  <si>
+    <t>PABLO JUNIOR GOMES LEAL</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
 </sst>
 </file>
@@ -764,12 +788,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -779,10 +803,10 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -803,7 +827,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -835,10 +859,10 @@
       <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
       <c r="E2" t="s">
@@ -859,7 +883,7 @@
       <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L2" s="1">
@@ -891,10 +915,10 @@
       <c r="B3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
@@ -915,7 +939,7 @@
       <c r="J3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="1">
@@ -947,10 +971,10 @@
       <c r="B4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
@@ -971,7 +995,7 @@
       <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="1">
@@ -1003,10 +1027,10 @@
       <c r="B5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
       <c r="E5" t="s">
@@ -1027,7 +1051,7 @@
       <c r="J5" t="s">
         <v>25</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="1">
@@ -1059,10 +1083,10 @@
       <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
@@ -1083,7 +1107,7 @@
       <c r="J6" t="s">
         <v>25</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L6" s="1">
@@ -1115,10 +1139,10 @@
       <c r="B7" t="s">
         <v>65</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
       <c r="E7" t="s">
@@ -1139,7 +1163,7 @@
       <c r="J7" t="s">
         <v>25</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L7" s="1">
@@ -1171,10 +1195,10 @@
       <c r="B8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8" t="s">
@@ -1195,7 +1219,7 @@
       <c r="J8" t="s">
         <v>25</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="1">
@@ -1227,10 +1251,10 @@
       <c r="B9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
@@ -1251,7 +1275,7 @@
       <c r="J9" t="s">
         <v>25</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="1">
@@ -1283,10 +1307,10 @@
       <c r="B10" t="s">
         <v>66</v>
       </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
         <v>20</v>
       </c>
       <c r="E10" t="s">
@@ -1307,7 +1331,7 @@
       <c r="J10" t="s">
         <v>25</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L10" s="1">
@@ -1339,10 +1363,10 @@
       <c r="B11" t="s">
         <v>46</v>
       </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
         <v>20</v>
       </c>
       <c r="E11" t="s">
@@ -1363,7 +1387,7 @@
       <c r="J11" t="s">
         <v>25</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L11" s="1">
@@ -1395,10 +1419,10 @@
       <c r="B12" t="s">
         <v>52</v>
       </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
         <v>20</v>
       </c>
       <c r="E12" t="s">
@@ -1419,7 +1443,7 @@
       <c r="J12" t="s">
         <v>25</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="1">
@@ -1451,10 +1475,10 @@
       <c r="B13" t="s">
         <v>63</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
@@ -1475,7 +1499,7 @@
       <c r="J13" t="s">
         <v>25</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L13" s="1">
@@ -1507,10 +1531,10 @@
       <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
         <v>20</v>
       </c>
       <c r="E14" t="s">
@@ -1531,7 +1555,7 @@
       <c r="J14" t="s">
         <v>25</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="1">
@@ -1563,10 +1587,10 @@
       <c r="B15" t="s">
         <v>67</v>
       </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
         <v>20</v>
       </c>
       <c r="E15" t="s">
@@ -1587,7 +1611,7 @@
       <c r="J15" t="s">
         <v>25</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L15" s="1">
@@ -1619,10 +1643,10 @@
       <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
         <v>20</v>
       </c>
       <c r="E16" t="s">
@@ -1643,7 +1667,7 @@
       <c r="J16" t="s">
         <v>25</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L16" s="1">
@@ -1675,10 +1699,10 @@
       <c r="B17" t="s">
         <v>51</v>
       </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
         <v>20</v>
       </c>
       <c r="E17" t="s">
@@ -1699,7 +1723,7 @@
       <c r="J17" t="s">
         <v>25</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L17" s="1">
@@ -1731,10 +1755,10 @@
       <c r="B18" t="s">
         <v>53</v>
       </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
         <v>20</v>
       </c>
       <c r="E18" t="s">
@@ -1755,7 +1779,7 @@
       <c r="J18" t="s">
         <v>25</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="1">
@@ -1787,10 +1811,10 @@
       <c r="B19" t="s">
         <v>43</v>
       </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
         <v>20</v>
       </c>
       <c r="E19" t="s">
@@ -1811,7 +1835,7 @@
       <c r="J19" t="s">
         <v>25</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="1">
@@ -1843,10 +1867,10 @@
       <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
         <v>20</v>
       </c>
       <c r="E20" t="s">
@@ -1867,7 +1891,7 @@
       <c r="J20" t="s">
         <v>25</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L20" s="1">
@@ -1883,7 +1907,7 @@
         <v>41.62</v>
       </c>
       <c r="P20" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q20" t="s">
         <v>29</v>
@@ -1899,10 +1923,10 @@
       <c r="B21" t="s">
         <v>64</v>
       </c>
-      <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
         <v>20</v>
       </c>
       <c r="E21" t="s">
@@ -1923,7 +1947,7 @@
       <c r="J21" t="s">
         <v>25</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="1">
@@ -1955,10 +1979,10 @@
       <c r="B22" t="s">
         <v>39</v>
       </c>
-      <c r="C22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
         <v>20</v>
       </c>
       <c r="E22" t="s">
@@ -1979,7 +2003,7 @@
       <c r="J22" t="s">
         <v>25</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L22" s="1">
@@ -2011,10 +2035,10 @@
       <c r="B23" t="s">
         <v>38</v>
       </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
@@ -2035,7 +2059,7 @@
       <c r="J23" t="s">
         <v>25</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L23" s="1">
@@ -2067,10 +2091,10 @@
       <c r="B24" t="s">
         <v>62</v>
       </c>
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" t="s">
         <v>20</v>
       </c>
       <c r="E24" t="s">
@@ -2091,7 +2115,7 @@
       <c r="J24" t="s">
         <v>25</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="1">
@@ -2123,10 +2147,10 @@
       <c r="B25" t="s">
         <v>47</v>
       </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
         <v>20</v>
       </c>
       <c r="E25" t="s">
@@ -2147,7 +2171,7 @@
       <c r="J25" t="s">
         <v>25</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L25" s="1">
@@ -2163,7 +2187,7 @@
         <v>8.77</v>
       </c>
       <c r="P25" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q25" t="s">
         <v>29</v>
@@ -2179,10 +2203,10 @@
       <c r="B26" t="s">
         <v>18</v>
       </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
         <v>20</v>
       </c>
       <c r="E26" t="s">
@@ -2203,7 +2227,7 @@
       <c r="J26" t="s">
         <v>25</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L26" s="1">
@@ -2235,10 +2259,10 @@
       <c r="B27" t="s">
         <v>48</v>
       </c>
-      <c r="C27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
@@ -2259,7 +2283,7 @@
       <c r="J27" t="s">
         <v>25</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L27" s="1">
@@ -2291,10 +2315,10 @@
       <c r="B28" t="s">
         <v>97</v>
       </c>
-      <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
         <v>20</v>
       </c>
       <c r="E28" t="s">
@@ -2315,7 +2339,7 @@
       <c r="J28" t="s">
         <v>25</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L28" s="1">
@@ -2347,10 +2371,10 @@
       <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
         <v>20</v>
       </c>
       <c r="E29" t="s">
@@ -2371,7 +2395,7 @@
       <c r="J29" t="s">
         <v>25</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="1">
@@ -2403,10 +2427,10 @@
       <c r="B30" t="s">
         <v>102</v>
       </c>
-      <c r="C30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
         <v>20</v>
       </c>
       <c r="E30" t="s">
@@ -2427,7 +2451,7 @@
       <c r="J30" t="s">
         <v>25</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L30" s="1">
@@ -2437,7 +2461,7 @@
         <v>606392</v>
       </c>
       <c r="N30" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O30">
         <v>5.13</v>
@@ -2459,10 +2483,10 @@
       <c r="B31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
         <v>20</v>
       </c>
       <c r="E31" t="s">
@@ -2483,7 +2507,7 @@
       <c r="J31" t="s">
         <v>25</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K31" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L31" s="1">
@@ -2515,10 +2539,10 @@
       <c r="B32" t="s">
         <v>105</v>
       </c>
-      <c r="C32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
         <v>20</v>
       </c>
       <c r="E32" t="s">
@@ -2539,7 +2563,7 @@
       <c r="J32" t="s">
         <v>25</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L32" s="1">
@@ -2571,10 +2595,10 @@
       <c r="B33" t="s">
         <v>108</v>
       </c>
-      <c r="C33" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
         <v>20</v>
       </c>
       <c r="E33" t="s">
@@ -2595,7 +2619,7 @@
       <c r="J33" t="s">
         <v>25</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L33" s="1">
@@ -2627,10 +2651,10 @@
       <c r="B34" t="s">
         <v>107</v>
       </c>
-      <c r="C34" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
         <v>20</v>
       </c>
       <c r="E34" t="s">
@@ -2651,7 +2675,7 @@
       <c r="J34" t="s">
         <v>25</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="1">
@@ -2683,10 +2707,10 @@
       <c r="B35" t="s">
         <v>109</v>
       </c>
-      <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
         <v>20</v>
       </c>
       <c r="E35" t="s">
@@ -2707,7 +2731,7 @@
       <c r="J35" t="s">
         <v>25</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L35" s="1">
@@ -2720,10 +2744,10 @@
         <v>27</v>
       </c>
       <c r="O35">
-        <v>9.1</v>
+        <v>20.25</v>
       </c>
       <c r="P35" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="Q35" t="s">
         <v>29</v>
@@ -2739,10 +2763,10 @@
       <c r="B36" t="s">
         <v>110</v>
       </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
         <v>20</v>
       </c>
       <c r="E36" t="s">
@@ -2763,7 +2787,7 @@
       <c r="J36" t="s">
         <v>25</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L36" s="1">
@@ -2795,10 +2819,10 @@
       <c r="B37" t="s">
         <v>112</v>
       </c>
-      <c r="C37" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
         <v>20</v>
       </c>
       <c r="E37" t="s">
@@ -2819,7 +2843,7 @@
       <c r="J37" t="s">
         <v>25</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L37" s="1">
@@ -2851,10 +2875,10 @@
       <c r="B38" t="s">
         <v>113</v>
       </c>
-      <c r="C38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
         <v>20</v>
       </c>
       <c r="E38" t="s">
@@ -2875,7 +2899,7 @@
       <c r="J38" t="s">
         <v>25</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L38" s="1">
@@ -2891,7 +2915,7 @@
         <v>3.39</v>
       </c>
       <c r="P38" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="Q38" t="s">
         <v>29</v>
@@ -2907,10 +2931,10 @@
       <c r="B39" t="s">
         <v>114</v>
       </c>
-      <c r="C39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
         <v>20</v>
       </c>
       <c r="E39" t="s">
@@ -2931,7 +2955,7 @@
       <c r="J39" t="s">
         <v>25</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L39" s="1">
@@ -2947,7 +2971,7 @@
         <v>10.9</v>
       </c>
       <c r="P39" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="Q39" t="s">
         <v>29</v>
@@ -2963,10 +2987,10 @@
       <c r="B40" t="s">
         <v>116</v>
       </c>
-      <c r="C40" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
         <v>20</v>
       </c>
       <c r="E40" t="s">
@@ -2987,7 +3011,7 @@
       <c r="J40" t="s">
         <v>25</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L40" s="1">
@@ -3019,10 +3043,10 @@
       <c r="B41" t="s">
         <v>117</v>
       </c>
-      <c r="C41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
         <v>20</v>
       </c>
       <c r="E41" t="s">
@@ -3043,7 +3067,7 @@
       <c r="J41" t="s">
         <v>25</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L41" s="1">
@@ -3053,7 +3077,7 @@
         <v>605070</v>
       </c>
       <c r="N41" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O41">
         <v>3.19</v>
@@ -3062,7 +3086,7 @@
         <v>36</v>
       </c>
       <c r="Q41" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="R41" t="s">
         <v>26</v>
@@ -3075,10 +3099,10 @@
       <c r="B42" t="s">
         <v>118</v>
       </c>
-      <c r="C42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
         <v>20</v>
       </c>
       <c r="E42" t="s">
@@ -3099,7 +3123,7 @@
       <c r="J42" t="s">
         <v>25</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L42" s="1">
@@ -3131,10 +3155,10 @@
       <c r="B43" t="s">
         <v>120</v>
       </c>
-      <c r="C43" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="1" t="s">
+      <c r="C43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
         <v>20</v>
       </c>
       <c r="E43" t="s">
@@ -3155,7 +3179,7 @@
       <c r="J43" t="s">
         <v>25</v>
       </c>
-      <c r="K43" t="s">
+      <c r="K43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L43" s="1">
@@ -3187,10 +3211,10 @@
       <c r="B44" t="s">
         <v>122</v>
       </c>
-      <c r="C44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" t="s">
         <v>20</v>
       </c>
       <c r="E44" t="s">
@@ -3211,7 +3235,7 @@
       <c r="J44" t="s">
         <v>25</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L44" s="1">
@@ -3243,10 +3267,10 @@
       <c r="B45" t="s">
         <v>124</v>
       </c>
-      <c r="C45" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
         <v>20</v>
       </c>
       <c r="E45" t="s">
@@ -3267,14 +3291,14 @@
       <c r="J45" t="s">
         <v>25</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L45" s="1">
         <v>46259</v>
       </c>
       <c r="M45">
-        <v>605659</v>
+        <v>614542</v>
       </c>
       <c r="N45" t="s">
         <v>27</v>
@@ -3283,7 +3307,7 @@
         <v>20.53</v>
       </c>
       <c r="P45" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q45" t="s">
         <v>29</v>
@@ -3299,10 +3323,10 @@
       <c r="B46" t="s">
         <v>125</v>
       </c>
-      <c r="C46" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
         <v>20</v>
       </c>
       <c r="E46" t="s">
@@ -3323,7 +3347,7 @@
       <c r="J46" t="s">
         <v>25</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L46" s="1">
@@ -3355,10 +3379,10 @@
       <c r="B47" t="s">
         <v>126</v>
       </c>
-      <c r="C47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
         <v>20</v>
       </c>
       <c r="E47" t="s">
@@ -3379,7 +3403,7 @@
       <c r="J47" t="s">
         <v>25</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L47" s="1">
@@ -3411,10 +3435,10 @@
       <c r="B48" t="s">
         <v>127</v>
       </c>
-      <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s">
         <v>20</v>
       </c>
       <c r="E48" t="s">
@@ -3435,7 +3459,7 @@
       <c r="J48" t="s">
         <v>25</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L48" s="1">
@@ -3467,10 +3491,10 @@
       <c r="B49" t="s">
         <v>128</v>
       </c>
-      <c r="C49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
         <v>20</v>
       </c>
       <c r="E49" t="s">
@@ -3491,7 +3515,7 @@
       <c r="J49" t="s">
         <v>25</v>
       </c>
-      <c r="K49" t="s">
+      <c r="K49" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L49" s="1">
@@ -3523,10 +3547,10 @@
       <c r="B50" t="s">
         <v>130</v>
       </c>
-      <c r="C50" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" t="s">
         <v>20</v>
       </c>
       <c r="E50" t="s">
@@ -3547,7 +3571,7 @@
       <c r="J50" t="s">
         <v>25</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L50" s="1">
@@ -3563,7 +3587,7 @@
         <v>2.89</v>
       </c>
       <c r="P50" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q50" t="s">
         <v>29</v>
@@ -3579,10 +3603,10 @@
       <c r="B51" t="s">
         <v>131</v>
       </c>
-      <c r="C51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" t="s">
         <v>20</v>
       </c>
       <c r="E51" t="s">
@@ -3603,7 +3627,7 @@
       <c r="J51" t="s">
         <v>25</v>
       </c>
-      <c r="K51" t="s">
+      <c r="K51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L51" s="1">
@@ -3628,15 +3652,239 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" t="s">
+        <v>98</v>
+      </c>
+      <c r="F52" t="s">
+        <v>99</v>
+      </c>
+      <c r="G52" t="s">
+        <v>100</v>
+      </c>
+      <c r="H52">
+        <v>3</v>
+      </c>
+      <c r="I52" t="s">
+        <v>132</v>
+      </c>
+      <c r="J52" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L52" s="1">
+        <v>46268</v>
+      </c>
+      <c r="M52">
+        <v>615019</v>
+      </c>
+      <c r="N52" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52">
+        <v>7.95</v>
+      </c>
+      <c r="P52" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>29</v>
+      </c>
+      <c r="R52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="I53" t="s">
+        <v>132</v>
+      </c>
+      <c r="J53" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="1">
+        <v>46268</v>
+      </c>
+      <c r="M53">
+        <v>614995</v>
+      </c>
+      <c r="N53" t="s">
+        <v>27</v>
+      </c>
+      <c r="O53">
+        <v>1.91</v>
+      </c>
+      <c r="P53" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>29</v>
+      </c>
+      <c r="R53" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54">
+        <v>4</v>
+      </c>
+      <c r="I54" t="s">
+        <v>132</v>
+      </c>
+      <c r="J54" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" s="1">
+        <v>46269</v>
+      </c>
+      <c r="M54">
+        <v>615314</v>
+      </c>
+      <c r="N54" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54">
+        <v>12.23</v>
+      </c>
+      <c r="P54" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>29</v>
+      </c>
+      <c r="R54" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55" t="s">
+        <v>132</v>
+      </c>
+      <c r="J55" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="1">
+        <v>46269</v>
+      </c>
+      <c r="M55">
+        <v>615322</v>
+      </c>
+      <c r="N55" t="s">
+        <v>27</v>
+      </c>
+      <c r="O55">
+        <v>16.34</v>
+      </c>
+      <c r="P55" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>29</v>
+      </c>
+      <c r="R55" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -4213,6 +4461,120 @@
         <v>66</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>274.47700000000003</v>
+      </c>
+      <c r="E16">
+        <v>93.796340000000001</v>
+      </c>
+      <c r="F16">
+        <v>40</v>
+      </c>
+      <c r="G16">
+        <v>60</v>
+      </c>
+      <c r="H16">
+        <v>18</v>
+      </c>
+      <c r="I16">
+        <v>0.45</v>
+      </c>
+      <c r="J16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K16">
+        <v>48</v>
+      </c>
+      <c r="L16">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17">
+        <v>7.3949699999999998</v>
+      </c>
+      <c r="F17">
+        <v>28</v>
+      </c>
+      <c r="G17">
+        <v>60</v>
+      </c>
+      <c r="H17">
+        <v>36</v>
+      </c>
+      <c r="I17">
+        <v>1.2857142857142858</v>
+      </c>
+      <c r="J17">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="K17">
+        <v>11</v>
+      </c>
+      <c r="L17">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18">
+        <v>43.323610000000002</v>
+      </c>
+      <c r="F18">
+        <v>40</v>
+      </c>
+      <c r="G18">
+        <v>60</v>
+      </c>
+      <c r="H18">
+        <v>14</v>
+      </c>
+      <c r="I18">
+        <v>0.35</v>
+      </c>
+      <c r="J18">
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="K18">
+        <v>32</v>
+      </c>
+      <c r="L18">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -4221,7 +4583,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03D8E35-98BA-491C-80D3-FD8BDE5E2A5E}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -4295,8 +4657,42 @@
         <v>17</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4312,15 +4708,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -4581,6 +4968,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
@@ -4593,14 +4989,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4617,4 +5005,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF8BB44E-307D-4A1A-94C6-5A6439E2F26C}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDDB13DD-D46B-4FF5-B63E-AC1E563D8EAB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$K$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$J$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="144">
   <si>
     <t>Usuário</t>
   </si>
@@ -442,9 +442,6 @@
     <t>SEP</t>
   </si>
   <si>
-    <t>AGUARDANDO ASSINATURA</t>
-  </si>
-  <si>
     <t>VALIDAR DOCUMENTAÇÃO</t>
   </si>
   <si>
@@ -464,6 +461,18 @@
   </si>
   <si>
     <t>Semana 5</t>
+  </si>
+  <si>
+    <t>PADARIA E CONFEITARIA DAVINDE</t>
+  </si>
+  <si>
+    <t>ALONSO DE MELO FEITOSA</t>
+  </si>
+  <si>
+    <t>Paracuru</t>
+  </si>
+  <si>
+    <t>ERICK FERREIRA DOS SANTOS</t>
   </si>
 </sst>
 </file>
@@ -788,22 +797,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -824,13 +833,13 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -856,10 +865,10 @@
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
@@ -880,13 +889,13 @@
       <c r="I2" t="s">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2">
         <v>46205</v>
       </c>
       <c r="M2">
@@ -912,10 +921,10 @@
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
@@ -936,13 +945,13 @@
       <c r="I3" t="s">
         <v>34</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3">
         <v>46205</v>
       </c>
       <c r="M3">
@@ -968,10 +977,10 @@
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
@@ -992,13 +1001,13 @@
       <c r="I4" t="s">
         <v>34</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4">
         <v>46205</v>
       </c>
       <c r="M4">
@@ -1024,10 +1033,10 @@
       <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
@@ -1048,13 +1057,13 @@
       <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5">
         <v>46209</v>
       </c>
       <c r="M5">
@@ -1080,10 +1089,10 @@
       <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
@@ -1104,13 +1113,13 @@
       <c r="I6" t="s">
         <v>34</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6">
         <v>46210</v>
       </c>
       <c r="M6">
@@ -1136,10 +1145,10 @@
       <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
@@ -1160,13 +1169,13 @@
       <c r="I7" t="s">
         <v>34</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7">
         <v>46211</v>
       </c>
       <c r="M7">
@@ -1192,10 +1201,10 @@
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>50</v>
       </c>
       <c r="D8" t="s">
@@ -1216,13 +1225,13 @@
       <c r="I8" t="s">
         <v>34</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8">
         <v>46213</v>
       </c>
       <c r="M8">
@@ -1248,10 +1257,10 @@
       <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
@@ -1272,13 +1281,13 @@
       <c r="I9" t="s">
         <v>34</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9">
         <v>46218</v>
       </c>
       <c r="M9">
@@ -1304,10 +1313,10 @@
       <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
@@ -1328,13 +1337,13 @@
       <c r="I10" t="s">
         <v>34</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10">
         <v>46218</v>
       </c>
       <c r="M10">
@@ -1360,10 +1369,10 @@
       <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11" t="s">
@@ -1384,13 +1393,13 @@
       <c r="I11" t="s">
         <v>34</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11">
         <v>46219</v>
       </c>
       <c r="M11">
@@ -1416,10 +1425,10 @@
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
@@ -1440,13 +1449,13 @@
       <c r="I12" t="s">
         <v>34</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12">
         <v>46223</v>
       </c>
       <c r="M12">
@@ -1472,10 +1481,10 @@
       <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
@@ -1496,13 +1505,13 @@
       <c r="I13" t="s">
         <v>34</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13">
         <v>46224</v>
       </c>
       <c r="M13">
@@ -1528,10 +1537,10 @@
       <c r="A14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14" t="s">
@@ -1552,13 +1561,13 @@
       <c r="I14" t="s">
         <v>34</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14">
         <v>46225</v>
       </c>
       <c r="M14">
@@ -1584,10 +1593,10 @@
       <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
@@ -1608,13 +1617,13 @@
       <c r="I15" t="s">
         <v>34</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15">
         <v>46227</v>
       </c>
       <c r="M15">
@@ -1640,10 +1649,10 @@
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
@@ -1664,13 +1673,13 @@
       <c r="I16" t="s">
         <v>34</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16">
         <v>46231</v>
       </c>
       <c r="M16">
@@ -1696,10 +1705,10 @@
       <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>19</v>
       </c>
       <c r="D17" t="s">
@@ -1720,13 +1729,13 @@
       <c r="I17" t="s">
         <v>34</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17">
         <v>46231</v>
       </c>
       <c r="M17">
@@ -1752,10 +1761,10 @@
       <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>19</v>
       </c>
       <c r="D18" t="s">
@@ -1776,13 +1785,13 @@
       <c r="I18" t="s">
         <v>34</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18">
         <v>46231</v>
       </c>
       <c r="M18">
@@ -1808,10 +1817,10 @@
       <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>19</v>
       </c>
       <c r="D19" t="s">
@@ -1832,13 +1841,13 @@
       <c r="I19" t="s">
         <v>24</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19">
         <v>46237</v>
       </c>
       <c r="M19">
@@ -1864,10 +1873,10 @@
       <c r="A20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>19</v>
       </c>
       <c r="D20" t="s">
@@ -1888,13 +1897,13 @@
       <c r="I20" t="s">
         <v>24</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20">
         <v>46238</v>
       </c>
       <c r="M20">
@@ -1920,10 +1929,10 @@
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>19</v>
       </c>
       <c r="D21" t="s">
@@ -1944,13 +1953,13 @@
       <c r="I21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21">
         <v>46239</v>
       </c>
       <c r="M21">
@@ -1976,10 +1985,10 @@
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" t="s">
@@ -2000,13 +2009,13 @@
       <c r="I22" t="s">
         <v>24</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22">
         <v>46240</v>
       </c>
       <c r="M22">
@@ -2032,10 +2041,10 @@
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>19</v>
       </c>
       <c r="D23" t="s">
@@ -2056,13 +2065,13 @@
       <c r="I23" t="s">
         <v>24</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23">
         <v>46241</v>
       </c>
       <c r="M23">
@@ -2088,10 +2097,10 @@
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>19</v>
       </c>
       <c r="D24" t="s">
@@ -2112,13 +2121,13 @@
       <c r="I24" t="s">
         <v>24</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24">
         <v>46241</v>
       </c>
       <c r="M24">
@@ -2131,7 +2140,7 @@
         <v>6.12</v>
       </c>
       <c r="P24" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q24" t="s">
         <v>29</v>
@@ -2144,10 +2153,10 @@
       <c r="A25" t="s">
         <v>30</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>19</v>
       </c>
       <c r="D25" t="s">
@@ -2168,13 +2177,13 @@
       <c r="I25" t="s">
         <v>24</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25">
         <v>46244</v>
       </c>
       <c r="M25">
@@ -2200,10 +2209,10 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>19</v>
       </c>
       <c r="D26" t="s">
@@ -2224,13 +2233,13 @@
       <c r="I26" t="s">
         <v>24</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26">
         <v>46245</v>
       </c>
       <c r="M26">
@@ -2256,10 +2265,10 @@
       <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>19</v>
       </c>
       <c r="D27" t="s">
@@ -2280,13 +2289,13 @@
       <c r="I27" t="s">
         <v>24</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27">
         <v>46245</v>
       </c>
       <c r="M27">
@@ -2312,10 +2321,10 @@
       <c r="A28" t="s">
         <v>74</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>19</v>
       </c>
       <c r="D28" t="s">
@@ -2336,13 +2345,13 @@
       <c r="I28" t="s">
         <v>24</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L28">
         <v>46247</v>
       </c>
       <c r="M28">
@@ -2368,10 +2377,10 @@
       <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>19</v>
       </c>
       <c r="D29" t="s">
@@ -2392,13 +2401,13 @@
       <c r="I29" t="s">
         <v>24</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29">
         <v>46247</v>
       </c>
       <c r="M29">
@@ -2424,10 +2433,10 @@
       <c r="A30" t="s">
         <v>74</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>19</v>
       </c>
       <c r="D30" t="s">
@@ -2448,13 +2457,13 @@
       <c r="I30" t="s">
         <v>24</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30">
         <v>46248</v>
       </c>
       <c r="M30">
@@ -2480,10 +2489,10 @@
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31" t="s">
@@ -2504,13 +2513,13 @@
       <c r="I31" t="s">
         <v>24</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L31">
         <v>46251</v>
       </c>
       <c r="M31">
@@ -2536,10 +2545,10 @@
       <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>19</v>
       </c>
       <c r="D32" t="s">
@@ -2560,13 +2569,13 @@
       <c r="I32" t="s">
         <v>24</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32">
         <v>46252</v>
       </c>
       <c r="M32">
@@ -2592,10 +2601,10 @@
       <c r="A33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>19</v>
       </c>
       <c r="D33" t="s">
@@ -2616,13 +2625,13 @@
       <c r="I33" t="s">
         <v>24</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L33">
         <v>46253</v>
       </c>
       <c r="M33">
@@ -2648,10 +2657,10 @@
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>19</v>
       </c>
       <c r="D34" t="s">
@@ -2672,13 +2681,13 @@
       <c r="I34" t="s">
         <v>24</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L34">
         <v>46253</v>
       </c>
       <c r="M34">
@@ -2704,10 +2713,10 @@
       <c r="A35" t="s">
         <v>74</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>19</v>
       </c>
       <c r="D35" t="s">
@@ -2728,26 +2737,26 @@
       <c r="I35" t="s">
         <v>24</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35">
         <v>46254</v>
       </c>
       <c r="M35">
         <v>608550</v>
       </c>
       <c r="N35" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O35">
         <v>20.25</v>
       </c>
       <c r="P35" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="Q35" t="s">
         <v>29</v>
@@ -2760,10 +2769,10 @@
       <c r="A36" t="s">
         <v>74</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>19</v>
       </c>
       <c r="D36" t="s">
@@ -2784,13 +2793,13 @@
       <c r="I36" t="s">
         <v>24</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L36">
         <v>46255</v>
       </c>
       <c r="M36">
@@ -2816,10 +2825,10 @@
       <c r="A37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" t="s">
@@ -2840,13 +2849,13 @@
       <c r="I37" t="s">
         <v>24</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L37">
         <v>46255</v>
       </c>
       <c r="M37">
@@ -2872,10 +2881,10 @@
       <c r="A38" t="s">
         <v>74</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
@@ -2896,13 +2905,13 @@
       <c r="I38" t="s">
         <v>24</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L38">
         <v>46255</v>
       </c>
       <c r="M38">
@@ -2915,7 +2924,7 @@
         <v>3.39</v>
       </c>
       <c r="P38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q38" t="s">
         <v>29</v>
@@ -2928,10 +2937,10 @@
       <c r="A39" t="s">
         <v>74</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>19</v>
       </c>
       <c r="D39" t="s">
@@ -2952,13 +2961,13 @@
       <c r="I39" t="s">
         <v>24</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L39">
         <v>46255</v>
       </c>
       <c r="M39">
@@ -2971,7 +2980,7 @@
         <v>10.9</v>
       </c>
       <c r="P39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q39" t="s">
         <v>29</v>
@@ -2984,10 +2993,10 @@
       <c r="A40" t="s">
         <v>74</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>19</v>
       </c>
       <c r="D40" t="s">
@@ -3008,13 +3017,13 @@
       <c r="I40" t="s">
         <v>24</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L40">
         <v>46255</v>
       </c>
       <c r="M40">
@@ -3040,10 +3049,10 @@
       <c r="A41" t="s">
         <v>74</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>19</v>
       </c>
       <c r="D41" t="s">
@@ -3064,13 +3073,13 @@
       <c r="I41" t="s">
         <v>24</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L41">
         <v>46255</v>
       </c>
       <c r="M41">
@@ -3086,7 +3095,7 @@
         <v>36</v>
       </c>
       <c r="Q41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R41" t="s">
         <v>26</v>
@@ -3096,10 +3105,10 @@
       <c r="A42" t="s">
         <v>30</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>19</v>
       </c>
       <c r="D42" t="s">
@@ -3120,13 +3129,13 @@
       <c r="I42" t="s">
         <v>24</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L42">
         <v>46255</v>
       </c>
       <c r="M42">
@@ -3152,10 +3161,10 @@
       <c r="A43" t="s">
         <v>30</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>19</v>
       </c>
       <c r="D43" t="s">
@@ -3176,13 +3185,13 @@
       <c r="I43" t="s">
         <v>24</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L43">
         <v>46258</v>
       </c>
       <c r="M43">
@@ -3208,10 +3217,10 @@
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>19</v>
       </c>
       <c r="D44" t="s">
@@ -3232,13 +3241,13 @@
       <c r="I44" t="s">
         <v>24</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L44">
         <v>46259</v>
       </c>
       <c r="M44">
@@ -3264,10 +3273,10 @@
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>19</v>
       </c>
       <c r="D45" t="s">
@@ -3288,13 +3297,13 @@
       <c r="I45" t="s">
         <v>24</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L45" s="1">
+      <c r="L45">
         <v>46259</v>
       </c>
       <c r="M45">
@@ -3320,10 +3329,10 @@
       <c r="A46" t="s">
         <v>30</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>19</v>
       </c>
       <c r="D46" t="s">
@@ -3344,29 +3353,29 @@
       <c r="I46" t="s">
         <v>24</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L46" s="1">
+      <c r="L46">
         <v>46259</v>
       </c>
       <c r="M46">
         <v>610910</v>
       </c>
       <c r="N46" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O46">
         <v>8.44</v>
       </c>
       <c r="P46" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="Q46" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="R46" t="s">
         <v>26</v>
@@ -3376,10 +3385,10 @@
       <c r="A47" t="s">
         <v>30</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>19</v>
       </c>
       <c r="D47" t="s">
@@ -3400,13 +3409,13 @@
       <c r="I47" t="s">
         <v>24</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L47">
         <v>46259</v>
       </c>
       <c r="M47">
@@ -3419,7 +3428,7 @@
         <v>4.17</v>
       </c>
       <c r="P47" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q47" t="s">
         <v>29</v>
@@ -3432,10 +3441,10 @@
       <c r="A48" t="s">
         <v>74</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>19</v>
       </c>
       <c r="D48" t="s">
@@ -3456,13 +3465,13 @@
       <c r="I48" t="s">
         <v>24</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L48" s="1">
+      <c r="L48">
         <v>46261</v>
       </c>
       <c r="M48">
@@ -3488,10 +3497,10 @@
       <c r="A49" t="s">
         <v>30</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>19</v>
       </c>
       <c r="D49" t="s">
@@ -3512,13 +3521,13 @@
       <c r="I49" t="s">
         <v>24</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L49" s="1">
+      <c r="L49">
         <v>46261</v>
       </c>
       <c r="M49">
@@ -3531,7 +3540,7 @@
         <v>9.85</v>
       </c>
       <c r="P49" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q49" t="s">
         <v>29</v>
@@ -3544,10 +3553,10 @@
       <c r="A50" t="s">
         <v>74</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>19</v>
       </c>
       <c r="D50" t="s">
@@ -3568,13 +3577,13 @@
       <c r="I50" t="s">
         <v>24</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L50">
         <v>46262</v>
       </c>
       <c r="M50">
@@ -3600,10 +3609,10 @@
       <c r="A51" t="s">
         <v>30</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>19</v>
       </c>
       <c r="D51" t="s">
@@ -3624,13 +3633,13 @@
       <c r="I51" t="s">
         <v>132</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L51" s="1">
+      <c r="L51">
         <v>46266</v>
       </c>
       <c r="M51">
@@ -3643,23 +3652,23 @@
         <v>2.33</v>
       </c>
       <c r="P51" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q51" t="s">
         <v>29</v>
       </c>
-      <c r="R51" t="e">
-        <v>#N/A</v>
+      <c r="R51" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>74</v>
       </c>
-      <c r="B52" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="1" t="s">
+      <c r="B52" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" t="s">
         <v>19</v>
       </c>
       <c r="D52" t="s">
@@ -3680,13 +3689,13 @@
       <c r="I52" t="s">
         <v>132</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L52" s="1">
+      <c r="L52">
         <v>46268</v>
       </c>
       <c r="M52">
@@ -3699,7 +3708,7 @@
         <v>7.95</v>
       </c>
       <c r="P52" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="Q52" t="s">
         <v>29</v>
@@ -3712,10 +3721,10 @@
       <c r="A53" t="s">
         <v>30</v>
       </c>
-      <c r="B53" t="s">
-        <v>137</v>
-      </c>
-      <c r="C53" s="1" t="s">
+      <c r="B53" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" t="s">
         <v>19</v>
       </c>
       <c r="D53" t="s">
@@ -3736,13 +3745,13 @@
       <c r="I53" t="s">
         <v>132</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L53" s="1">
+      <c r="L53">
         <v>46268</v>
       </c>
       <c r="M53">
@@ -3755,23 +3764,23 @@
         <v>1.91</v>
       </c>
       <c r="P53" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q53" t="s">
         <v>29</v>
       </c>
-      <c r="R53" t="e">
-        <v>#N/A</v>
+      <c r="R53" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>30</v>
       </c>
-      <c r="B54" t="s">
-        <v>138</v>
-      </c>
-      <c r="C54" s="1" t="s">
+      <c r="B54" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" t="s">
         <v>19</v>
       </c>
       <c r="D54" t="s">
@@ -3792,13 +3801,13 @@
       <c r="I54" t="s">
         <v>132</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L54" s="1">
+      <c r="L54">
         <v>46269</v>
       </c>
       <c r="M54">
@@ -3811,23 +3820,23 @@
         <v>12.23</v>
       </c>
       <c r="P54" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q54" t="s">
         <v>29</v>
       </c>
-      <c r="R54" t="e">
-        <v>#N/A</v>
+      <c r="R54" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>30</v>
       </c>
-      <c r="B55" t="s">
-        <v>139</v>
-      </c>
-      <c r="C55" s="1" t="s">
+      <c r="B55" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
         <v>19</v>
       </c>
       <c r="D55" t="s">
@@ -3848,13 +3857,13 @@
       <c r="I55" t="s">
         <v>132</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L55" s="1">
+      <c r="L55">
         <v>46269</v>
       </c>
       <c r="M55">
@@ -3876,15 +3885,174 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56">
+        <v>4</v>
+      </c>
+      <c r="I56" t="s">
+        <v>132</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56">
+        <v>46269</v>
+      </c>
+      <c r="M56">
+        <v>615654</v>
+      </c>
+      <c r="N56" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56">
+        <v>11.93</v>
+      </c>
+      <c r="P56" t="s">
+        <v>28</v>
+      </c>
+      <c r="R56" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>98</v>
+      </c>
+      <c r="F57" t="s">
+        <v>99</v>
+      </c>
+      <c r="G57" t="s">
+        <v>142</v>
+      </c>
+      <c r="H57">
+        <v>8</v>
+      </c>
+      <c r="I57" t="s">
+        <v>132</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57">
+        <v>46273</v>
+      </c>
+      <c r="M57">
+        <v>616899</v>
+      </c>
+      <c r="N57" t="s">
+        <v>27</v>
+      </c>
+      <c r="O57">
+        <v>6.36</v>
+      </c>
+      <c r="P57" t="s">
+        <v>28</v>
+      </c>
+      <c r="R57" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58">
+        <v>8</v>
+      </c>
+      <c r="I58" t="s">
+        <v>132</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58">
+        <v>46273</v>
+      </c>
+      <c r="M58">
+        <v>616788</v>
+      </c>
+      <c r="N58" t="s">
+        <v>27</v>
+      </c>
+      <c r="O58">
+        <v>32.82</v>
+      </c>
+      <c r="P58" t="s">
+        <v>56</v>
+      </c>
+      <c r="R58" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -4466,13 +4634,13 @@
         <v>46235</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
       <c r="D16">
-        <v>274.47700000000003</v>
+        <v>344.77100000000002</v>
       </c>
       <c r="E16">
         <v>93.796340000000001</v>
@@ -4481,7 +4649,7 @@
         <v>40</v>
       </c>
       <c r="G16">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H16">
         <v>18</v>
@@ -4490,13 +4658,13 @@
         <v>0.45</v>
       </c>
       <c r="J16">
-        <v>1.1000000000000001</v>
+        <v>1.0933333333333333</v>
       </c>
       <c r="K16">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="L16">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -4504,7 +4672,7 @@
         <v>46235</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s">
         <v>85</v>
@@ -4519,22 +4687,22 @@
         <v>28</v>
       </c>
       <c r="G17">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I17">
-        <v>1.2857142857142858</v>
+        <v>1.3571428571428572</v>
       </c>
       <c r="J17">
-        <v>0.78333333333333333</v>
+        <v>0.72</v>
       </c>
       <c r="K17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L17">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -4542,7 +4710,7 @@
         <v>46235</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" t="s">
         <v>87</v>
@@ -4557,23 +4725,26 @@
         <v>40</v>
       </c>
       <c r="G18">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H18">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I18">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="J18">
-        <v>0.76666666666666672</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="K18">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L18">
-        <v>46</v>
-      </c>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4708,6 +4879,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -4968,15 +5148,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
@@ -4989,6 +5160,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5005,12 +5184,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDDB13DD-D46B-4FF5-B63E-AC1E563D8EAB}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00B0B35F-76A1-405D-907C-CE7C1F47FC95}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$I$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="147">
   <si>
     <t>Usuário</t>
   </si>
@@ -442,9 +442,6 @@
     <t>SEP</t>
   </si>
   <si>
-    <t>VALIDAR DOCUMENTAÇÃO</t>
-  </si>
-  <si>
     <t>RESTRIÇÕES DE CRÉDITO</t>
   </si>
   <si>
@@ -473,6 +470,18 @@
   </si>
   <si>
     <t>ERICK FERREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>AGUARDANDO ASSINATURA</t>
+  </si>
+  <si>
+    <t>JONH SANTOS MONTEIRO</t>
+  </si>
+  <si>
+    <t>FABIO DUARTE ROSA</t>
+  </si>
+  <si>
+    <t>Semana1</t>
   </si>
 </sst>
 </file>
@@ -521,7 +530,23 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -797,19 +822,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R58"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -830,13 +854,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -865,7 +889,7 @@
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>54</v>
       </c>
       <c r="C2" t="s">
@@ -886,13 +910,13 @@
       <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
       <c r="L2">
@@ -921,7 +945,7 @@
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
@@ -942,13 +966,13 @@
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
       <c r="L3">
@@ -977,7 +1001,7 @@
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4" t="s">
@@ -998,13 +1022,13 @@
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>26</v>
       </c>
       <c r="L4">
@@ -1033,7 +1057,7 @@
       <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5" t="s">
@@ -1054,13 +1078,13 @@
       <c r="H5">
         <v>6</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>26</v>
       </c>
       <c r="L5">
@@ -1089,7 +1113,7 @@
       <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>37</v>
       </c>
       <c r="C6" t="s">
@@ -1110,13 +1134,13 @@
       <c r="H6">
         <v>7</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>26</v>
       </c>
       <c r="L6">
@@ -1145,7 +1169,7 @@
       <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7" t="s">
@@ -1166,13 +1190,13 @@
       <c r="H7">
         <v>8</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>26</v>
       </c>
       <c r="L7">
@@ -1201,7 +1225,7 @@
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>49</v>
       </c>
       <c r="C8" t="s">
@@ -1222,13 +1246,13 @@
       <c r="H8">
         <v>10</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>26</v>
       </c>
       <c r="L8">
@@ -1257,7 +1281,7 @@
       <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>40</v>
       </c>
       <c r="C9" t="s">
@@ -1278,13 +1302,13 @@
       <c r="H9">
         <v>15</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" t="s">
         <v>26</v>
       </c>
       <c r="L9">
@@ -1313,7 +1337,7 @@
       <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>66</v>
       </c>
       <c r="C10" t="s">
@@ -1334,13 +1358,13 @@
       <c r="H10">
         <v>15</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>26</v>
       </c>
       <c r="L10">
@@ -1369,7 +1393,7 @@
       <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>46</v>
       </c>
       <c r="C11" t="s">
@@ -1390,13 +1414,13 @@
       <c r="H11">
         <v>16</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" t="s">
         <v>26</v>
       </c>
       <c r="L11">
@@ -1425,7 +1449,7 @@
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>52</v>
       </c>
       <c r="C12" t="s">
@@ -1446,13 +1470,13 @@
       <c r="H12">
         <v>20</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" t="s">
         <v>26</v>
       </c>
       <c r="L12">
@@ -1481,7 +1505,7 @@
       <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>63</v>
       </c>
       <c r="C13" t="s">
@@ -1502,13 +1526,13 @@
       <c r="H13">
         <v>21</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" t="s">
         <v>26</v>
       </c>
       <c r="L13">
@@ -1537,7 +1561,7 @@
       <c r="A14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
@@ -1558,13 +1582,13 @@
       <c r="H14">
         <v>22</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" t="s">
         <v>26</v>
       </c>
       <c r="L14">
@@ -1593,7 +1617,7 @@
       <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>67</v>
       </c>
       <c r="C15" t="s">
@@ -1614,13 +1638,13 @@
       <c r="H15">
         <v>24</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" t="s">
         <v>26</v>
       </c>
       <c r="L15">
@@ -1649,7 +1673,7 @@
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" t="s">
@@ -1670,13 +1694,13 @@
       <c r="H16">
         <v>28</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" t="s">
         <v>26</v>
       </c>
       <c r="L16">
@@ -1705,7 +1729,7 @@
       <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>51</v>
       </c>
       <c r="C17" t="s">
@@ -1726,13 +1750,13 @@
       <c r="H17">
         <v>28</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" t="s">
         <v>26</v>
       </c>
       <c r="L17">
@@ -1761,7 +1785,7 @@
       <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>53</v>
       </c>
       <c r="C18" t="s">
@@ -1782,13 +1806,13 @@
       <c r="H18">
         <v>28</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" t="s">
         <v>26</v>
       </c>
       <c r="L18">
@@ -1817,7 +1841,7 @@
       <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>43</v>
       </c>
       <c r="C19" t="s">
@@ -1838,13 +1862,13 @@
       <c r="H19">
         <v>3</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" t="s">
         <v>26</v>
       </c>
       <c r="L19">
@@ -1873,7 +1897,7 @@
       <c r="A20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20" t="s">
@@ -1894,13 +1918,13 @@
       <c r="H20">
         <v>4</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" t="s">
         <v>26</v>
       </c>
       <c r="L20">
@@ -1929,7 +1953,7 @@
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>64</v>
       </c>
       <c r="C21" t="s">
@@ -1950,13 +1974,13 @@
       <c r="H21">
         <v>5</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" t="s">
         <v>26</v>
       </c>
       <c r="L21">
@@ -1985,7 +2009,7 @@
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>39</v>
       </c>
       <c r="C22" t="s">
@@ -2006,13 +2030,13 @@
       <c r="H22">
         <v>6</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" t="s">
         <v>26</v>
       </c>
       <c r="L22">
@@ -2041,7 +2065,7 @@
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>38</v>
       </c>
       <c r="C23" t="s">
@@ -2062,13 +2086,13 @@
       <c r="H23">
         <v>7</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" t="s">
         <v>26</v>
       </c>
       <c r="L23">
@@ -2097,7 +2121,7 @@
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>62</v>
       </c>
       <c r="C24" t="s">
@@ -2118,13 +2142,13 @@
       <c r="H24">
         <v>7</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" t="s">
         <v>26</v>
       </c>
       <c r="L24">
@@ -2153,7 +2177,7 @@
       <c r="A25" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>47</v>
       </c>
       <c r="C25" t="s">
@@ -2174,13 +2198,13 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" t="s">
         <v>26</v>
       </c>
       <c r="L25">
@@ -2209,7 +2233,7 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>18</v>
       </c>
       <c r="C26" t="s">
@@ -2230,13 +2254,13 @@
       <c r="H26">
         <v>11</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" t="s">
         <v>26</v>
       </c>
       <c r="L26">
@@ -2265,7 +2289,7 @@
       <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
@@ -2286,13 +2310,13 @@
       <c r="H27">
         <v>11</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" t="s">
         <v>26</v>
       </c>
       <c r="L27">
@@ -2321,7 +2345,7 @@
       <c r="A28" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>97</v>
       </c>
       <c r="C28" t="s">
@@ -2342,13 +2366,13 @@
       <c r="H28">
         <v>13</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" t="s">
         <v>26</v>
       </c>
       <c r="L28">
@@ -2364,7 +2388,7 @@
         <v>61.58</v>
       </c>
       <c r="P28" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="Q28" t="s">
         <v>29</v>
@@ -2377,7 +2401,7 @@
       <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>101</v>
       </c>
       <c r="C29" t="s">
@@ -2398,13 +2422,13 @@
       <c r="H29">
         <v>13</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" t="s">
         <v>26</v>
       </c>
       <c r="L29">
@@ -2433,7 +2457,7 @@
       <c r="A30" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>102</v>
       </c>
       <c r="C30" t="s">
@@ -2454,13 +2478,13 @@
       <c r="H30">
         <v>14</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" t="s">
         <v>26</v>
       </c>
       <c r="L30">
@@ -2489,7 +2513,7 @@
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>104</v>
       </c>
       <c r="C31" t="s">
@@ -2510,13 +2534,13 @@
       <c r="H31">
         <v>17</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" t="s">
         <v>26</v>
       </c>
       <c r="L31">
@@ -2545,7 +2569,7 @@
       <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>105</v>
       </c>
       <c r="C32" t="s">
@@ -2566,13 +2590,13 @@
       <c r="H32">
         <v>18</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" t="s">
         <v>26</v>
       </c>
       <c r="L32">
@@ -2601,7 +2625,7 @@
       <c r="A33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>108</v>
       </c>
       <c r="C33" t="s">
@@ -2622,13 +2646,13 @@
       <c r="H33">
         <v>19</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" t="s">
         <v>26</v>
       </c>
       <c r="L33">
@@ -2657,7 +2681,7 @@
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>107</v>
       </c>
       <c r="C34" t="s">
@@ -2678,13 +2702,13 @@
       <c r="H34">
         <v>19</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" t="s">
         <v>26</v>
       </c>
       <c r="L34">
@@ -2713,7 +2737,7 @@
       <c r="A35" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
@@ -2734,13 +2758,13 @@
       <c r="H35">
         <v>20</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" t="s">
         <v>26</v>
       </c>
       <c r="L35">
@@ -2769,7 +2793,7 @@
       <c r="A36" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>110</v>
       </c>
       <c r="C36" t="s">
@@ -2790,13 +2814,13 @@
       <c r="H36">
         <v>21</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" t="s">
         <v>26</v>
       </c>
       <c r="L36">
@@ -2825,7 +2849,7 @@
       <c r="A37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>112</v>
       </c>
       <c r="C37" t="s">
@@ -2846,13 +2870,13 @@
       <c r="H37">
         <v>21</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" t="s">
         <v>26</v>
       </c>
       <c r="L37">
@@ -2881,7 +2905,7 @@
       <c r="A38" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>113</v>
       </c>
       <c r="C38" t="s">
@@ -2902,13 +2926,13 @@
       <c r="H38">
         <v>21</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" t="s">
         <v>26</v>
       </c>
       <c r="L38">
@@ -2924,7 +2948,7 @@
         <v>3.39</v>
       </c>
       <c r="P38" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="Q38" t="s">
         <v>29</v>
@@ -2937,7 +2961,7 @@
       <c r="A39" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>114</v>
       </c>
       <c r="C39" t="s">
@@ -2958,13 +2982,13 @@
       <c r="H39">
         <v>21</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" t="s">
         <v>26</v>
       </c>
       <c r="L39">
@@ -2980,7 +3004,7 @@
         <v>10.9</v>
       </c>
       <c r="P39" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="Q39" t="s">
         <v>29</v>
@@ -2993,7 +3017,7 @@
       <c r="A40" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>116</v>
       </c>
       <c r="C40" t="s">
@@ -3014,13 +3038,13 @@
       <c r="H40">
         <v>21</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" t="s">
         <v>26</v>
       </c>
       <c r="L40">
@@ -3049,7 +3073,7 @@
       <c r="A41" t="s">
         <v>74</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>117</v>
       </c>
       <c r="C41" t="s">
@@ -3070,13 +3094,13 @@
       <c r="H41">
         <v>21</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" t="s">
         <v>26</v>
       </c>
       <c r="L41">
@@ -3095,7 +3119,7 @@
         <v>36</v>
       </c>
       <c r="Q41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R41" t="s">
         <v>26</v>
@@ -3105,7 +3129,7 @@
       <c r="A42" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>118</v>
       </c>
       <c r="C42" t="s">
@@ -3126,13 +3150,13 @@
       <c r="H42">
         <v>21</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" t="s">
         <v>26</v>
       </c>
       <c r="L42">
@@ -3161,7 +3185,7 @@
       <c r="A43" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>120</v>
       </c>
       <c r="C43" t="s">
@@ -3182,13 +3206,13 @@
       <c r="H43">
         <v>24</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" t="s">
         <v>26</v>
       </c>
       <c r="L43">
@@ -3217,7 +3241,7 @@
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>122</v>
       </c>
       <c r="C44" t="s">
@@ -3238,13 +3262,13 @@
       <c r="H44">
         <v>25</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="K44" t="s">
         <v>26</v>
       </c>
       <c r="L44">
@@ -3273,7 +3297,7 @@
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>124</v>
       </c>
       <c r="C45" t="s">
@@ -3294,13 +3318,13 @@
       <c r="H45">
         <v>25</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="K45" t="s">
         <v>26</v>
       </c>
       <c r="L45">
@@ -3329,7 +3353,7 @@
       <c r="A46" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>125</v>
       </c>
       <c r="C46" t="s">
@@ -3350,13 +3374,13 @@
       <c r="H46">
         <v>25</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="K46" t="s">
         <v>26</v>
       </c>
       <c r="L46">
@@ -3385,7 +3409,7 @@
       <c r="A47" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>126</v>
       </c>
       <c r="C47" t="s">
@@ -3406,13 +3430,13 @@
       <c r="H47">
         <v>25</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="K47" t="s">
         <v>26</v>
       </c>
       <c r="L47">
@@ -3441,7 +3465,7 @@
       <c r="A48" t="s">
         <v>74</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>127</v>
       </c>
       <c r="C48" t="s">
@@ -3462,13 +3486,13 @@
       <c r="H48">
         <v>27</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K48" t="s">
         <v>26</v>
       </c>
       <c r="L48">
@@ -3497,7 +3521,7 @@
       <c r="A49" t="s">
         <v>30</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>128</v>
       </c>
       <c r="C49" t="s">
@@ -3518,13 +3542,13 @@
       <c r="H49">
         <v>27</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K49" t="s">
         <v>26</v>
       </c>
       <c r="L49">
@@ -3553,7 +3577,7 @@
       <c r="A50" t="s">
         <v>74</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>130</v>
       </c>
       <c r="C50" t="s">
@@ -3574,13 +3598,13 @@
       <c r="H50">
         <v>28</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="K50" t="s">
         <v>26</v>
       </c>
       <c r="L50">
@@ -3609,7 +3633,7 @@
       <c r="A51" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>131</v>
       </c>
       <c r="C51" t="s">
@@ -3630,13 +3654,13 @@
       <c r="H51">
         <v>1</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="1" t="s">
         <v>132</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="K51" t="s">
         <v>26</v>
       </c>
       <c r="L51">
@@ -3665,8 +3689,8 @@
       <c r="A52" t="s">
         <v>74</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>135</v>
+      <c r="B52" t="s">
+        <v>134</v>
       </c>
       <c r="C52" t="s">
         <v>19</v>
@@ -3686,13 +3710,13 @@
       <c r="H52">
         <v>3</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="1" t="s">
         <v>132</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="K52" t="s">
         <v>26</v>
       </c>
       <c r="L52">
@@ -3721,8 +3745,8 @@
       <c r="A53" t="s">
         <v>30</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>136</v>
+      <c r="B53" t="s">
+        <v>135</v>
       </c>
       <c r="C53" t="s">
         <v>19</v>
@@ -3742,13 +3766,13 @@
       <c r="H53">
         <v>3</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="1" t="s">
         <v>132</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="K53" t="s">
         <v>26</v>
       </c>
       <c r="L53">
@@ -3777,8 +3801,8 @@
       <c r="A54" t="s">
         <v>30</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>137</v>
+      <c r="B54" t="s">
+        <v>136</v>
       </c>
       <c r="C54" t="s">
         <v>19</v>
@@ -3798,13 +3822,13 @@
       <c r="H54">
         <v>4</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="1" t="s">
         <v>132</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K54" t="s">
         <v>26</v>
       </c>
       <c r="L54">
@@ -3833,8 +3857,8 @@
       <c r="A55" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>138</v>
+      <c r="B55" t="s">
+        <v>137</v>
       </c>
       <c r="C55" t="s">
         <v>19</v>
@@ -3854,13 +3878,13 @@
       <c r="H55">
         <v>4</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="1" t="s">
         <v>132</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" t="s">
         <v>26</v>
       </c>
       <c r="L55">
@@ -3876,21 +3900,21 @@
         <v>16.34</v>
       </c>
       <c r="P55" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q55" t="s">
         <v>29</v>
       </c>
-      <c r="R55" t="e">
-        <v>#N/A</v>
+      <c r="R55" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>30</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>140</v>
+      <c r="B56" t="s">
+        <v>139</v>
       </c>
       <c r="C56" t="s">
         <v>19</v>
@@ -3910,13 +3934,13 @@
       <c r="H56">
         <v>4</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="1" t="s">
         <v>132</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="K56" t="s">
         <v>26</v>
       </c>
       <c r="L56">
@@ -3932,7 +3956,10 @@
         <v>11.93</v>
       </c>
       <c r="P56" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>29</v>
       </c>
       <c r="R56" t="e">
         <v>#N/A</v>
@@ -3942,8 +3969,8 @@
       <c r="A57" t="s">
         <v>74</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>141</v>
+      <c r="B57" t="s">
+        <v>140</v>
       </c>
       <c r="C57" t="s">
         <v>19</v>
@@ -3958,18 +3985,18 @@
         <v>99</v>
       </c>
       <c r="G57" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H57">
         <v>8</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="1" t="s">
         <v>132</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="K57" t="s">
         <v>26</v>
       </c>
       <c r="L57">
@@ -3986,6 +4013,9 @@
       </c>
       <c r="P57" t="s">
         <v>28</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>29</v>
       </c>
       <c r="R57" t="e">
         <v>#N/A</v>
@@ -3995,8 +4025,8 @@
       <c r="A58" t="s">
         <v>30</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>143</v>
+      <c r="B58" t="s">
+        <v>142</v>
       </c>
       <c r="C58" t="s">
         <v>19</v>
@@ -4016,13 +4046,13 @@
       <c r="H58">
         <v>8</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="1" t="s">
         <v>132</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="K58" t="s">
         <v>26</v>
       </c>
       <c r="L58">
@@ -4040,19 +4070,134 @@
       <c r="P58" t="s">
         <v>56</v>
       </c>
+      <c r="Q58" t="s">
+        <v>29</v>
+      </c>
       <c r="R58" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" t="s">
+        <v>144</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>98</v>
+      </c>
+      <c r="F59" t="s">
+        <v>99</v>
+      </c>
+      <c r="G59" t="s">
+        <v>100</v>
+      </c>
+      <c r="H59">
+        <v>9</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59">
+        <v>46274</v>
+      </c>
+      <c r="M59">
+        <v>617206</v>
+      </c>
+      <c r="N59" t="s">
+        <v>27</v>
+      </c>
+      <c r="O59">
+        <v>21.23</v>
+      </c>
+      <c r="P59" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>29</v>
+      </c>
+      <c r="R59" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60">
+        <v>9</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60">
+        <v>46274</v>
+      </c>
+      <c r="M60">
+        <v>617229</v>
+      </c>
+      <c r="N60" t="s">
+        <v>27</v>
+      </c>
+      <c r="O60">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="P60" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>29</v>
+      </c>
+      <c r="R60" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -4634,7 +4779,7 @@
         <v>46235</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
@@ -4672,7 +4817,7 @@
         <v>46235</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
         <v>85</v>
@@ -4710,7 +4855,7 @@
         <v>46235</v>
       </c>
       <c r="B18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
         <v>87</v>
@@ -4744,7 +4889,121 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
+      <c r="A19" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>25.39207</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19">
+        <v>0.6</v>
+      </c>
+      <c r="J19" t="s">
+        <v>86</v>
+      </c>
+      <c r="K19">
+        <v>11</v>
+      </c>
+      <c r="L19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20">
+        <v>5.8520000000000003</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>10</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>86</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21">
+        <v>44.969430000000003</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>5</v>
+      </c>
+      <c r="I21">
+        <v>0.25</v>
+      </c>
+      <c r="J21" t="s">
+        <v>86</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4868,6 +5127,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
@@ -4876,15 +5144,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5149,20 +5408,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
     <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00B0B35F-76A1-405D-907C-CE7C1F47FC95}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FFACEAB-2B7C-47E6-B2FC-CF30D8192BFE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="149">
   <si>
     <t>Usuário</t>
   </si>
@@ -482,6 +482,12 @@
   </si>
   <si>
     <t>Semana1</t>
+  </si>
+  <si>
+    <t>DECLINE MASSIVO – INATIVAÇÃO VENDEDOR</t>
+  </si>
+  <si>
+    <t>IZABELA IZARIAS</t>
   </si>
 </sst>
 </file>
@@ -530,23 +536,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -822,11 +812,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -851,13 +841,13 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -907,19 +897,19 @@
       <c r="G2" t="s">
         <v>55</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>25</v>
       </c>
       <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>46205</v>
       </c>
       <c r="M2">
@@ -963,19 +953,19 @@
       <c r="G3" t="s">
         <v>55</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>25</v>
       </c>
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>46205</v>
       </c>
       <c r="M3">
@@ -1019,19 +1009,19 @@
       <c r="G4" t="s">
         <v>44</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>25</v>
       </c>
       <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>46205</v>
       </c>
       <c r="M4">
@@ -1075,19 +1065,19 @@
       <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>6</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>25</v>
       </c>
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>46209</v>
       </c>
       <c r="M5">
@@ -1131,19 +1121,19 @@
       <c r="G6" t="s">
         <v>33</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>7</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>25</v>
       </c>
       <c r="K6" t="s">
         <v>26</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>46210</v>
       </c>
       <c r="M6">
@@ -1187,19 +1177,19 @@
       <c r="G7" t="s">
         <v>33</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>25</v>
       </c>
       <c r="K7" t="s">
         <v>26</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>46211</v>
       </c>
       <c r="M7">
@@ -1243,19 +1233,19 @@
       <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>25</v>
       </c>
       <c r="K8" t="s">
         <v>26</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>46213</v>
       </c>
       <c r="M8">
@@ -1299,19 +1289,19 @@
       <c r="G9" t="s">
         <v>41</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>15</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>25</v>
       </c>
       <c r="K9" t="s">
         <v>26</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>46218</v>
       </c>
       <c r="M9">
@@ -1355,19 +1345,19 @@
       <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>25</v>
       </c>
       <c r="K10" t="s">
         <v>26</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>46218</v>
       </c>
       <c r="M10">
@@ -1411,19 +1401,19 @@
       <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" t="s">
         <v>25</v>
       </c>
       <c r="K11" t="s">
         <v>26</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>46219</v>
       </c>
       <c r="M11">
@@ -1467,19 +1457,19 @@
       <c r="G12" t="s">
         <v>44</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>25</v>
       </c>
       <c r="K12" t="s">
         <v>26</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>46223</v>
       </c>
       <c r="M12">
@@ -1523,19 +1513,19 @@
       <c r="G13" t="s">
         <v>33</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>21</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" t="s">
         <v>25</v>
       </c>
       <c r="K13" t="s">
         <v>26</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>46224</v>
       </c>
       <c r="M13">
@@ -1579,19 +1569,19 @@
       <c r="G14" t="s">
         <v>33</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>22</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" t="s">
         <v>25</v>
       </c>
       <c r="K14" t="s">
         <v>26</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>46225</v>
       </c>
       <c r="M14">
@@ -1635,19 +1625,19 @@
       <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" t="s">
         <v>25</v>
       </c>
       <c r="K15" t="s">
         <v>26</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>46227</v>
       </c>
       <c r="M15">
@@ -1691,19 +1681,19 @@
       <c r="G16" t="s">
         <v>33</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>28</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>25</v>
       </c>
       <c r="K16" t="s">
         <v>26</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>46231</v>
       </c>
       <c r="M16">
@@ -1747,19 +1737,19 @@
       <c r="G17" t="s">
         <v>44</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" t="s">
         <v>25</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>46231</v>
       </c>
       <c r="M17">
@@ -1803,19 +1793,19 @@
       <c r="G18" t="s">
         <v>23</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>25</v>
       </c>
       <c r="K18" t="s">
         <v>26</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>46231</v>
       </c>
       <c r="M18">
@@ -1859,19 +1849,19 @@
       <c r="G19" t="s">
         <v>44</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" t="s">
         <v>25</v>
       </c>
       <c r="K19" t="s">
         <v>26</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>46237</v>
       </c>
       <c r="M19">
@@ -1915,19 +1905,19 @@
       <c r="G20" t="s">
         <v>33</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>25</v>
       </c>
       <c r="K20" t="s">
         <v>26</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>46238</v>
       </c>
       <c r="M20">
@@ -1971,19 +1961,19 @@
       <c r="G21" t="s">
         <v>44</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>5</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" t="s">
         <v>25</v>
       </c>
       <c r="K21" t="s">
         <v>26</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>46239</v>
       </c>
       <c r="M21">
@@ -2027,19 +2017,19 @@
       <c r="G22" t="s">
         <v>33</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>6</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" t="s">
         <v>25</v>
       </c>
       <c r="K22" t="s">
         <v>26</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>46240</v>
       </c>
       <c r="M22">
@@ -2083,19 +2073,19 @@
       <c r="G23" t="s">
         <v>33</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>7</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>25</v>
       </c>
       <c r="K23" t="s">
         <v>26</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>46241</v>
       </c>
       <c r="M23">
@@ -2139,19 +2129,19 @@
       <c r="G24" t="s">
         <v>44</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>7</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>25</v>
       </c>
       <c r="K24" t="s">
         <v>26</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>46241</v>
       </c>
       <c r="M24">
@@ -2195,19 +2185,19 @@
       <c r="G25" t="s">
         <v>33</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" t="s">
         <v>25</v>
       </c>
       <c r="K25" t="s">
         <v>26</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>46244</v>
       </c>
       <c r="M25">
@@ -2251,19 +2241,19 @@
       <c r="G26" t="s">
         <v>23</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>11</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" t="s">
         <v>25</v>
       </c>
       <c r="K26" t="s">
         <v>26</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>46245</v>
       </c>
       <c r="M26">
@@ -2307,19 +2297,19 @@
       <c r="G27" t="s">
         <v>33</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>11</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>25</v>
       </c>
       <c r="K27" t="s">
         <v>26</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>46245</v>
       </c>
       <c r="M27">
@@ -2363,19 +2353,19 @@
       <c r="G28" t="s">
         <v>100</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>13</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" t="s">
         <v>25</v>
       </c>
       <c r="K28" t="s">
         <v>26</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>46247</v>
       </c>
       <c r="M28">
@@ -2419,19 +2409,19 @@
       <c r="G29" t="s">
         <v>44</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>13</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" t="s">
         <v>25</v>
       </c>
       <c r="K29" t="s">
         <v>26</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>46247</v>
       </c>
       <c r="M29">
@@ -2475,19 +2465,19 @@
       <c r="G30" t="s">
         <v>100</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>14</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" t="s">
         <v>25</v>
       </c>
       <c r="K30" t="s">
         <v>26</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>46248</v>
       </c>
       <c r="M30">
@@ -2531,19 +2521,19 @@
       <c r="G31" t="s">
         <v>33</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" t="s">
         <v>25</v>
       </c>
       <c r="K31" t="s">
         <v>26</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="1">
         <v>46251</v>
       </c>
       <c r="M31">
@@ -2587,19 +2577,19 @@
       <c r="G32" t="s">
         <v>33</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" t="s">
         <v>25</v>
       </c>
       <c r="K32" t="s">
         <v>26</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="1">
         <v>46252</v>
       </c>
       <c r="M32">
@@ -2643,26 +2633,26 @@
       <c r="G33" t="s">
         <v>100</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>19</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" t="s">
         <v>25</v>
       </c>
       <c r="K33" t="s">
         <v>26</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="1">
         <v>46253</v>
       </c>
       <c r="M33">
         <v>608180</v>
       </c>
       <c r="N33" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O33">
         <v>3.73</v>
@@ -2671,7 +2661,7 @@
         <v>36</v>
       </c>
       <c r="Q33" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="R33" t="s">
         <v>26</v>
@@ -2699,19 +2689,19 @@
       <c r="G34" t="s">
         <v>44</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>19</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" t="s">
         <v>25</v>
       </c>
       <c r="K34" t="s">
         <v>26</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="1">
         <v>46253</v>
       </c>
       <c r="M34">
@@ -2755,19 +2745,19 @@
       <c r="G35" t="s">
         <v>100</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>20</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" t="s">
         <v>25</v>
       </c>
       <c r="K35" t="s">
         <v>26</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="1">
         <v>46254</v>
       </c>
       <c r="M35">
@@ -2811,19 +2801,19 @@
       <c r="G36" t="s">
         <v>100</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
         <v>21</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" t="s">
         <v>25</v>
       </c>
       <c r="K36" t="s">
         <v>26</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="1">
         <v>46255</v>
       </c>
       <c r="M36">
@@ -2867,26 +2857,26 @@
       <c r="G37" t="s">
         <v>100</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>21</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" t="s">
         <v>25</v>
       </c>
       <c r="K37" t="s">
         <v>26</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="1">
         <v>46255</v>
       </c>
       <c r="M37">
         <v>557624</v>
       </c>
       <c r="N37" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -2895,7 +2885,7 @@
         <v>56</v>
       </c>
       <c r="Q37" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="R37" t="s">
         <v>26</v>
@@ -2923,19 +2913,19 @@
       <c r="G38" t="s">
         <v>100</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>21</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" t="s">
         <v>25</v>
       </c>
       <c r="K38" t="s">
         <v>26</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="1">
         <v>46255</v>
       </c>
       <c r="M38">
@@ -2979,19 +2969,19 @@
       <c r="G39" t="s">
         <v>115</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>21</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" t="s">
         <v>25</v>
       </c>
       <c r="K39" t="s">
         <v>26</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="1">
         <v>46255</v>
       </c>
       <c r="M39">
@@ -3035,19 +3025,19 @@
       <c r="G40" t="s">
         <v>100</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>21</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" t="s">
         <v>25</v>
       </c>
       <c r="K40" t="s">
         <v>26</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="1">
         <v>46255</v>
       </c>
       <c r="M40">
@@ -3091,19 +3081,19 @@
       <c r="G41" t="s">
         <v>100</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="1">
         <v>21</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" t="s">
         <v>25</v>
       </c>
       <c r="K41" t="s">
         <v>26</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="1">
         <v>46255</v>
       </c>
       <c r="M41">
@@ -3147,19 +3137,19 @@
       <c r="G42" t="s">
         <v>33</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
         <v>21</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" t="s">
         <v>25</v>
       </c>
       <c r="K42" t="s">
         <v>26</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="1">
         <v>46255</v>
       </c>
       <c r="M42">
@@ -3203,19 +3193,19 @@
       <c r="G43" t="s">
         <v>33</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
         <v>24</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" t="s">
         <v>25</v>
       </c>
       <c r="K43" t="s">
         <v>26</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="1">
         <v>46258</v>
       </c>
       <c r="M43">
@@ -3259,19 +3249,19 @@
       <c r="G44" t="s">
         <v>23</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
         <v>25</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="J44" t="s">
         <v>25</v>
       </c>
       <c r="K44" t="s">
         <v>26</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="1">
         <v>46259</v>
       </c>
       <c r="M44">
@@ -3315,19 +3305,19 @@
       <c r="G45" t="s">
         <v>23</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
         <v>25</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" t="s">
         <v>25</v>
       </c>
       <c r="K45" t="s">
         <v>26</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="1">
         <v>46259</v>
       </c>
       <c r="M45">
@@ -3371,19 +3361,19 @@
       <c r="G46" t="s">
         <v>44</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
         <v>25</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" t="s">
         <v>25</v>
       </c>
       <c r="K46" t="s">
         <v>26</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="1">
         <v>46259</v>
       </c>
       <c r="M46">
@@ -3427,19 +3417,19 @@
       <c r="G47" t="s">
         <v>33</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
         <v>25</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" t="s">
         <v>25</v>
       </c>
       <c r="K47" t="s">
         <v>26</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="1">
         <v>46259</v>
       </c>
       <c r="M47">
@@ -3483,26 +3473,26 @@
       <c r="G48" t="s">
         <v>100</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
         <v>27</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" t="s">
         <v>25</v>
       </c>
       <c r="K48" t="s">
         <v>26</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="1">
         <v>46261</v>
       </c>
       <c r="M48">
         <v>611732</v>
       </c>
       <c r="N48" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O48">
         <v>10.1</v>
@@ -3511,7 +3501,7 @@
         <v>36</v>
       </c>
       <c r="Q48" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="R48" t="s">
         <v>26</v>
@@ -3539,19 +3529,19 @@
       <c r="G49" t="s">
         <v>33</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="1">
         <v>27</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" t="s">
         <v>25</v>
       </c>
       <c r="K49" t="s">
         <v>26</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="1">
         <v>46261</v>
       </c>
       <c r="M49">
@@ -3595,26 +3585,26 @@
       <c r="G50" t="s">
         <v>100</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="1">
         <v>28</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" t="s">
         <v>25</v>
       </c>
       <c r="K50" t="s">
         <v>26</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="1">
         <v>46262</v>
       </c>
       <c r="M50">
         <v>612663</v>
       </c>
       <c r="N50" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O50">
         <v>2.89</v>
@@ -3623,7 +3613,7 @@
         <v>36</v>
       </c>
       <c r="Q50" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="R50" t="s">
         <v>26</v>
@@ -3651,19 +3641,19 @@
       <c r="G51" t="s">
         <v>33</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" t="s">
         <v>25</v>
       </c>
       <c r="K51" t="s">
         <v>26</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="1">
         <v>46266</v>
       </c>
       <c r="M51">
@@ -3707,26 +3697,26 @@
       <c r="G52" t="s">
         <v>100</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="1">
         <v>3</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" t="s">
         <v>25</v>
       </c>
       <c r="K52" t="s">
         <v>26</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="1">
         <v>46268</v>
       </c>
       <c r="M52">
         <v>615019</v>
       </c>
       <c r="N52" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O52">
         <v>7.95</v>
@@ -3735,7 +3725,7 @@
         <v>36</v>
       </c>
       <c r="Q52" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="R52" t="s">
         <v>26</v>
@@ -3763,19 +3753,19 @@
       <c r="G53" t="s">
         <v>33</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="1">
         <v>3</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J53" s="1" t="s">
+      <c r="J53" t="s">
         <v>25</v>
       </c>
       <c r="K53" t="s">
         <v>26</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="1">
         <v>46268</v>
       </c>
       <c r="M53">
@@ -3819,19 +3809,19 @@
       <c r="G54" t="s">
         <v>33</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="1">
         <v>4</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" t="s">
         <v>25</v>
       </c>
       <c r="K54" t="s">
         <v>26</v>
       </c>
-      <c r="L54">
+      <c r="L54" s="1">
         <v>46269</v>
       </c>
       <c r="M54">
@@ -3875,19 +3865,19 @@
       <c r="G55" t="s">
         <v>33</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="1">
         <v>4</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J55" t="s">
         <v>25</v>
       </c>
       <c r="K55" t="s">
         <v>26</v>
       </c>
-      <c r="L55">
+      <c r="L55" s="1">
         <v>46269</v>
       </c>
       <c r="M55">
@@ -3931,19 +3921,19 @@
       <c r="G56" t="s">
         <v>33</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="1">
         <v>4</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" t="s">
         <v>25</v>
       </c>
       <c r="K56" t="s">
         <v>26</v>
       </c>
-      <c r="L56">
+      <c r="L56" s="1">
         <v>46269</v>
       </c>
       <c r="M56">
@@ -3987,19 +3977,19 @@
       <c r="G57" t="s">
         <v>141</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="1">
         <v>8</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" t="s">
         <v>25</v>
       </c>
       <c r="K57" t="s">
         <v>26</v>
       </c>
-      <c r="L57">
+      <c r="L57" s="1">
         <v>46273</v>
       </c>
       <c r="M57">
@@ -4043,19 +4033,19 @@
       <c r="G58" t="s">
         <v>33</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="1">
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" t="s">
         <v>25</v>
       </c>
       <c r="K58" t="s">
         <v>26</v>
       </c>
-      <c r="L58">
+      <c r="L58" s="1">
         <v>46273</v>
       </c>
       <c r="M58">
@@ -4099,19 +4089,19 @@
       <c r="G59" t="s">
         <v>100</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="1">
         <v>9</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" t="s">
         <v>25</v>
       </c>
       <c r="K59" t="s">
         <v>26</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="1">
         <v>46274</v>
       </c>
       <c r="M59">
@@ -4124,7 +4114,7 @@
         <v>21.23</v>
       </c>
       <c r="P59" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q59" t="s">
         <v>29</v>
@@ -4155,19 +4145,19 @@
       <c r="G60" t="s">
         <v>33</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="1">
         <v>9</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="J60" t="s">
         <v>25</v>
       </c>
       <c r="K60" t="s">
         <v>26</v>
       </c>
-      <c r="L60">
+      <c r="L60" s="1">
         <v>46274</v>
       </c>
       <c r="M60">
@@ -4182,15 +4172,65 @@
       <c r="P60" t="s">
         <v>56</v>
       </c>
-      <c r="Q60" t="s">
-        <v>29</v>
-      </c>
       <c r="R60" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" t="s">
+        <v>148</v>
+      </c>
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" t="s">
+        <v>44</v>
+      </c>
+      <c r="H61" s="1">
+        <v>10</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J61" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="1">
+        <v>46275</v>
+      </c>
+      <c r="M61">
+        <v>617914</v>
+      </c>
+      <c r="N61" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="P61" t="s">
+        <v>28</v>
+      </c>
+      <c r="R61" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4899,31 +4939,31 @@
         <v>30</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>68.915999999999997</v>
       </c>
       <c r="E19">
-        <v>25.39207</v>
+        <v>46.350480000000005</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I19">
-        <v>0.6</v>
-      </c>
-      <c r="J19" t="s">
-        <v>86</v>
+        <v>0.65</v>
+      </c>
+      <c r="J19">
+        <v>1.1333333333333333</v>
       </c>
       <c r="K19">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L19">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -4940,28 +4980,28 @@
         <v>86</v>
       </c>
       <c r="E20">
-        <v>5.8520000000000003</v>
+        <v>30.749839999999999</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20" t="s">
-        <v>86</v>
+        <v>0.6</v>
+      </c>
+      <c r="J20">
+        <v>0.6333333333333333</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -4978,28 +5018,28 @@
         <v>86</v>
       </c>
       <c r="E21">
-        <v>44.969430000000003</v>
+        <v>77.769009999999994</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H21">
         <v>5</v>
       </c>
       <c r="I21">
-        <v>0.25</v>
-      </c>
-      <c r="J21" t="s">
-        <v>86</v>
+        <v>0.17857142857142858</v>
+      </c>
+      <c r="J21">
+        <v>0.96666666666666667</v>
       </c>
       <c r="K21">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L21">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FFACEAB-2B7C-47E6-B2FC-CF30D8192BFE}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE957350-F75A-4875-9301-CCFC486384A5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$G$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="142">
   <si>
     <t>Usuário</t>
   </si>
@@ -124,9 +124,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>Neg Aberta</t>
-  </si>
-  <si>
     <t>LEAD AGENDADO</t>
   </si>
   <si>
@@ -226,9 +223,6 @@
     <t>Venda</t>
   </si>
   <si>
-    <t>FECHAMENTO DE VENDA</t>
-  </si>
-  <si>
     <t>GIOVANNA NUBIA DA SILVA CUNHA</t>
   </si>
   <si>
@@ -325,15 +319,6 @@
     <t>Qualificado</t>
   </si>
   <si>
-    <t>INELEGÍVEL - BAIXO CONSUMO</t>
-  </si>
-  <si>
-    <t>INELEGÍVEL CONCORRÊNCIA RETORNO 180 DIAS</t>
-  </si>
-  <si>
-    <t>FALTA DE CONTATO - DECISOR NÃO ENCONTRAD</t>
-  </si>
-  <si>
     <t>FELDER COMERCIO DE PANIFICACAO LTDA EPP</t>
   </si>
   <si>
@@ -352,9 +337,6 @@
     <t>DANIELLE CASTELO MARTINS MACIEL</t>
   </si>
   <si>
-    <t>POSSUI USINA PROPRIA</t>
-  </si>
-  <si>
     <t>CLARICE LUNARDI</t>
   </si>
   <si>
@@ -376,9 +358,6 @@
     <t>ELIEZER SOARES CAVALCANTE</t>
   </si>
   <si>
-    <t>ANALISE DE CRÉDITO</t>
-  </si>
-  <si>
     <t>HISSA DEMETRIO FABRIC DE BISCOITOS EIREL</t>
   </si>
   <si>
@@ -406,15 +385,9 @@
     <t>GENI NATALIA DA SILVA</t>
   </si>
   <si>
-    <t>CNPJ BAIXADO OU INATIVO NA RF</t>
-  </si>
-  <si>
     <t>ROSILENE ALVES DE ALMEIDA</t>
   </si>
   <si>
-    <t>INELEGÍVEL CONCORRÊNCIA RETORNO 90 DIAS</t>
-  </si>
-  <si>
     <t>METAIS SOUZA RESENDE LTDA</t>
   </si>
   <si>
@@ -442,9 +415,6 @@
     <t>SEP</t>
   </si>
   <si>
-    <t>RESTRIÇÕES DE CRÉDITO</t>
-  </si>
-  <si>
     <t>MIKAEL DE SOUZA LIMA</t>
   </si>
   <si>
@@ -484,10 +454,19 @@
     <t>Semana1</t>
   </si>
   <si>
-    <t>DECLINE MASSIVO – INATIVAÇÃO VENDEDOR</t>
-  </si>
-  <si>
     <t>IZABELA IZARIAS</t>
+  </si>
+  <si>
+    <t>Em andamento</t>
+  </si>
+  <si>
+    <t>Não encontrado</t>
+  </si>
+  <si>
+    <t>LAERCIO GOMES PINTO</t>
+  </si>
+  <si>
+    <t>VICENTE JOAQUIM DOS SANTOS</t>
   </si>
 </sst>
 </file>
@@ -812,11 +791,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="9" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -838,13 +817,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -872,15 +851,15 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
@@ -889,24 +868,24 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
-        <v>55</v>
+      <c r="G2" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H2" s="1">
         <v>2</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>34</v>
+      <c r="I2" t="s">
+        <v>33</v>
       </c>
       <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L2" s="1">
@@ -916,16 +895,13 @@
         <v>585567</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O2">
         <v>1.41</v>
       </c>
       <c r="P2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="R2" t="s">
         <v>26</v>
@@ -933,10 +909,10 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -945,24 +921,24 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
-        <v>55</v>
+      <c r="G3" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>34</v>
+      <c r="I3" t="s">
+        <v>33</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="1">
@@ -972,16 +948,13 @@
         <v>585435</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O3">
         <v>34.979999999999997</v>
       </c>
       <c r="P3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="R3" t="s">
         <v>26</v>
@@ -989,10 +962,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -1001,24 +974,24 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
-        <v>44</v>
+      <c r="G4" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H4" s="1">
         <v>2</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
+      <c r="I4" t="s">
+        <v>33</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="1">
@@ -1028,16 +1001,16 @@
         <v>589815</v>
       </c>
       <c r="N4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O4">
         <v>30.92</v>
       </c>
       <c r="P4" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R4" t="s">
         <v>26</v>
@@ -1045,10 +1018,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -1057,24 +1030,24 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
-        <v>33</v>
+      <c r="G5" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H5" s="1">
         <v>6</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>34</v>
+      <c r="I5" t="s">
+        <v>33</v>
       </c>
       <c r="J5" t="s">
         <v>25</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="1">
@@ -1084,16 +1057,16 @@
         <v>587363</v>
       </c>
       <c r="N5" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O5">
         <v>7.85</v>
       </c>
       <c r="P5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R5" t="s">
         <v>26</v>
@@ -1101,10 +1074,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -1113,24 +1086,24 @@
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" t="s">
-        <v>33</v>
+      <c r="G6" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H6" s="1">
         <v>7</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>34</v>
+      <c r="I6" t="s">
+        <v>33</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L6" s="1">
@@ -1140,16 +1113,16 @@
         <v>588146</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O6">
         <v>67.37</v>
       </c>
       <c r="P6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R6" t="s">
         <v>26</v>
@@ -1157,10 +1130,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -1169,24 +1142,24 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" t="s">
-        <v>33</v>
+      <c r="G7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H7" s="1">
         <v>8</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>34</v>
+      <c r="I7" t="s">
+        <v>33</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L7" s="1">
@@ -1196,16 +1169,16 @@
         <v>588663</v>
       </c>
       <c r="N7" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O7">
         <v>35.78</v>
       </c>
       <c r="P7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R7" t="s">
         <v>26</v>
@@ -1213,36 +1186,36 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
-        <v>33</v>
+      <c r="G8" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H8" s="1">
         <v>10</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>34</v>
+      <c r="I8" t="s">
+        <v>33</v>
       </c>
       <c r="J8" t="s">
         <v>25</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="1">
@@ -1252,16 +1225,16 @@
         <v>589870</v>
       </c>
       <c r="N8" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O8">
         <v>27.46</v>
       </c>
       <c r="P8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R8" t="s">
         <v>26</v>
@@ -1269,10 +1242,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -1281,24 +1254,24 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" t="s">
-        <v>41</v>
+      <c r="G9" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H9" s="1">
         <v>15</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>34</v>
+      <c r="I9" t="s">
+        <v>33</v>
       </c>
       <c r="J9" t="s">
         <v>25</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="1">
@@ -1308,16 +1281,16 @@
         <v>591481</v>
       </c>
       <c r="N9" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O9">
         <v>10</v>
       </c>
       <c r="P9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R9" t="s">
         <v>26</v>
@@ -1325,10 +1298,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -1337,24 +1310,24 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
       </c>
-      <c r="G10" t="s">
-        <v>33</v>
+      <c r="G10" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H10" s="1">
         <v>15</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>34</v>
+      <c r="I10" t="s">
+        <v>33</v>
       </c>
       <c r="J10" t="s">
         <v>25</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L10" s="1">
@@ -1364,16 +1337,16 @@
         <v>591629</v>
       </c>
       <c r="N10" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O10">
         <v>10.44</v>
       </c>
       <c r="P10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R10" t="s">
         <v>26</v>
@@ -1381,10 +1354,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -1393,24 +1366,24 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
       </c>
-      <c r="G11" t="s">
-        <v>33</v>
+      <c r="G11" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H11" s="1">
         <v>16</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>34</v>
+      <c r="I11" t="s">
+        <v>33</v>
       </c>
       <c r="J11" t="s">
         <v>25</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L11" s="1">
@@ -1420,16 +1393,16 @@
         <v>594789</v>
       </c>
       <c r="N11" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O11">
         <v>10.75</v>
       </c>
       <c r="P11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R11" t="s">
         <v>26</v>
@@ -1437,10 +1410,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -1449,43 +1422,43 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
       </c>
-      <c r="G12" t="s">
-        <v>44</v>
+      <c r="G12" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>34</v>
+      <c r="I12" t="s">
+        <v>33</v>
       </c>
       <c r="J12" t="s">
         <v>25</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="1">
         <v>46223</v>
       </c>
-      <c r="M12">
-        <v>594209</v>
+      <c r="M12" t="s">
+        <v>139</v>
       </c>
       <c r="N12" t="s">
-        <v>60</v>
-      </c>
-      <c r="O12">
-        <v>41.35</v>
+        <v>139</v>
+      </c>
+      <c r="O12" t="s">
+        <v>139</v>
       </c>
       <c r="P12" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R12" t="s">
         <v>26</v>
@@ -1493,10 +1466,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -1505,43 +1478,43 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
       </c>
-      <c r="G13" t="s">
-        <v>33</v>
+      <c r="G13" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H13" s="1">
         <v>21</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>34</v>
+      <c r="I13" t="s">
+        <v>33</v>
       </c>
       <c r="J13" t="s">
         <v>25</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L13" s="1">
         <v>46224</v>
       </c>
-      <c r="M13">
-        <v>593210</v>
+      <c r="M13" t="s">
+        <v>139</v>
       </c>
       <c r="N13" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13">
-        <v>3.5</v>
+        <v>139</v>
+      </c>
+      <c r="O13" t="s">
+        <v>139</v>
       </c>
       <c r="P13" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="R13" t="s">
         <v>26</v>
@@ -1549,10 +1522,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -1561,24 +1534,24 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
       </c>
-      <c r="G14" t="s">
-        <v>33</v>
+      <c r="G14" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H14" s="1">
         <v>22</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>34</v>
+      <c r="I14" t="s">
+        <v>33</v>
       </c>
       <c r="J14" t="s">
         <v>25</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="1">
@@ -1588,16 +1561,16 @@
         <v>595396</v>
       </c>
       <c r="N14" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O14">
         <v>11.66</v>
       </c>
       <c r="P14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R14" t="s">
         <v>26</v>
@@ -1605,10 +1578,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -1617,43 +1590,43 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
       </c>
-      <c r="G15" t="s">
-        <v>33</v>
+      <c r="G15" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H15" s="1">
         <v>24</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>34</v>
+      <c r="I15" t="s">
+        <v>33</v>
       </c>
       <c r="J15" t="s">
         <v>25</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L15" s="1">
         <v>46227</v>
       </c>
-      <c r="M15">
-        <v>582148</v>
+      <c r="M15" t="s">
+        <v>139</v>
       </c>
       <c r="N15" t="s">
-        <v>60</v>
-      </c>
-      <c r="O15">
-        <v>7.87</v>
+        <v>139</v>
+      </c>
+      <c r="O15" t="s">
+        <v>139</v>
       </c>
       <c r="P15" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R15" t="s">
         <v>26</v>
@@ -1661,36 +1634,36 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
         <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="1">
+        <v>28</v>
+      </c>
+      <c r="I16" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="1">
-        <v>28</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="J16" t="s">
         <v>25</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L16" s="1">
@@ -1700,16 +1673,16 @@
         <v>593213</v>
       </c>
       <c r="N16" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O16">
         <v>3.66</v>
       </c>
       <c r="P16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R16" t="s">
         <v>26</v>
@@ -1717,10 +1690,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
         <v>19</v>
@@ -1729,43 +1702,43 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
       </c>
-      <c r="G17" t="s">
-        <v>44</v>
+      <c r="G17" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H17" s="1">
         <v>28</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>34</v>
+      <c r="I17" t="s">
+        <v>33</v>
       </c>
       <c r="J17" t="s">
         <v>25</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L17" s="1">
         <v>46231</v>
       </c>
-      <c r="M17">
-        <v>598334</v>
+      <c r="M17" t="s">
+        <v>139</v>
       </c>
       <c r="N17" t="s">
-        <v>45</v>
-      </c>
-      <c r="O17">
-        <v>9.7899999999999991</v>
+        <v>139</v>
+      </c>
+      <c r="O17" t="s">
+        <v>139</v>
       </c>
       <c r="P17" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q17" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="R17" t="s">
         <v>26</v>
@@ -1773,10 +1746,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
@@ -1785,24 +1758,24 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="1">
         <v>28</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>34</v>
+      <c r="I18" t="s">
+        <v>33</v>
       </c>
       <c r="J18" t="s">
         <v>25</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="1">
@@ -1812,16 +1785,16 @@
         <v>598353</v>
       </c>
       <c r="N18" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O18">
         <v>6.9</v>
       </c>
       <c r="P18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R18" t="s">
         <v>26</v>
@@ -1829,10 +1802,10 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
@@ -1841,24 +1814,24 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
         <v>22</v>
       </c>
-      <c r="G19" t="s">
-        <v>44</v>
+      <c r="G19" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H19" s="1">
         <v>3</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>24</v>
       </c>
       <c r="J19" t="s">
         <v>25</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="1">
@@ -1868,16 +1841,16 @@
         <v>601583</v>
       </c>
       <c r="N19" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -1885,10 +1858,10 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -1897,24 +1870,24 @@
         <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="G20" t="s">
-        <v>33</v>
+      <c r="G20" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H20" s="1">
         <v>4</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>24</v>
       </c>
       <c r="J20" t="s">
         <v>25</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L20" s="1">
@@ -1924,16 +1897,16 @@
         <v>601025</v>
       </c>
       <c r="N20" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O20">
         <v>41.62</v>
       </c>
       <c r="P20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R20" t="s">
         <v>26</v>
@@ -1941,10 +1914,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -1953,24 +1926,24 @@
         <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
         <v>22</v>
       </c>
-      <c r="G21" t="s">
-        <v>44</v>
+      <c r="G21" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H21" s="1">
         <v>5</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>24</v>
       </c>
       <c r="J21" t="s">
         <v>25</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="1">
@@ -1980,16 +1953,16 @@
         <v>601537</v>
       </c>
       <c r="N21" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O21">
         <v>4.63</v>
       </c>
       <c r="P21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R21" t="s">
         <v>26</v>
@@ -1997,10 +1970,10 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
@@ -2009,24 +1982,24 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
         <v>22</v>
       </c>
-      <c r="G22" t="s">
-        <v>33</v>
+      <c r="G22" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H22" s="1">
         <v>6</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" t="s">
         <v>24</v>
       </c>
       <c r="J22" t="s">
         <v>25</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L22" s="1">
@@ -2036,16 +2009,16 @@
         <v>601944</v>
       </c>
       <c r="N22" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O22">
         <v>1.96</v>
       </c>
       <c r="P22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R22" t="s">
         <v>26</v>
@@ -2053,10 +2026,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
@@ -2065,24 +2038,24 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F23" t="s">
         <v>22</v>
       </c>
-      <c r="G23" t="s">
-        <v>33</v>
+      <c r="G23" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H23" s="1">
         <v>7</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>24</v>
       </c>
       <c r="J23" t="s">
         <v>25</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L23" s="1">
@@ -2092,16 +2065,16 @@
         <v>603017</v>
       </c>
       <c r="N23" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O23">
         <v>1.89</v>
       </c>
       <c r="P23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R23" t="s">
         <v>26</v>
@@ -2109,10 +2082,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -2121,24 +2094,24 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>22</v>
       </c>
-      <c r="G24" t="s">
-        <v>44</v>
+      <c r="G24" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H24" s="1">
         <v>7</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" t="s">
         <v>24</v>
       </c>
       <c r="J24" t="s">
         <v>25</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="1">
@@ -2148,16 +2121,16 @@
         <v>602969</v>
       </c>
       <c r="N24" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O24">
         <v>6.12</v>
       </c>
       <c r="P24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R24" t="s">
         <v>26</v>
@@ -2165,10 +2138,10 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -2177,24 +2150,24 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
       </c>
-      <c r="G25" t="s">
-        <v>33</v>
+      <c r="G25" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H25" s="1">
         <v>10</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" t="s">
         <v>24</v>
       </c>
       <c r="J25" t="s">
         <v>25</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L25" s="1">
@@ -2204,16 +2177,16 @@
         <v>603608</v>
       </c>
       <c r="N25" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O25">
         <v>8.77</v>
       </c>
       <c r="P25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R25" t="s">
         <v>26</v>
@@ -2238,19 +2211,19 @@
       <c r="F26" t="s">
         <v>22</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="1">
         <v>11</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" t="s">
         <v>24</v>
       </c>
       <c r="J26" t="s">
         <v>25</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L26" s="1">
@@ -2260,16 +2233,16 @@
         <v>604128</v>
       </c>
       <c r="N26" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O26">
         <v>8.3699999999999992</v>
       </c>
       <c r="P26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R26" t="e">
         <v>#N/A</v>
@@ -2277,10 +2250,10 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -2289,24 +2262,24 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
         <v>22</v>
       </c>
-      <c r="G27" t="s">
-        <v>33</v>
+      <c r="G27" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H27" s="1">
         <v>11</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" t="s">
         <v>24</v>
       </c>
       <c r="J27" t="s">
         <v>25</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L27" s="1">
@@ -2316,16 +2289,16 @@
         <v>604194</v>
       </c>
       <c r="N27" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O27">
         <v>2.98</v>
       </c>
       <c r="P27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R27" t="s">
         <v>26</v>
@@ -2333,10 +2306,10 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
@@ -2345,24 +2318,24 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
-      </c>
-      <c r="G28" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H28" s="1">
         <v>13</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" t="s">
         <v>24</v>
       </c>
       <c r="J28" t="s">
         <v>25</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L28" s="1">
@@ -2372,16 +2345,16 @@
         <v>605287</v>
       </c>
       <c r="N28" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O28">
         <v>61.58</v>
       </c>
       <c r="P28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R28" t="s">
         <v>26</v>
@@ -2389,10 +2362,10 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
         <v>19</v>
@@ -2401,24 +2374,24 @@
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
         <v>22</v>
       </c>
-      <c r="G29" t="s">
-        <v>44</v>
+      <c r="G29" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H29" s="1">
         <v>13</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" t="s">
         <v>24</v>
       </c>
       <c r="J29" t="s">
         <v>25</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="1">
@@ -2428,16 +2401,16 @@
         <v>605244</v>
       </c>
       <c r="N29" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O29">
         <v>91.5</v>
       </c>
       <c r="P29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R29" t="s">
         <v>26</v>
@@ -2445,10 +2418,10 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -2457,43 +2430,43 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
-      </c>
-      <c r="G30" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H30" s="1">
         <v>14</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" t="s">
         <v>24</v>
       </c>
       <c r="J30" t="s">
         <v>25</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L30" s="1">
         <v>46248</v>
       </c>
-      <c r="M30">
-        <v>606392</v>
+      <c r="M30" t="s">
+        <v>139</v>
       </c>
       <c r="N30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O30">
-        <v>5.13</v>
+        <v>139</v>
+      </c>
+      <c r="O30" t="s">
+        <v>139</v>
       </c>
       <c r="P30" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R30" t="s">
         <v>26</v>
@@ -2501,10 +2474,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
         <v>19</v>
@@ -2513,24 +2486,24 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" t="s">
         <v>22</v>
       </c>
-      <c r="G31" t="s">
-        <v>33</v>
+      <c r="G31" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H31" s="1">
         <v>17</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" t="s">
         <v>24</v>
       </c>
       <c r="J31" t="s">
         <v>25</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K31" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L31" s="1">
@@ -2540,16 +2513,16 @@
         <v>606908</v>
       </c>
       <c r="N31" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O31">
         <v>37.299999999999997</v>
       </c>
       <c r="P31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R31" t="s">
         <v>26</v>
@@ -2557,10 +2530,10 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
@@ -2569,24 +2542,24 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
         <v>22</v>
       </c>
-      <c r="G32" t="s">
-        <v>33</v>
+      <c r="G32" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H32" s="1">
         <v>18</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" t="s">
         <v>24</v>
       </c>
       <c r="J32" t="s">
         <v>25</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L32" s="1">
@@ -2596,16 +2569,16 @@
         <v>581722</v>
       </c>
       <c r="N32" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O32">
         <v>21.24</v>
       </c>
       <c r="P32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R32" t="s">
         <v>26</v>
@@ -2613,10 +2586,10 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
@@ -2625,43 +2598,43 @@
         <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F33" t="s">
-        <v>99</v>
-      </c>
-      <c r="G33" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H33" s="1">
         <v>19</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" t="s">
         <v>24</v>
       </c>
       <c r="J33" t="s">
         <v>25</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L33" s="1">
         <v>46253</v>
       </c>
-      <c r="M33">
-        <v>608180</v>
+      <c r="M33" t="s">
+        <v>139</v>
       </c>
       <c r="N33" t="s">
-        <v>45</v>
-      </c>
-      <c r="O33">
-        <v>3.73</v>
+        <v>139</v>
+      </c>
+      <c r="O33" t="s">
+        <v>139</v>
       </c>
       <c r="P33" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q33" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R33" t="s">
         <v>26</v>
@@ -2669,10 +2642,10 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
         <v>19</v>
@@ -2681,24 +2654,24 @@
         <v>20</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F34" t="s">
         <v>22</v>
       </c>
-      <c r="G34" t="s">
-        <v>44</v>
+      <c r="G34" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H34" s="1">
         <v>19</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" t="s">
         <v>24</v>
       </c>
       <c r="J34" t="s">
         <v>25</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="1">
@@ -2708,16 +2681,16 @@
         <v>608150</v>
       </c>
       <c r="N34" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O34">
         <v>4.54</v>
       </c>
       <c r="P34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R34" t="s">
         <v>26</v>
@@ -2725,10 +2698,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
         <v>19</v>
@@ -2737,43 +2710,43 @@
         <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
-      </c>
-      <c r="G35" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H35" s="1">
         <v>20</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" t="s">
         <v>24</v>
       </c>
       <c r="J35" t="s">
         <v>25</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L35" s="1">
         <v>46254</v>
       </c>
-      <c r="M35">
-        <v>608550</v>
+      <c r="M35" t="s">
+        <v>139</v>
       </c>
       <c r="N35" t="s">
-        <v>60</v>
-      </c>
-      <c r="O35">
-        <v>20.25</v>
+        <v>139</v>
+      </c>
+      <c r="O35" t="s">
+        <v>139</v>
       </c>
       <c r="P35" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="Q35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R35" t="s">
         <v>26</v>
@@ -2781,10 +2754,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
         <v>19</v>
@@ -2793,43 +2766,43 @@
         <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
-      </c>
-      <c r="G36" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H36" s="1">
         <v>21</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" t="s">
         <v>24</v>
       </c>
       <c r="J36" t="s">
         <v>25</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L36" s="1">
         <v>46255</v>
       </c>
-      <c r="M36">
-        <v>605051</v>
+      <c r="M36" t="s">
+        <v>139</v>
       </c>
       <c r="N36" t="s">
-        <v>45</v>
-      </c>
-      <c r="O36">
-        <v>5.89</v>
+        <v>139</v>
+      </c>
+      <c r="O36" t="s">
+        <v>139</v>
       </c>
       <c r="P36" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Q36" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="R36" t="s">
         <v>26</v>
@@ -2837,10 +2810,10 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
@@ -2849,43 +2822,43 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
-        <v>99</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H37" s="1">
         <v>21</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" t="s">
         <v>24</v>
       </c>
       <c r="J37" t="s">
         <v>25</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L37" s="1">
         <v>46255</v>
       </c>
-      <c r="M37">
-        <v>557624</v>
+      <c r="M37" t="s">
+        <v>139</v>
       </c>
       <c r="N37" t="s">
-        <v>45</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="O37" t="s">
+        <v>139</v>
       </c>
       <c r="P37" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Q37" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R37" t="s">
         <v>26</v>
@@ -2893,10 +2866,10 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
@@ -2905,24 +2878,24 @@
         <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>99</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H38" s="1">
         <v>21</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" t="s">
         <v>24</v>
       </c>
       <c r="J38" t="s">
         <v>25</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L38" s="1">
@@ -2932,16 +2905,16 @@
         <v>609384</v>
       </c>
       <c r="N38" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O38">
         <v>3.39</v>
       </c>
       <c r="P38" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Q38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R38" t="s">
         <v>26</v>
@@ -2949,10 +2922,10 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
         <v>19</v>
@@ -2961,24 +2934,24 @@
         <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F39" t="s">
-        <v>99</v>
-      </c>
-      <c r="G39" t="s">
-        <v>115</v>
+        <v>94</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="H39" s="1">
         <v>21</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" t="s">
         <v>24</v>
       </c>
       <c r="J39" t="s">
         <v>25</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L39" s="1">
@@ -2988,16 +2961,16 @@
         <v>609414</v>
       </c>
       <c r="N39" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O39">
         <v>10.9</v>
       </c>
       <c r="P39" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Q39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R39" t="s">
         <v>26</v>
@@ -3005,10 +2978,10 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
@@ -3017,24 +2990,24 @@
         <v>20</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H40" s="1">
         <v>21</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" t="s">
         <v>24</v>
       </c>
       <c r="J40" t="s">
         <v>25</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L40" s="1">
@@ -3044,16 +3017,16 @@
         <v>604864</v>
       </c>
       <c r="N40" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O40">
         <v>19.47</v>
       </c>
       <c r="P40" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="Q40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R40" t="s">
         <v>26</v>
@@ -3061,10 +3034,10 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
         <v>19</v>
@@ -3073,43 +3046,43 @@
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H41" s="1">
         <v>21</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" t="s">
         <v>24</v>
       </c>
       <c r="J41" t="s">
         <v>25</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L41" s="1">
         <v>46255</v>
       </c>
-      <c r="M41">
-        <v>605070</v>
+      <c r="M41" t="s">
+        <v>139</v>
       </c>
       <c r="N41" t="s">
-        <v>45</v>
-      </c>
-      <c r="O41">
-        <v>3.19</v>
+        <v>139</v>
+      </c>
+      <c r="O41" t="s">
+        <v>139</v>
       </c>
       <c r="P41" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="R41" t="s">
         <v>26</v>
@@ -3117,10 +3090,10 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
         <v>19</v>
@@ -3129,24 +3102,24 @@
         <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42" t="s">
         <v>22</v>
       </c>
-      <c r="G42" t="s">
-        <v>33</v>
+      <c r="G42" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H42" s="1">
         <v>21</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" t="s">
         <v>24</v>
       </c>
       <c r="J42" t="s">
         <v>25</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L42" s="1">
@@ -3156,16 +3129,16 @@
         <v>609512</v>
       </c>
       <c r="N42" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O42">
         <v>7.15</v>
       </c>
       <c r="P42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R42" t="s">
         <v>26</v>
@@ -3173,10 +3146,10 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
         <v>19</v>
@@ -3185,24 +3158,24 @@
         <v>20</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F43" t="s">
         <v>22</v>
       </c>
-      <c r="G43" t="s">
-        <v>33</v>
+      <c r="G43" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H43" s="1">
         <v>24</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" t="s">
         <v>24</v>
       </c>
       <c r="J43" t="s">
         <v>25</v>
       </c>
-      <c r="K43" t="s">
+      <c r="K43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L43" s="1">
@@ -3212,16 +3185,16 @@
         <v>610104</v>
       </c>
       <c r="N43" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O43">
         <v>9.2200000000000006</v>
       </c>
       <c r="P43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R43" t="s">
         <v>26</v>
@@ -3232,7 +3205,7 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
         <v>19</v>
@@ -3246,38 +3219,38 @@
       <c r="F44" t="s">
         <v>22</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="1">
         <v>25</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" t="s">
         <v>24</v>
       </c>
       <c r="J44" t="s">
         <v>25</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L44" s="1">
         <v>46259</v>
       </c>
-      <c r="M44">
-        <v>610626</v>
+      <c r="M44" t="s">
+        <v>139</v>
       </c>
       <c r="N44" t="s">
-        <v>45</v>
-      </c>
-      <c r="O44">
-        <v>4.63</v>
+        <v>139</v>
+      </c>
+      <c r="O44" t="s">
+        <v>139</v>
       </c>
       <c r="P44" t="s">
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="R44" t="e">
         <v>#N/A</v>
@@ -3288,7 +3261,7 @@
         <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
         <v>19</v>
@@ -3302,19 +3275,19 @@
       <c r="F45" t="s">
         <v>22</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="1">
         <v>25</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" t="s">
         <v>24</v>
       </c>
       <c r="J45" t="s">
         <v>25</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L45" s="1">
@@ -3324,16 +3297,16 @@
         <v>614542</v>
       </c>
       <c r="N45" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O45">
         <v>20.53</v>
       </c>
       <c r="P45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R45" t="s">
         <v>26</v>
@@ -3341,10 +3314,10 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
         <v>19</v>
@@ -3353,43 +3326,43 @@
         <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F46" t="s">
         <v>22</v>
       </c>
-      <c r="G46" t="s">
-        <v>44</v>
+      <c r="G46" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H46" s="1">
         <v>25</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" t="s">
         <v>24</v>
       </c>
       <c r="J46" t="s">
         <v>25</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L46" s="1">
         <v>46259</v>
       </c>
-      <c r="M46">
-        <v>610910</v>
+      <c r="M46" t="s">
+        <v>139</v>
       </c>
       <c r="N46" t="s">
-        <v>45</v>
-      </c>
-      <c r="O46">
-        <v>8.44</v>
+        <v>139</v>
+      </c>
+      <c r="O46" t="s">
+        <v>139</v>
       </c>
       <c r="P46" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="R46" t="s">
         <v>26</v>
@@ -3397,10 +3370,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C47" t="s">
         <v>19</v>
@@ -3409,24 +3382,24 @@
         <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F47" t="s">
         <v>22</v>
       </c>
-      <c r="G47" t="s">
-        <v>33</v>
+      <c r="G47" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H47" s="1">
         <v>25</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" t="s">
         <v>24</v>
       </c>
       <c r="J47" t="s">
         <v>25</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L47" s="1">
@@ -3436,16 +3409,16 @@
         <v>610596</v>
       </c>
       <c r="N47" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O47">
         <v>4.17</v>
       </c>
       <c r="P47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R47" t="s">
         <v>26</v>
@@ -3453,10 +3426,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C48" t="s">
         <v>19</v>
@@ -3465,43 +3438,43 @@
         <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F48" t="s">
-        <v>99</v>
-      </c>
-      <c r="G48" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H48" s="1">
         <v>27</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" t="s">
         <v>24</v>
       </c>
       <c r="J48" t="s">
         <v>25</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L48" s="1">
         <v>46261</v>
       </c>
-      <c r="M48">
-        <v>611732</v>
+      <c r="M48" t="s">
+        <v>139</v>
       </c>
       <c r="N48" t="s">
-        <v>45</v>
-      </c>
-      <c r="O48">
-        <v>10.1</v>
+        <v>139</v>
+      </c>
+      <c r="O48" t="s">
+        <v>139</v>
       </c>
       <c r="P48" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q48" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R48" t="s">
         <v>26</v>
@@ -3509,10 +3482,10 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C49" t="s">
         <v>19</v>
@@ -3521,24 +3494,24 @@
         <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F49" t="s">
         <v>22</v>
       </c>
-      <c r="G49" t="s">
-        <v>33</v>
+      <c r="G49" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H49" s="1">
         <v>27</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" t="s">
         <v>24</v>
       </c>
       <c r="J49" t="s">
         <v>25</v>
       </c>
-      <c r="K49" t="s">
+      <c r="K49" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L49" s="1">
@@ -3548,16 +3521,16 @@
         <v>611797</v>
       </c>
       <c r="N49" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O49">
         <v>9.85</v>
       </c>
       <c r="P49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R49" t="s">
         <v>26</v>
@@ -3565,10 +3538,10 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C50" t="s">
         <v>19</v>
@@ -3577,43 +3550,43 @@
         <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F50" t="s">
-        <v>99</v>
-      </c>
-      <c r="G50" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H50" s="1">
         <v>28</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" t="s">
         <v>24</v>
       </c>
       <c r="J50" t="s">
         <v>25</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L50" s="1">
         <v>46262</v>
       </c>
-      <c r="M50">
-        <v>612663</v>
+      <c r="M50" t="s">
+        <v>139</v>
       </c>
       <c r="N50" t="s">
-        <v>45</v>
-      </c>
-      <c r="O50">
-        <v>2.89</v>
+        <v>139</v>
+      </c>
+      <c r="O50" t="s">
+        <v>139</v>
       </c>
       <c r="P50" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R50" t="s">
         <v>26</v>
@@ -3621,10 +3594,10 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C51" t="s">
         <v>19</v>
@@ -3633,24 +3606,24 @@
         <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F51" t="s">
         <v>22</v>
       </c>
-      <c r="G51" t="s">
-        <v>33</v>
+      <c r="G51" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H51" s="1">
         <v>1</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>132</v>
+      <c r="I51" t="s">
+        <v>123</v>
       </c>
       <c r="J51" t="s">
         <v>25</v>
       </c>
-      <c r="K51" t="s">
+      <c r="K51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L51" s="1">
@@ -3660,16 +3633,16 @@
         <v>614020</v>
       </c>
       <c r="N51" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O51">
         <v>2.33</v>
       </c>
       <c r="P51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R51" t="s">
         <v>26</v>
@@ -3677,10 +3650,10 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C52" t="s">
         <v>19</v>
@@ -3689,43 +3662,43 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F52" t="s">
-        <v>99</v>
-      </c>
-      <c r="G52" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H52" s="1">
         <v>3</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>132</v>
+      <c r="I52" t="s">
+        <v>123</v>
       </c>
       <c r="J52" t="s">
         <v>25</v>
       </c>
-      <c r="K52" t="s">
+      <c r="K52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L52" s="1">
         <v>46268</v>
       </c>
-      <c r="M52">
-        <v>615019</v>
+      <c r="M52" t="s">
+        <v>139</v>
       </c>
       <c r="N52" t="s">
-        <v>45</v>
-      </c>
-      <c r="O52">
-        <v>7.95</v>
+        <v>139</v>
+      </c>
+      <c r="O52" t="s">
+        <v>139</v>
       </c>
       <c r="P52" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R52" t="s">
         <v>26</v>
@@ -3733,10 +3706,10 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C53" t="s">
         <v>19</v>
@@ -3745,24 +3718,24 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F53" t="s">
         <v>22</v>
       </c>
-      <c r="G53" t="s">
-        <v>33</v>
+      <c r="G53" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H53" s="1">
         <v>3</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>132</v>
+      <c r="I53" t="s">
+        <v>123</v>
       </c>
       <c r="J53" t="s">
         <v>25</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L53" s="1">
@@ -3772,16 +3745,16 @@
         <v>614995</v>
       </c>
       <c r="N53" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O53">
         <v>1.91</v>
       </c>
       <c r="P53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R53" t="s">
         <v>26</v>
@@ -3789,10 +3762,10 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C54" t="s">
         <v>19</v>
@@ -3801,24 +3774,24 @@
         <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F54" t="s">
         <v>22</v>
       </c>
-      <c r="G54" t="s">
-        <v>33</v>
+      <c r="G54" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H54" s="1">
         <v>4</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>132</v>
+      <c r="I54" t="s">
+        <v>123</v>
       </c>
       <c r="J54" t="s">
         <v>25</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L54" s="1">
@@ -3828,16 +3801,16 @@
         <v>615314</v>
       </c>
       <c r="N54" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O54">
         <v>12.23</v>
       </c>
       <c r="P54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R54" t="s">
         <v>26</v>
@@ -3845,10 +3818,10 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
         <v>19</v>
@@ -3857,24 +3830,24 @@
         <v>20</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F55" t="s">
         <v>22</v>
       </c>
-      <c r="G55" t="s">
-        <v>33</v>
+      <c r="G55" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H55" s="1">
         <v>4</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>132</v>
+      <c r="I55" t="s">
+        <v>123</v>
       </c>
       <c r="J55" t="s">
         <v>25</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K55" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L55" s="1">
@@ -3884,16 +3857,16 @@
         <v>615322</v>
       </c>
       <c r="N55" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O55">
         <v>16.34</v>
       </c>
       <c r="P55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R55" t="s">
         <v>26</v>
@@ -3901,10 +3874,10 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
         <v>19</v>
@@ -3913,24 +3886,24 @@
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F56" t="s">
         <v>22</v>
       </c>
-      <c r="G56" t="s">
-        <v>33</v>
+      <c r="G56" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H56" s="1">
         <v>4</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>132</v>
+      <c r="I56" t="s">
+        <v>123</v>
       </c>
       <c r="J56" t="s">
         <v>25</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K56" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L56" s="1">
@@ -3940,16 +3913,16 @@
         <v>615654</v>
       </c>
       <c r="N56" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O56">
         <v>11.93</v>
       </c>
       <c r="P56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R56" t="e">
         <v>#N/A</v>
@@ -3957,10 +3930,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C57" t="s">
         <v>19</v>
@@ -3969,24 +3942,24 @@
         <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F57" t="s">
-        <v>99</v>
-      </c>
-      <c r="G57" t="s">
-        <v>141</v>
+        <v>94</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="H57" s="1">
         <v>8</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>132</v>
+      <c r="I57" t="s">
+        <v>123</v>
       </c>
       <c r="J57" t="s">
         <v>25</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L57" s="1">
@@ -3996,16 +3969,16 @@
         <v>616899</v>
       </c>
       <c r="N57" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O57">
         <v>6.36</v>
       </c>
       <c r="P57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R57" t="e">
         <v>#N/A</v>
@@ -4013,10 +3986,10 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C58" t="s">
         <v>19</v>
@@ -4025,24 +3998,24 @@
         <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F58" t="s">
         <v>22</v>
       </c>
-      <c r="G58" t="s">
-        <v>33</v>
+      <c r="G58" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H58" s="1">
         <v>8</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>132</v>
+      <c r="I58" t="s">
+        <v>123</v>
       </c>
       <c r="J58" t="s">
         <v>25</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L58" s="1">
@@ -4052,16 +4025,16 @@
         <v>616788</v>
       </c>
       <c r="N58" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O58">
         <v>32.82</v>
       </c>
       <c r="P58" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R58" t="e">
         <v>#N/A</v>
@@ -4069,10 +4042,10 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
         <v>19</v>
@@ -4081,24 +4054,24 @@
         <v>20</v>
       </c>
       <c r="E59" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F59" t="s">
-        <v>99</v>
-      </c>
-      <c r="G59" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H59" s="1">
         <v>9</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>132</v>
+      <c r="I59" t="s">
+        <v>123</v>
       </c>
       <c r="J59" t="s">
         <v>25</v>
       </c>
-      <c r="K59" t="s">
+      <c r="K59" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L59" s="1">
@@ -4108,16 +4081,16 @@
         <v>617206</v>
       </c>
       <c r="N59" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O59">
         <v>21.23</v>
       </c>
       <c r="P59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R59" t="e">
         <v>#N/A</v>
@@ -4125,10 +4098,10 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C60" t="s">
         <v>19</v>
@@ -4137,24 +4110,24 @@
         <v>20</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F60" t="s">
         <v>22</v>
       </c>
-      <c r="G60" t="s">
-        <v>33</v>
+      <c r="G60" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H60" s="1">
         <v>9</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>132</v>
+      <c r="I60" t="s">
+        <v>123</v>
       </c>
       <c r="J60" t="s">
         <v>25</v>
       </c>
-      <c r="K60" t="s">
+      <c r="K60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L60" s="1">
@@ -4164,13 +4137,16 @@
         <v>617229</v>
       </c>
       <c r="N60" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O60">
         <v>2.2200000000000002</v>
       </c>
       <c r="P60" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>28</v>
       </c>
       <c r="R60" t="e">
         <v>#N/A</v>
@@ -4178,10 +4154,10 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s">
         <v>19</v>
@@ -4190,24 +4166,24 @@
         <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F61" t="s">
         <v>22</v>
       </c>
-      <c r="G61" t="s">
-        <v>44</v>
+      <c r="G61" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H61" s="1">
         <v>10</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>132</v>
+      <c r="I61" t="s">
+        <v>123</v>
       </c>
       <c r="J61" t="s">
         <v>25</v>
       </c>
-      <c r="K61" t="s">
+      <c r="K61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L61" s="1">
@@ -4217,20 +4193,135 @@
         <v>617914</v>
       </c>
       <c r="N61" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="O61">
         <v>8.4600000000000009</v>
       </c>
       <c r="P61" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q61" t="s">
         <v>28</v>
       </c>
       <c r="R61" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" s="1">
+        <v>11</v>
+      </c>
+      <c r="I62" t="s">
+        <v>123</v>
+      </c>
+      <c r="J62" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="1">
+        <v>46276</v>
+      </c>
+      <c r="M62">
+        <v>615347</v>
+      </c>
+      <c r="N62" t="s">
+        <v>138</v>
+      </c>
+      <c r="O62">
+        <v>2.76</v>
+      </c>
+      <c r="P62" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>28</v>
+      </c>
+      <c r="R62" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63" s="1">
+        <v>11</v>
+      </c>
+      <c r="I63" t="s">
+        <v>123</v>
+      </c>
+      <c r="J63" t="s">
+        <v>25</v>
+      </c>
+      <c r="K63" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="1">
+        <v>46276</v>
+      </c>
+      <c r="M63">
+        <v>618930</v>
+      </c>
+      <c r="N63" t="s">
+        <v>138</v>
+      </c>
+      <c r="O63">
+        <v>17.97</v>
+      </c>
+      <c r="P63" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>28</v>
+      </c>
+      <c r="R63" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4246,40 +4337,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
         <v>75</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>76</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>77</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>78</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>79</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>80</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>81</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>82</v>
-      </c>
-      <c r="K1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -4287,10 +4378,10 @@
         <v>46204</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>937.51199999999994</v>
@@ -4325,10 +4416,10 @@
         <v>46235</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>279.04500000000002</v>
@@ -4363,13 +4454,13 @@
         <v>46235</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>51.615999999997996</v>
@@ -4387,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K4">
         <v>12</v>
@@ -4401,13 +4492,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>104.44589999999999</v>
@@ -4425,7 +4516,7 @@
         <v>4.0816326530612242E-2</v>
       </c>
       <c r="J5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K5">
         <v>13</v>
@@ -4439,13 +4530,13 @@
         <v>46235</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>3.7643</v>
@@ -4463,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -4477,10 +4568,10 @@
         <v>46235</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>121.46199999999999</v>
@@ -4515,13 +4606,13 @@
         <v>46235</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>242.07859999999999</v>
@@ -4553,13 +4644,13 @@
         <v>46235</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E9">
         <v>450.55970000000002</v>
@@ -4591,10 +4682,10 @@
         <v>46235</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>241.82899999999998</v>
@@ -4629,13 +4720,13 @@
         <v>46235</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E11">
         <v>244.2174</v>
@@ -4667,13 +4758,13 @@
         <v>46235</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E12">
         <v>196.87350000000001</v>
@@ -4705,10 +4796,10 @@
         <v>46235</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>241.82899999999998</v>
@@ -4743,13 +4834,13 @@
         <v>46235</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E14">
         <v>37.135120000000001</v>
@@ -4781,13 +4872,13 @@
         <v>46235</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E15">
         <v>32.418210000000002</v>
@@ -4819,10 +4910,10 @@
         <v>46235</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16">
         <v>344.77100000000002</v>
@@ -4857,13 +4948,13 @@
         <v>46235</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E17">
         <v>7.3949699999999998</v>
@@ -4895,13 +4986,13 @@
         <v>46235</v>
       </c>
       <c r="B18" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E18">
         <v>43.323610000000002</v>
@@ -4933,37 +5024,37 @@
         <v>46266</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19">
+        <v>115.85599999999999</v>
+      </c>
+      <c r="E19">
+        <v>69.57874000000001</v>
+      </c>
+      <c r="F19">
         <v>30</v>
       </c>
-      <c r="D19">
-        <v>68.915999999999997</v>
-      </c>
-      <c r="E19">
-        <v>46.350480000000005</v>
-      </c>
-      <c r="F19">
-        <v>20</v>
-      </c>
       <c r="G19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19">
-        <v>0.65</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="J19">
-        <v>1.1333333333333333</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="K19">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L19">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -4971,37 +5062,37 @@
         <v>46266</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E20">
-        <v>30.749839999999999</v>
+        <v>54.136720000000004</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H20">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I20">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J20">
-        <v>0.6333333333333333</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="K20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -5009,37 +5100,37 @@
         <v>46266</v>
       </c>
       <c r="B21" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E21">
-        <v>77.769009999999994</v>
+        <v>120.63414</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G21">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>0.17857142857142858</v>
+        <v>0.21052631578947367</v>
       </c>
       <c r="J21">
-        <v>0.96666666666666667</v>
+        <v>0.97777777777777775</v>
       </c>
       <c r="K21">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L21">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -5063,13 +5154,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5077,7 +5168,7 @@
         <v>46204</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -5088,7 +5179,7 @@
         <v>46204</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C3">
         <v>15</v>
@@ -5099,7 +5190,7 @@
         <v>46235</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -5110,7 +5201,7 @@
         <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -5121,7 +5212,7 @@
         <v>46235</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -5132,7 +5223,7 @@
         <v>46266</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -5143,7 +5234,7 @@
         <v>46266</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -5154,7 +5245,7 @@
         <v>46266</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>17</v>
@@ -5167,15 +5258,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
@@ -5186,7 +5268,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -5447,15 +5529,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5466,7 +5549,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5483,4 +5566,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE957350-F75A-4875-9301-CCFC486384A5}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A715BF21-69AF-436F-A41F-07B3675F17B3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -5226,7 +5226,7 @@
         <v>71</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5237,7 +5237,7 @@
         <v>72</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5248,7 +5248,7 @@
         <v>70</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5258,14 +5258,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5530,21 +5528,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5569,9 +5566,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>